--- a/database/event/6975/event_6975_evp_summary.xlsx
+++ b/database/event/6975/event_6975_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6131</v>
+        <v>7.0084</v>
       </c>
       <c r="C2" t="n">
-        <v>3.80655</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2.556755845020386</v>
+        <v>2.4099</v>
       </c>
       <c r="E2" t="n">
-        <v>98.0089</v>
+        <v>7.0084</v>
       </c>
       <c r="F2" t="n">
-        <v>40.57093014716196</v>
+        <v>4.1843</v>
       </c>
       <c r="G2" t="n">
-        <v>57.4380146457191</v>
+        <v>2.8241</v>
       </c>
       <c r="H2" t="n">
-        <v>44.18163361873363</v>
+        <v>4.2741</v>
       </c>
       <c r="I2" t="n">
-        <v>43.15415376713517</v>
+        <v>3.4642</v>
       </c>
       <c r="J2" t="n">
-        <v>57.4380146457191</v>
+        <v>2.8241</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -541,7 +529,7 @@
         <v>115</v>
       </c>
       <c r="M2" t="n">
-        <v>100.5922</v>
+        <v>6.2883</v>
       </c>
       <c r="N2" t="n">
         <v>220</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7917</v>
+        <v>6.523</v>
       </c>
       <c r="C3" t="n">
-        <v>3.39585</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.101691565902438</v>
+        <v>2.2138</v>
       </c>
       <c r="E3" t="n">
-        <v>78.20829999999999</v>
+        <v>6.523</v>
       </c>
       <c r="F3" t="n">
-        <v>42.75492202206242</v>
+        <v>3.2686</v>
       </c>
       <c r="G3" t="n">
-        <v>35.4533593453543</v>
+        <v>3.2544</v>
       </c>
       <c r="H3" t="n">
-        <v>47.8603717937165</v>
+        <v>3.2686</v>
       </c>
       <c r="I3" t="n">
-        <v>62.77499928292117</v>
+        <v>3.2838</v>
       </c>
       <c r="J3" t="n">
-        <v>35.4533593453543</v>
+        <v>3.2544</v>
       </c>
       <c r="K3" t="n">
         <v>141</v>
@@ -587,7 +575,7 @@
         <v>117</v>
       </c>
       <c r="M3" t="n">
-        <v>98.22839999999999</v>
+        <v>6.5382</v>
       </c>
       <c r="N3" t="n">
         <v>258</v>
@@ -596,81 +584,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6588</v>
+        <v>6.3702</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3294</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.033732049344225</v>
+        <v>2.1521</v>
       </c>
       <c r="E4" t="n">
-        <v>75.2512</v>
+        <v>6.3702</v>
       </c>
       <c r="F4" t="n">
-        <v>12.92633521543459</v>
+        <v>4.1142</v>
       </c>
       <c r="G4" t="n">
-        <v>62.32490562897139</v>
+        <v>2.256</v>
       </c>
       <c r="H4" t="n">
-        <v>12.92633521543459</v>
+        <v>4.1142</v>
       </c>
       <c r="I4" t="n">
-        <v>13.70792757729807</v>
+        <v>3.3347</v>
       </c>
       <c r="J4" t="n">
-        <v>62.32490562897139</v>
+        <v>2.256</v>
       </c>
       <c r="K4" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="L4" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="M4" t="n">
-        <v>76.03279999999999</v>
+        <v>5.5907</v>
       </c>
       <c r="N4" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.5145</v>
+        <v>5.6307</v>
       </c>
       <c r="C5" t="n">
-        <v>3.25725</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.961637723991719</v>
+        <v>1.8533</v>
       </c>
       <c r="E5" t="n">
-        <v>72.1143</v>
+        <v>5.6307</v>
       </c>
       <c r="F5" t="n">
-        <v>32.41612405235478</v>
+        <v>2.9466</v>
       </c>
       <c r="G5" t="n">
-        <v>39.69816331823024</v>
+        <v>2.6841</v>
       </c>
       <c r="H5" t="n">
-        <v>32.77535411965762</v>
+        <v>2.9466</v>
       </c>
       <c r="I5" t="n">
-        <v>32.01313658199116</v>
+        <v>2.3883</v>
       </c>
       <c r="J5" t="n">
-        <v>39.69816331823024</v>
+        <v>2.6841</v>
       </c>
       <c r="K5" t="n">
         <v>105</v>
@@ -679,7 +667,7 @@
         <v>115</v>
       </c>
       <c r="M5" t="n">
-        <v>71.71129999999999</v>
+        <v>5.0724</v>
       </c>
       <c r="N5" t="n">
         <v>220</v>
@@ -688,127 +676,127 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.441</v>
+        <v>5.6181</v>
       </c>
       <c r="C6" t="n">
-        <v>2.7205</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.476455174699965</v>
+        <v>1.8482</v>
       </c>
       <c r="E6" t="n">
-        <v>51.0031</v>
+        <v>5.6181</v>
       </c>
       <c r="F6" t="n">
-        <v>15.71543873771552</v>
+        <v>4.0919</v>
       </c>
       <c r="G6" t="n">
-        <v>35.28768522304107</v>
+        <v>1.5262</v>
       </c>
       <c r="H6" t="n">
-        <v>15.71543873771552</v>
+        <v>4.0919</v>
       </c>
       <c r="I6" t="n">
-        <v>15.34996341823376</v>
+        <v>3.3166</v>
       </c>
       <c r="J6" t="n">
-        <v>35.28768522304107</v>
+        <v>1.5262</v>
       </c>
       <c r="K6" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="L6" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>50.6376</v>
+        <v>4.8428</v>
       </c>
       <c r="N6" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2593</v>
+        <v>5.5371</v>
       </c>
       <c r="C7" t="n">
-        <v>2.12965</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.033743150128742</v>
+        <v>1.8155</v>
       </c>
       <c r="E7" t="n">
-        <v>31.7399</v>
+        <v>5.5371</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.295932175829227</v>
+        <v>1.3924</v>
       </c>
       <c r="G7" t="n">
-        <v>37.03586147333549</v>
+        <v>4.1447</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.295932175829227</v>
+        <v>1.3924</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.946292435273684</v>
+        <v>1.3989</v>
       </c>
       <c r="J7" t="n">
-        <v>37.03586147333549</v>
+        <v>4.1447</v>
       </c>
       <c r="K7" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="L7" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="M7" t="n">
-        <v>30.0896</v>
+        <v>5.543600000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>258</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0573</v>
+        <v>4.376</v>
       </c>
       <c r="C8" t="n">
-        <v>2.02865</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9664199682885337</v>
+        <v>1.3464</v>
       </c>
       <c r="E8" t="n">
-        <v>28.8106</v>
+        <v>4.376</v>
       </c>
       <c r="F8" t="n">
-        <v>20.81035212842676</v>
+        <v>3.5956</v>
       </c>
       <c r="G8" t="n">
-        <v>8.000224711591237</v>
+        <v>0.7804</v>
       </c>
       <c r="H8" t="n">
-        <v>20.81035212842676</v>
+        <v>3.5956</v>
       </c>
       <c r="I8" t="n">
-        <v>22.06865248968047</v>
+        <v>2.9143</v>
       </c>
       <c r="J8" t="n">
-        <v>8.000224711591237</v>
+        <v>0.7804</v>
       </c>
       <c r="K8" t="n">
         <v>114</v>
@@ -817,7 +805,7 @@
         <v>101</v>
       </c>
       <c r="M8" t="n">
-        <v>30.0689</v>
+        <v>3.6947</v>
       </c>
       <c r="N8" t="n">
         <v>215</v>
@@ -826,219 +814,219 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9145</v>
+        <v>2.8676</v>
       </c>
       <c r="C9" t="n">
-        <v>1.45725</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6253829607375901</v>
+        <v>0.7371</v>
       </c>
       <c r="E9" t="n">
-        <v>13.9714</v>
+        <v>2.8676</v>
       </c>
       <c r="F9" t="n">
-        <v>-9.172351125462527</v>
+        <v>2.6303</v>
       </c>
       <c r="G9" t="n">
-        <v>23.14379575489994</v>
+        <v>0.2373</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.172351125462527</v>
+        <v>2.6303</v>
       </c>
       <c r="I9" t="n">
-        <v>-9.726958402816074</v>
+        <v>2.1319</v>
       </c>
       <c r="J9" t="n">
-        <v>23.14379575489994</v>
+        <v>0.2373</v>
       </c>
       <c r="K9" t="n">
         <v>114</v>
       </c>
       <c r="L9" t="n">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="M9" t="n">
-        <v>13.4168</v>
+        <v>2.3692</v>
       </c>
       <c r="N9" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2698</v>
+        <v>2.7621</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1349</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4598054250024148</v>
+        <v>0.6945</v>
       </c>
       <c r="E10" t="n">
-        <v>6.7669</v>
+        <v>2.7621</v>
       </c>
       <c r="F10" t="n">
-        <v>6.766868910453686</v>
+        <v>-0.1615</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.9236</v>
       </c>
       <c r="H10" t="n">
-        <v>6.766868910453686</v>
+        <v>-0.1615</v>
       </c>
       <c r="I10" t="n">
-        <v>5.287599892819625</v>
+        <v>-0.1623</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2.9236</v>
       </c>
       <c r="K10" t="n">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2876</v>
+        <v>2.7613</v>
       </c>
       <c r="N10" t="n">
-        <v>84</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2352</v>
+        <v>2.7532</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1176</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4514126399547268</v>
+        <v>0.6909</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4017</v>
+        <v>2.7532</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.789379537497215</v>
+        <v>0.2537</v>
       </c>
       <c r="G11" t="n">
-        <v>16.19106330915325</v>
+        <v>2.4995</v>
       </c>
       <c r="H11" t="n">
-        <v>-9.789379537497215</v>
+        <v>0.2537</v>
       </c>
       <c r="I11" t="n">
-        <v>-9.561719548253093</v>
+        <v>0.2549</v>
       </c>
       <c r="J11" t="n">
-        <v>16.19106330915325</v>
+        <v>2.4995</v>
       </c>
       <c r="K11" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="L11" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="M11" t="n">
-        <v>6.6293</v>
+        <v>2.7544</v>
       </c>
       <c r="N11" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.984</v>
+        <v>1.9353</v>
       </c>
       <c r="C12" t="n">
-        <v>0.992</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3918852439410437</v>
+        <v>0.3605</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8115</v>
+        <v>1.9353</v>
       </c>
       <c r="F12" t="n">
-        <v>25.38733718120478</v>
+        <v>2.5877</v>
       </c>
       <c r="G12" t="n">
-        <v>-21.57579723570426</v>
+        <v>-0.6524</v>
       </c>
       <c r="H12" t="n">
-        <v>25.38733718120478</v>
+        <v>2.5877</v>
       </c>
       <c r="I12" t="n">
-        <v>21.49067612548497</v>
+        <v>2.5998</v>
       </c>
       <c r="J12" t="n">
-        <v>-21.57579723570426</v>
+        <v>-0.6524</v>
       </c>
       <c r="K12" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0851</v>
+        <v>1.9474</v>
       </c>
       <c r="N12" t="n">
-        <v>133</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9687</v>
+        <v>1.8431</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9843499999999999</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3883420160528906</v>
+        <v>0.3232</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6574</v>
+        <v>1.8431</v>
       </c>
       <c r="F13" t="n">
-        <v>22.90131815968952</v>
+        <v>0.6952</v>
       </c>
       <c r="G13" t="n">
-        <v>-19.24395041814451</v>
+        <v>1.1479</v>
       </c>
       <c r="H13" t="n">
-        <v>22.90131815968952</v>
+        <v>0.6952</v>
       </c>
       <c r="I13" t="n">
-        <v>23.64694247186545</v>
+        <v>0.6985</v>
       </c>
       <c r="J13" t="n">
-        <v>-19.24395041814451</v>
+        <v>1.1479</v>
       </c>
       <c r="K13" t="n">
         <v>111</v>
@@ -1047,7 +1035,7 @@
         <v>65</v>
       </c>
       <c r="M13" t="n">
-        <v>4.403</v>
+        <v>1.8464</v>
       </c>
       <c r="N13" t="n">
         <v>176</v>
@@ -1056,737 +1044,737 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7885</v>
+        <v>1.7889</v>
       </c>
       <c r="C14" t="n">
-        <v>0.89425</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3472634247555237</v>
+        <v>0.3013</v>
       </c>
       <c r="E14" t="n">
-        <v>1.87</v>
+        <v>1.7889</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.31355759120674</v>
+        <v>2.41</v>
       </c>
       <c r="G14" t="n">
-        <v>12.1835221073262</v>
+        <v>-0.6211</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.31355759120674</v>
+        <v>2.41</v>
       </c>
       <c r="I14" t="n">
-        <v>-10.64934783836231</v>
+        <v>1.9534</v>
       </c>
       <c r="J14" t="n">
-        <v>12.1835221073262</v>
+        <v>-0.6211</v>
       </c>
       <c r="K14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L14" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5342</v>
+        <v>1.3323</v>
       </c>
       <c r="N14" t="n">
-        <v>176</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7186</v>
+        <v>1.6551</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8593</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3316662109890417</v>
+        <v>0.2473</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1913</v>
+        <v>1.6551</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.007857188991558819</v>
+        <v>2.3315</v>
       </c>
       <c r="G15" t="n">
-        <v>1.199158943964957</v>
+        <v>-0.6764</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.007857188991558819</v>
+        <v>2.3315</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.00833227483756005</v>
+        <v>2.3423</v>
       </c>
       <c r="J15" t="n">
-        <v>1.199158943964957</v>
+        <v>-0.6764</v>
       </c>
       <c r="K15" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L15" t="n">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1908</v>
+        <v>1.6659</v>
       </c>
       <c r="N15" t="n">
-        <v>240</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6214</v>
+        <v>1.3605</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8107</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3102744032477135</v>
+        <v>0.1282</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2605</v>
+        <v>1.3605</v>
       </c>
       <c r="F16" t="n">
-        <v>11.10152922514734</v>
+        <v>1.9955</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.84102341392345</v>
+        <v>-0.635</v>
       </c>
       <c r="H16" t="n">
-        <v>11.10152922514734</v>
+        <v>1.9955</v>
       </c>
       <c r="I16" t="n">
-        <v>11.77278448062136</v>
+        <v>1.9955</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.84102341392345</v>
+        <v>-0.635</v>
       </c>
       <c r="K16" t="n">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="L16" t="n">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9318</v>
+        <v>1.3605</v>
       </c>
       <c r="N16" t="n">
-        <v>215</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5223</v>
+        <v>1.0214</v>
       </c>
       <c r="C17" t="n">
-        <v>0.76115</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2888066825906551</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6736</v>
+        <v>1.0214</v>
       </c>
       <c r="F17" t="n">
-        <v>17.41293606781132</v>
+        <v>1.0214</v>
       </c>
       <c r="G17" t="n">
-        <v>-18.0865293075308</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>17.41293606781132</v>
+        <v>1.0214</v>
       </c>
       <c r="I17" t="n">
-        <v>17.97986887001912</v>
+        <v>1.0214</v>
       </c>
       <c r="J17" t="n">
-        <v>-18.0865293075308</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L17" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1067</v>
+        <v>1.0214</v>
       </c>
       <c r="N17" t="n">
-        <v>176</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1447</v>
+        <v>1.0131</v>
       </c>
       <c r="C18" t="n">
-        <v>0.57235</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2102049984668687</v>
+        <v>-0.0121</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.0937</v>
+        <v>1.0131</v>
       </c>
       <c r="F18" t="n">
-        <v>15.93121391401934</v>
+        <v>1.0131</v>
       </c>
       <c r="G18" t="n">
-        <v>-20.0249074855567</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>15.93121391401934</v>
+        <v>1.0131</v>
       </c>
       <c r="I18" t="n">
-        <v>16.89449661579725</v>
+        <v>1.0131</v>
       </c>
       <c r="J18" t="n">
-        <v>-20.0249074855567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1304</v>
+        <v>1.0131</v>
       </c>
       <c r="N18" t="n">
-        <v>215</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0624</v>
+        <v>0.9377</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5312</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1937012911910479</v>
+        <v>-0.0426</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.8118</v>
+        <v>0.9377</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.811799492033519</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3384</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.811799492033519</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.476092550728854</v>
+        <v>0.6021</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3384</v>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.4761</v>
+        <v>0.9404999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5314</v>
+        <v>0.5977</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2657</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09260093009773342</v>
+        <v>-0.1799</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.210900000000001</v>
+        <v>0.5977</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.15558294735909</v>
+        <v>0.5977</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9447253132937889</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.15558294735909</v>
+        <v>0.5977</v>
       </c>
       <c r="I20" t="n">
-        <v>-10.48622983401729</v>
+        <v>0.5977</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9447253132937889</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-9.541499999999999</v>
+        <v>0.5977</v>
       </c>
       <c r="N20" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2877</v>
+        <v>0.1012</v>
       </c>
       <c r="C21" t="n">
-        <v>0.14385</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.04911634121291959</v>
+        <v>-0.3805</v>
       </c>
       <c r="E21" t="n">
-        <v>-11.103</v>
+        <v>0.1012</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.10295013223239</v>
+        <v>-0.3277</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.4289</v>
       </c>
       <c r="H21" t="n">
-        <v>-11.10295013223239</v>
+        <v>-0.3277</v>
       </c>
       <c r="I21" t="n">
-        <v>-10.32832570440222</v>
+        <v>-0.3277</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.4289</v>
       </c>
       <c r="K21" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M21" t="n">
-        <v>-10.3283</v>
+        <v>0.1012</v>
       </c>
       <c r="N21" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.0906</v>
+        <v>0.0622</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0453</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.01521412348921554</v>
+        <v>-0.3962</v>
       </c>
       <c r="E22" t="n">
-        <v>-13.9021</v>
+        <v>0.0622</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.839101631877019</v>
+        <v>0.0622</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.06298246454978</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.839101631877019</v>
+        <v>0.0622</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.9428674279145</v>
+        <v>0.0622</v>
       </c>
       <c r="J22" t="n">
-        <v>-8.06298246454978</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-13.0058</v>
+        <v>0.0622</v>
       </c>
       <c r="N22" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3172</v>
+        <v>0.0422</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1586</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05429099528187224</v>
+        <v>-0.4043</v>
       </c>
       <c r="E23" t="n">
-        <v>-15.6024</v>
+        <v>0.0422</v>
       </c>
       <c r="F23" t="n">
-        <v>-17.23233655885358</v>
+        <v>0.5565</v>
       </c>
       <c r="G23" t="n">
-        <v>1.629947644860843</v>
+        <v>-0.5143</v>
       </c>
       <c r="H23" t="n">
-        <v>-17.23233655885358</v>
+        <v>0.5565</v>
       </c>
       <c r="I23" t="n">
-        <v>-14.58737327307605</v>
+        <v>0.5591</v>
       </c>
       <c r="J23" t="n">
-        <v>1.629947644860843</v>
+        <v>-0.5143</v>
       </c>
       <c r="K23" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L23" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="M23" t="n">
-        <v>-12.9574</v>
+        <v>0.04480000000000006</v>
       </c>
       <c r="N23" t="n">
-        <v>133</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.5564</v>
+        <v>0.0277</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.2782</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09716505445434272</v>
+        <v>-0.4102</v>
       </c>
       <c r="E24" t="n">
-        <v>-17.4679</v>
+        <v>0.0277</v>
       </c>
       <c r="F24" t="n">
-        <v>19.83463087652586</v>
+        <v>0.157</v>
       </c>
       <c r="G24" t="n">
-        <v>-37.30254704526823</v>
+        <v>-0.1293</v>
       </c>
       <c r="H24" t="n">
-        <v>19.83463087652586</v>
+        <v>0.157</v>
       </c>
       <c r="I24" t="n">
-        <v>21.03393413882742</v>
+        <v>0.157</v>
       </c>
       <c r="J24" t="n">
-        <v>-37.30254704526823</v>
+        <v>-0.1293</v>
       </c>
       <c r="K24" t="n">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="L24" t="n">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="M24" t="n">
-        <v>-16.2686</v>
+        <v>0.0277</v>
       </c>
       <c r="N24" t="n">
-        <v>215</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6807</v>
+        <v>-0.0711</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.34035</v>
+        <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1201386001647244</v>
+        <v>-0.4501</v>
       </c>
       <c r="E25" t="n">
-        <v>-18.4675</v>
+        <v>-0.0711</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.102994516561873</v>
+        <v>-0.0711</v>
       </c>
       <c r="G25" t="n">
-        <v>-17.36454185349032</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.102994516561873</v>
+        <v>-0.0711</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.138905965938307</v>
+        <v>-0.0711</v>
       </c>
       <c r="J25" t="n">
-        <v>-17.36454185349032</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-18.5034</v>
+        <v>-0.0711</v>
       </c>
       <c r="N25" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7461</v>
+        <v>-0.1871</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.37305</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1324124025180801</v>
+        <v>-0.4969</v>
       </c>
       <c r="E26" t="n">
-        <v>-19.0016</v>
+        <v>-0.1871</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.530068046424012</v>
+        <v>0.0143</v>
       </c>
       <c r="G26" t="n">
-        <v>-12.47152349012143</v>
+        <v>-0.2014</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.530068046424012</v>
+        <v>0.0143</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.924909370161277</v>
+        <v>0.0116</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.47152349012143</v>
+        <v>-0.2014</v>
       </c>
       <c r="K26" t="n">
         <v>114</v>
       </c>
       <c r="L26" t="n">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="M26" t="n">
-        <v>-19.3964</v>
+        <v>-0.1898</v>
       </c>
       <c r="N26" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.4183</v>
+        <v>-0.3122</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.7091499999999999</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2666619969044895</v>
+        <v>-0.5475</v>
       </c>
       <c r="E27" t="n">
-        <v>-24.843</v>
+        <v>-0.3122</v>
       </c>
       <c r="F27" t="n">
-        <v>-24.84303230751269</v>
+        <v>-1.4212</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1.109</v>
       </c>
       <c r="H27" t="n">
-        <v>-24.84303230751269</v>
+        <v>-1.4212</v>
       </c>
       <c r="I27" t="n">
-        <v>-23.10979749536064</v>
+        <v>-1.1519</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.109</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M27" t="n">
-        <v>-23.1098</v>
+        <v>-0.04289999999999994</v>
       </c>
       <c r="N27" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.5489</v>
+        <v>-0.3457</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.77445</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2945359688967402</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-26.0559</v>
+        <v>-0.3457</v>
       </c>
       <c r="F28" t="n">
-        <v>-26.05587885046519</v>
+        <v>0.1352</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.4809</v>
       </c>
       <c r="H28" t="n">
-        <v>-26.05587885046519</v>
+        <v>0.1352</v>
       </c>
       <c r="I28" t="n">
-        <v>-24.23802683764204</v>
+        <v>0.1358</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.4809</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M28" t="n">
-        <v>-24.238</v>
+        <v>-0.3451</v>
       </c>
       <c r="N28" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.9335</v>
+        <v>-0.3949</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.96675</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3802205345547994</v>
+        <v>-0.5809</v>
       </c>
       <c r="E29" t="n">
-        <v>-29.7842</v>
+        <v>-0.3949</v>
       </c>
       <c r="F29" t="n">
-        <v>-29.78416806850901</v>
+        <v>-0.1317</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.2632</v>
       </c>
       <c r="H29" t="n">
-        <v>-29.78416806850901</v>
+        <v>-0.1317</v>
       </c>
       <c r="I29" t="n">
-        <v>-23.27321039771867</v>
+        <v>-0.1317</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.2632</v>
       </c>
       <c r="K29" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M29" t="n">
-        <v>-23.2732</v>
+        <v>-0.3949</v>
       </c>
       <c r="N29" t="n">
-        <v>84</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
@@ -1796,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.0351</v>
+        <v>-0.4029</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.01755</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4038118235475289</v>
+        <v>-0.5841</v>
       </c>
       <c r="E30" t="n">
-        <v>-30.8107</v>
+        <v>-0.4029</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.522156582971203</v>
+        <v>0.3614</v>
       </c>
       <c r="G30" t="n">
-        <v>-27.28851080564117</v>
+        <v>-0.7643</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.522156582971203</v>
+        <v>0.3614</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.44024596476257</v>
+        <v>0.2929</v>
       </c>
       <c r="J30" t="n">
-        <v>-27.28851080564117</v>
+        <v>-0.7643</v>
       </c>
       <c r="K30" t="n">
         <v>105</v>
@@ -1829,7 +1817,7 @@
         <v>115</v>
       </c>
       <c r="M30" t="n">
-        <v>-30.7288</v>
+        <v>-0.4714</v>
       </c>
       <c r="N30" t="n">
         <v>220</v>
@@ -1838,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.1249</v>
+        <v>-0.5314</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.06245</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.424980082606576</v>
+        <v>-0.636</v>
       </c>
       <c r="E31" t="n">
-        <v>-31.7317</v>
+        <v>-0.5314</v>
       </c>
       <c r="F31" t="n">
-        <v>-31.73173632802388</v>
+        <v>-0.5314</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-31.73173632802388</v>
+        <v>-0.5314</v>
       </c>
       <c r="I31" t="n">
-        <v>-24.79503117724656</v>
+        <v>-0.5314</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1875,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-24.795</v>
+        <v>-0.5314</v>
       </c>
       <c r="N31" t="n">
         <v>84</v>
@@ -1884,262 +1872,262 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.1432</v>
+        <v>-0.5759</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.0716</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4293108385247122</v>
+        <v>-0.654</v>
       </c>
       <c r="E32" t="n">
-        <v>-31.9202</v>
+        <v>-0.5759</v>
       </c>
       <c r="F32" t="n">
-        <v>-31.92017528983179</v>
+        <v>-0.3457</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.2302</v>
       </c>
       <c r="H32" t="n">
-        <v>-31.92017528983179</v>
+        <v>-0.3457</v>
       </c>
       <c r="I32" t="n">
-        <v>-24.94227650554298</v>
+        <v>-0.3473</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.2302</v>
       </c>
       <c r="K32" t="n">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M32" t="n">
-        <v>-24.9423</v>
+        <v>-0.5775</v>
       </c>
       <c r="N32" t="n">
-        <v>84</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.1518</v>
+        <v>-0.6511</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.0759</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.4313604245932827</v>
+        <v>-0.6844</v>
       </c>
       <c r="E33" t="n">
-        <v>-32.0094</v>
+        <v>-0.6511</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.826665040869488</v>
+        <v>0.4675</v>
       </c>
       <c r="G33" t="n">
-        <v>-29.18269141691499</v>
+        <v>-1.1186</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.826665040869488</v>
+        <v>0.4675</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.997579671247643</v>
+        <v>0.4697</v>
       </c>
       <c r="J33" t="n">
-        <v>-29.18269141691499</v>
+        <v>-1.1186</v>
       </c>
       <c r="K33" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="L33" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="M33" t="n">
-        <v>-32.1803</v>
+        <v>-0.6489</v>
       </c>
       <c r="N33" t="n">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-2.1547</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.07735</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4320737452531973</v>
+        <v>-0.7042</v>
       </c>
       <c r="E34" t="n">
-        <v>-32.0404</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-5.682751724627068</v>
+        <v>-0.3964</v>
       </c>
       <c r="G34" t="n">
-        <v>-26.35764259516841</v>
+        <v>-0.3037</v>
       </c>
       <c r="H34" t="n">
-        <v>-5.682751724627068</v>
+        <v>-0.3964</v>
       </c>
       <c r="I34" t="n">
-        <v>-4.810515413405239</v>
+        <v>-0.3982</v>
       </c>
       <c r="J34" t="n">
-        <v>-26.35764259516841</v>
+        <v>-0.3037</v>
       </c>
       <c r="K34" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="L34" t="n">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="M34" t="n">
-        <v>-31.1682</v>
+        <v>-0.7019</v>
       </c>
       <c r="N34" t="n">
-        <v>133</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-2.2664</v>
+        <v>-1.0375</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.1332</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4589666375016603</v>
+        <v>-0.8405</v>
       </c>
       <c r="E35" t="n">
-        <v>-33.2106</v>
+        <v>-1.0375</v>
       </c>
       <c r="F35" t="n">
-        <v>-6.543602452778893</v>
+        <v>-0.216</v>
       </c>
       <c r="G35" t="n">
-        <v>-26.6669498697085</v>
+        <v>-0.8215</v>
       </c>
       <c r="H35" t="n">
-        <v>-6.543602452778893</v>
+        <v>-0.216</v>
       </c>
       <c r="I35" t="n">
-        <v>-8.582771589226269</v>
+        <v>-0.216</v>
       </c>
       <c r="J35" t="n">
-        <v>-26.6669498697085</v>
+        <v>-0.8215</v>
       </c>
       <c r="K35" t="n">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="L35" t="n">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="M35" t="n">
-        <v>-35.2497</v>
+        <v>-1.0375</v>
       </c>
       <c r="N35" t="n">
-        <v>258</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-2.3917</v>
+        <v>-1.0514</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.19585</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4897647508940474</v>
+        <v>-0.8461</v>
       </c>
       <c r="E36" t="n">
-        <v>-34.5506</v>
+        <v>-1.0514</v>
       </c>
       <c r="F36" t="n">
-        <v>-17.61216330823532</v>
+        <v>-1.0514</v>
       </c>
       <c r="G36" t="n">
-        <v>-16.93847019707742</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-17.61216330823532</v>
+        <v>-1.0514</v>
       </c>
       <c r="I36" t="n">
-        <v>-14.90890103301781</v>
+        <v>-1.0514</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.93847019707742</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L36" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-31.8474</v>
+        <v>-1.0514</v>
       </c>
       <c r="N36" t="n">
-        <v>133</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.6459</v>
+        <v>-1.101</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.32295</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.5542444944382677</v>
+        <v>-0.8661</v>
       </c>
       <c r="E37" t="n">
-        <v>-37.3563</v>
+        <v>-1.101</v>
       </c>
       <c r="F37" t="n">
-        <v>-37.3562628598164</v>
+        <v>-1.101</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-37.3562628598164</v>
+        <v>-1.101</v>
       </c>
       <c r="I37" t="n">
-        <v>-29.19001004860073</v>
+        <v>-1.101</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2151,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-29.19</v>
+        <v>-1.101</v>
       </c>
       <c r="N37" t="n">
         <v>84</v>
@@ -2164,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-4.0489</v>
+        <v>-1.1916</v>
       </c>
       <c r="C38" t="n">
-        <v>-2.02445</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9636846766999595</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>-55.1717</v>
+        <v>-1.1916</v>
       </c>
       <c r="F38" t="n">
-        <v>-39.88632636731008</v>
+        <v>-2.7756</v>
       </c>
       <c r="G38" t="n">
-        <v>-15.28541358848651</v>
+        <v>1.5839</v>
       </c>
       <c r="H38" t="n">
-        <v>-39.88632636731008</v>
+        <v>-2.7756</v>
       </c>
       <c r="I38" t="n">
-        <v>-52.31601877014624</v>
+        <v>-2.7885</v>
       </c>
       <c r="J38" t="n">
-        <v>-15.28541358848651</v>
+        <v>1.5839</v>
       </c>
       <c r="K38" t="n">
         <v>141</v>
@@ -2197,7 +2185,7 @@
         <v>117</v>
       </c>
       <c r="M38" t="n">
-        <v>-67.6014</v>
+        <v>-1.2046</v>
       </c>
       <c r="N38" t="n">
         <v>258</v>
@@ -2206,139 +2194,139 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-4.2444</v>
+        <v>-1.238</v>
       </c>
       <c r="C39" t="n">
-        <v>-2.1222</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.028704939480596</v>
+        <v>-0.9215</v>
       </c>
       <c r="E39" t="n">
-        <v>-58.0009</v>
+        <v>-1.238</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.942272757172604</v>
+        <v>-1.238</v>
       </c>
       <c r="G39" t="n">
-        <v>-55.05861551509937</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.942272757172604</v>
+        <v>-1.238</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.120177621559784</v>
+        <v>-1.238</v>
       </c>
       <c r="J39" t="n">
-        <v>-55.05861551509937</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="L39" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.1788</v>
+        <v>-1.238</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.0193</v>
+        <v>-2</v>
       </c>
       <c r="C40" t="n">
-        <v>-2.50965</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.308387053848685</v>
+        <v>-1.2293</v>
       </c>
       <c r="E40" t="n">
-        <v>-70.1704</v>
+        <v>-2</v>
       </c>
       <c r="F40" t="n">
-        <v>-31.99193722912855</v>
+        <v>-2</v>
       </c>
       <c r="G40" t="n">
-        <v>-38.17842174618096</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-31.99193722912855</v>
+        <v>-2</v>
       </c>
       <c r="I40" t="n">
-        <v>-41.96151766797327</v>
+        <v>-2</v>
       </c>
       <c r="J40" t="n">
-        <v>-38.17842174618096</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-80.1399</v>
+        <v>-2</v>
       </c>
       <c r="N40" t="n">
-        <v>258</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.1063</v>
+        <v>-3.2346</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.55315</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.342093880138247</v>
+        <v>-1.7281</v>
       </c>
       <c r="E41" t="n">
-        <v>-71.637</v>
+        <v>-3.2346</v>
       </c>
       <c r="F41" t="n">
-        <v>-71.63700347615644</v>
+        <v>-1.7443</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-1.4903</v>
       </c>
       <c r="H41" t="n">
-        <v>-71.63700347615644</v>
+        <v>-1.7443</v>
       </c>
       <c r="I41" t="n">
-        <v>-66.63907300107576</v>
+        <v>-1.7524</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-1.4903</v>
       </c>
       <c r="K41" t="n">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M41" t="n">
-        <v>-66.6391</v>
+        <v>-3.2427</v>
       </c>
       <c r="N41" t="n">
-        <v>100</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>2.986306484975163</v>
+        <v>2.2614</v>
       </c>
       <c r="J2" t="n">
-        <v>47.78090375960261</v>
+        <v>36.1824</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.79</v>
       </c>
       <c r="I3" t="n">
-        <v>2.086952955664335</v>
+        <v>1.5924</v>
       </c>
       <c r="J3" t="n">
-        <v>33.39124729062937</v>
+        <v>25.4784</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.51</v>
       </c>
       <c r="I4" t="n">
-        <v>1.194077338367777</v>
+        <v>1.0159</v>
       </c>
       <c r="J4" t="n">
-        <v>19.10523741388442</v>
+        <v>16.2544</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>1.23</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5596931245277657</v>
+        <v>0.4294</v>
       </c>
       <c r="J5" t="n">
-        <v>8.95508999244425</v>
+        <v>6.8704</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>1.12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3436377599563756</v>
+        <v>0.1687</v>
       </c>
       <c r="J6" t="n">
-        <v>5.498204159302009</v>
+        <v>2.6992</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3829039732819595</v>
+        <v>0.9721</v>
       </c>
       <c r="J7" t="n">
-        <v>6.126463572511352</v>
+        <v>15.5536</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>0.61</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.452814805614456</v>
+        <v>-0.5432</v>
       </c>
       <c r="J8" t="n">
-        <v>-23.24503688983129</v>
+        <v>-8.6912</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>0.57</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.550584059305181</v>
+        <v>-0.6031</v>
       </c>
       <c r="J9" t="n">
-        <v>-24.80934494888289</v>
+        <v>-9.6496</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.37</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9210979836392</v>
+        <v>-0.8666</v>
       </c>
       <c r="J10" t="n">
-        <v>-30.73756773822721</v>
+        <v>-13.8656</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.162685150085264</v>
+        <v>-1.0668</v>
       </c>
       <c r="J11" t="n">
-        <v>-34.60296240136423</v>
+        <v>-17.0688</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.28</v>
       </c>
       <c r="I12" t="n">
-        <v>1.036975714850427</v>
+        <v>0.8316</v>
       </c>
       <c r="J12" t="n">
-        <v>24.88741715641024</v>
+        <v>19.9584</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4697242891312823</v>
+        <v>0.393</v>
       </c>
       <c r="J13" t="n">
-        <v>11.27338293915078</v>
+        <v>9.432</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2375217875338124</v>
+        <v>-0.1541</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.700522900811497</v>
+        <v>-3.6984</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2711798171840684</v>
+        <v>-0.1937</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.508315612417641</v>
+        <v>-4.6488</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4776906224036179</v>
+        <v>-0.4206</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.46457493768683</v>
+        <v>-10.0944</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8598595032884149</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>20.63662807892196</v>
+        <v>15.6408</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4221280406837047</v>
+        <v>0.3641</v>
       </c>
       <c r="J18" t="n">
-        <v>10.13107297640891</v>
+        <v>8.7384</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06012519635203403</v>
+        <v>0.1678</v>
       </c>
       <c r="J19" t="n">
-        <v>1.443004712448817</v>
+        <v>4.0272</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2910077829119997</v>
+        <v>0.03</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.984186789887993</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.366331261317479</v>
+        <v>-0.7006</v>
       </c>
       <c r="J21" t="n">
-        <v>-32.7919502716195</v>
+        <v>-16.8144</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7196074338186359</v>
+        <v>1.035</v>
       </c>
       <c r="J22" t="n">
-        <v>16.55097097782863</v>
+        <v>23.805</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5339988843998869</v>
+        <v>0.7422</v>
       </c>
       <c r="J23" t="n">
-        <v>12.2819743411974</v>
+        <v>17.0706</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3245479268070632</v>
+        <v>0.4549</v>
       </c>
       <c r="J24" t="n">
-        <v>7.464602316562455</v>
+        <v>10.4627</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.07097473548338287</v>
+        <v>-0.0907</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.632418916117806</v>
+        <v>-2.0861</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4581289897720127</v>
+        <v>-0.6849</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.53696676475629</v>
+        <v>-15.7527</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5771712395033073</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>13.27493850857607</v>
+        <v>11.7438</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.08244541362928956</v>
+        <v>0.1398</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.89624451347366</v>
+        <v>3.2154</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3474964169757579</v>
+        <v>-0.1099</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.992417590442432</v>
+        <v>-2.5277</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4573236534619137</v>
+        <v>-0.2072</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.51844402962401</v>
+        <v>-4.7656</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.74</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7347349058810997</v>
+        <v>-0.4652</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.89890283526529</v>
+        <v>-10.6996</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.07</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2188507563368728</v>
+        <v>0.2507</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.939313614063711</v>
+        <v>4.5126</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>0.76</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7970234855977497</v>
+        <v>-0.3815</v>
       </c>
       <c r="J33" t="n">
-        <v>-14.3464227407595</v>
+        <v>-6.867</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>0.76</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7970234855977497</v>
+        <v>-0.3815</v>
       </c>
       <c r="J34" t="n">
-        <v>-14.3464227407595</v>
+        <v>-6.867</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8511924902873266</v>
+        <v>-0.4282</v>
       </c>
       <c r="J35" t="n">
-        <v>-15.32146482517188</v>
+        <v>-7.7076</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8679821708723859</v>
+        <v>-0.4432</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.62367907570295</v>
+        <v>-7.9776</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.92</v>
       </c>
       <c r="I37" t="n">
-        <v>1.803862842137898</v>
+        <v>1.0933</v>
       </c>
       <c r="J37" t="n">
-        <v>32.46953115848217</v>
+        <v>19.6794</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.53</v>
       </c>
       <c r="I38" t="n">
-        <v>1.236637408822683</v>
+        <v>0.6833</v>
       </c>
       <c r="J38" t="n">
-        <v>22.25947335880829</v>
+        <v>12.2994</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.38</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8284017071446135</v>
+        <v>0.4838</v>
       </c>
       <c r="J39" t="n">
-        <v>14.91123072860304</v>
+        <v>8.708399999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>1.37</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7968463250108566</v>
+        <v>0.4694</v>
       </c>
       <c r="J40" t="n">
-        <v>14.34323385019542</v>
+        <v>8.449199999999999</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3646754572094697</v>
+        <v>-0.481</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.564158229770454</v>
+        <v>-8.657999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.93</v>
       </c>
       <c r="I42" t="n">
-        <v>1.254245695066029</v>
+        <v>1.8519</v>
       </c>
       <c r="J42" t="n">
-        <v>25.08491390132057</v>
+        <v>37.038</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.32</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5199771107006224</v>
+        <v>0.7719</v>
       </c>
       <c r="J43" t="n">
-        <v>10.39954221401245</v>
+        <v>15.438</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3780461555412853</v>
+        <v>0.6294</v>
       </c>
       <c r="J44" t="n">
-        <v>7.560923110825707</v>
+        <v>12.588</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>1.03</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.04004423109236341</v>
+        <v>-0.0211</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8008846218472682</v>
+        <v>-0.422</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1594171305651382</v>
+        <v>-0.2926</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.188342611302764</v>
+        <v>-5.852</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.414940056577508</v>
+        <v>0.611</v>
       </c>
       <c r="J47" t="n">
-        <v>8.29880113155016</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.32</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3130534089784368</v>
+        <v>0.5605</v>
       </c>
       <c r="J48" t="n">
-        <v>6.261068179568737</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.87</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6964667452800183</v>
+        <v>-0.2644</v>
       </c>
       <c r="J49" t="n">
-        <v>-13.92933490560037</v>
+        <v>-5.288</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9831111029845782</v>
+        <v>-0.5514</v>
       </c>
       <c r="J50" t="n">
-        <v>-19.66222205969156</v>
+        <v>-11.028</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.096926125420556</v>
+        <v>-0.676</v>
       </c>
       <c r="J51" t="n">
-        <v>-21.93852250841113</v>
+        <v>-13.52</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.43</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6498063914498451</v>
+        <v>1.1025</v>
       </c>
       <c r="J52" t="n">
-        <v>18.84438535204551</v>
+        <v>31.9725</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2764461525422814</v>
+        <v>0.4549</v>
       </c>
       <c r="J53" t="n">
-        <v>8.016938423726161</v>
+        <v>13.1921</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1758754441119408</v>
+        <v>0.3219</v>
       </c>
       <c r="J54" t="n">
-        <v>5.100387879246283</v>
+        <v>9.335100000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.08835198456416295</v>
+        <v>0.1693</v>
       </c>
       <c r="J55" t="n">
-        <v>2.562207552360726</v>
+        <v>4.9097</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0565738922437987</v>
+        <v>-0.164</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.640642875070162</v>
+        <v>-4.756</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.697087949664615</v>
+        <v>0.7543</v>
       </c>
       <c r="J57" t="n">
-        <v>20.21555054027383</v>
+        <v>21.8747</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.006838458077140335</v>
+        <v>0.203</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1983152842370697</v>
+        <v>5.887</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.72</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.7229756090302788</v>
+        <v>-0.4787</v>
       </c>
       <c r="J59" t="n">
-        <v>-20.96629266187809</v>
+        <v>-13.8823</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7370853040324159</v>
+        <v>-0.4923</v>
       </c>
       <c r="J60" t="n">
-        <v>-21.37547381694006</v>
+        <v>-14.2767</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7913457369413016</v>
+        <v>-0.5455</v>
       </c>
       <c r="J61" t="n">
-        <v>-22.94902637129775</v>
+        <v>-15.8195</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1410328394059298</v>
+        <v>0.3616</v>
       </c>
       <c r="J62" t="n">
-        <v>3.102722466930455</v>
+        <v>7.9552</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.04</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.07201410422235649</v>
+        <v>0.1574</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.584310292891843</v>
+        <v>3.4628</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1560787568150957</v>
+        <v>0.0538</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.433732649932106</v>
+        <v>1.1836</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8836181544779061</v>
+        <v>-0.539</v>
       </c>
       <c r="J65" t="n">
-        <v>-19.43959939851393</v>
+        <v>-11.858</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9551818542668129</v>
+        <v>-0.6038</v>
       </c>
       <c r="J66" t="n">
-        <v>-21.01400079386988</v>
+        <v>-13.2836</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.66</v>
       </c>
       <c r="I67" t="n">
-        <v>1.101174092365054</v>
+        <v>0.8884</v>
       </c>
       <c r="J67" t="n">
-        <v>24.2258300320312</v>
+        <v>19.5448</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>1.27</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6102947090518434</v>
+        <v>0.4249</v>
       </c>
       <c r="J68" t="n">
-        <v>13.42648359914055</v>
+        <v>9.347799999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>1.09</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1887514884916905</v>
+        <v>0.1283</v>
       </c>
       <c r="J69" t="n">
-        <v>4.15253274681719</v>
+        <v>2.8226</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0917078519284423</v>
+        <v>0.0367</v>
       </c>
       <c r="J70" t="n">
-        <v>2.017572742425731</v>
+        <v>0.8074</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4327467952992303</v>
+        <v>-0.442</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.520429496583066</v>
+        <v>-9.724</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8020115162197297</v>
+        <v>1.4923</v>
       </c>
       <c r="J72" t="n">
-        <v>19.24827638927351</v>
+        <v>35.8152</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.11</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2127202296262872</v>
+        <v>0.3597</v>
       </c>
       <c r="J73" t="n">
-        <v>5.105285511030893</v>
+        <v>8.6328</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.06294551845789569</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.510692442989496</v>
+        <v>-1.7856</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2950267298636558</v>
+        <v>-0.3802</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.08064151672774</v>
+        <v>-9.1248</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5070098822759835</v>
+        <v>-0.6751</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.16823717462361</v>
+        <v>-16.2024</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.53</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7979142544130037</v>
+        <v>0.8034</v>
       </c>
       <c r="J77" t="n">
-        <v>19.14994210591209</v>
+        <v>19.2816</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.005640753991435231</v>
+        <v>0.1424</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.1353780957944455</v>
+        <v>3.4176</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5567262290806742</v>
+        <v>-0.3504</v>
       </c>
       <c r="J79" t="n">
-        <v>-13.36142949793618</v>
+        <v>-8.409599999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6494513357006204</v>
+        <v>-0.4365</v>
       </c>
       <c r="J80" t="n">
-        <v>-15.58683205681489</v>
+        <v>-10.476</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6494513357006204</v>
+        <v>-0.4365</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.58683205681489</v>
+        <v>-10.476</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5475085715964066</v>
+        <v>0.5177</v>
       </c>
       <c r="J82" t="n">
-        <v>12.59269714671735</v>
+        <v>11.9071</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.23</v>
       </c>
       <c r="I83" t="n">
-        <v>0.419908016357515</v>
+        <v>0.3824</v>
       </c>
       <c r="J83" t="n">
-        <v>9.657884376222846</v>
+        <v>8.795199999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3072347341159445</v>
+        <v>0.2754</v>
       </c>
       <c r="J84" t="n">
-        <v>7.066398884666723</v>
+        <v>6.3342</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>1.15</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2876856161735392</v>
+        <v>0.2585</v>
       </c>
       <c r="J85" t="n">
-        <v>6.6167691719914</v>
+        <v>5.9455</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3836002900110387</v>
+        <v>-0.4494</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.822806670253891</v>
+        <v>-10.3362</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3434104205848184</v>
+        <v>0.5265</v>
       </c>
       <c r="J87" t="n">
-        <v>7.898439673450824</v>
+        <v>12.1095</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.164638568447174</v>
+        <v>-0.0522</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.786687074285002</v>
+        <v>-1.2006</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.95</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2094609324732434</v>
+        <v>-0.0988</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.817601446884598</v>
+        <v>-2.2724</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2898621652304558</v>
+        <v>-0.1692</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.666829800300483</v>
+        <v>-3.8916</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6998298290574461</v>
+        <v>-0.6495</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.09608606832126</v>
+        <v>-14.9385</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.03607462305361943</v>
+        <v>0.4212</v>
       </c>
       <c r="J92" t="n">
-        <v>0.6854178380187691</v>
+        <v>8.002800000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.421920146312604</v>
+        <v>-0.2703</v>
       </c>
       <c r="J93" t="n">
-        <v>-8.016482779939476</v>
+        <v>-5.1357</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>0.74</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.5696513969916878</v>
+        <v>-0.403</v>
       </c>
       <c r="J94" t="n">
-        <v>-10.82337654284207</v>
+        <v>-7.657</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.67</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.6649316952107381</v>
+        <v>-0.508</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.63370220900402</v>
+        <v>-9.651999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.54</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8052116869630049</v>
+        <v>-0.6818</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.29902205229709</v>
+        <v>-12.9542</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.59</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7930345860984269</v>
+        <v>1.3546</v>
       </c>
       <c r="J97" t="n">
-        <v>15.06765713587011</v>
+        <v>25.7374</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.42</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6311864800233967</v>
+        <v>1.0108</v>
       </c>
       <c r="J98" t="n">
-        <v>11.99254312044454</v>
+        <v>19.2052</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3788797824801692</v>
+        <v>0.6118</v>
       </c>
       <c r="J99" t="n">
-        <v>7.198715867123214</v>
+        <v>11.6242</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1878630489207711</v>
+        <v>0.2252</v>
       </c>
       <c r="J100" t="n">
-        <v>3.569397929494651</v>
+        <v>4.2788</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>1.08</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1543970310460175</v>
+        <v>0.1406</v>
       </c>
       <c r="J101" t="n">
-        <v>2.933543589874332</v>
+        <v>2.6714</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.17</v>
       </c>
       <c r="I102" t="n">
-        <v>0.09920179824372372</v>
+        <v>0.3381</v>
       </c>
       <c r="J102" t="n">
-        <v>2.281641359605645</v>
+        <v>7.7763</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.03029027317346002</v>
+        <v>0.2263</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.6966762829895805</v>
+        <v>5.2049</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.04759099466999668</v>
+        <v>0.209</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.094592877409924</v>
+        <v>4.807</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4284307017348011</v>
+        <v>-0.246</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.853906139900424</v>
+        <v>-5.658</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5750877122231255</v>
+        <v>-0.4269</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.22701738113189</v>
+        <v>-9.8187</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.93</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9279623862270416</v>
+        <v>1.8854</v>
       </c>
       <c r="J107" t="n">
-        <v>21.34313488322196</v>
+        <v>43.3642</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4470540882873029</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>10.28224403060797</v>
+        <v>20.1135</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>1.25</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3437411163741441</v>
+        <v>0.6854</v>
       </c>
       <c r="J109" t="n">
-        <v>7.906045676605314</v>
+        <v>15.7642</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.71</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5032869127357394</v>
+        <v>-0.9287</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.57559899292201</v>
+        <v>-21.3601</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5501436237688987</v>
+        <v>-1.036</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.65330334668467</v>
+        <v>-23.828</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.3</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2784439202719413</v>
+        <v>0.8338</v>
       </c>
       <c r="J112" t="n">
-        <v>6.68265408652659</v>
+        <v>20.0112</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2356531512178018</v>
+        <v>0.7158</v>
       </c>
       <c r="J113" t="n">
-        <v>5.655675629227243</v>
+        <v>17.1792</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>1.12</v>
       </c>
       <c r="I114" t="n">
-        <v>0.07411791439430851</v>
+        <v>0.347</v>
       </c>
       <c r="J114" t="n">
-        <v>1.778829945463404</v>
+        <v>8.327999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>1.05</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0641694420457761</v>
+        <v>0.1194</v>
       </c>
       <c r="J115" t="n">
-        <v>-1.540066609098626</v>
+        <v>2.8656</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4311822962042999</v>
+        <v>-0.4236</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.3483751089032</v>
+        <v>-10.1664</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.44</v>
       </c>
       <c r="I117" t="n">
-        <v>0.425404196899336</v>
+        <v>0.6794</v>
       </c>
       <c r="J117" t="n">
-        <v>10.20970072558406</v>
+        <v>16.3056</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3724996879581834</v>
+        <v>0.607</v>
       </c>
       <c r="J118" t="n">
-        <v>8.939992510996401</v>
+        <v>14.568</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2215954826686481</v>
+        <v>0.0356</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.318291584047554</v>
+        <v>0.8544</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.83</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5343618765857679</v>
+        <v>-0.3499</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.82468503805843</v>
+        <v>-8.397600000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.8340223500868835</v>
+        <v>-0.7109</v>
       </c>
       <c r="J121" t="n">
-        <v>-20.0165364020852</v>
+        <v>-17.0616</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.9</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6897365559045749</v>
+        <v>1.8053</v>
       </c>
       <c r="J122" t="n">
-        <v>12.41525800628235</v>
+        <v>32.4954</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.81</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6485683932715373</v>
+        <v>1.708</v>
       </c>
       <c r="J123" t="n">
-        <v>11.67423107888767</v>
+        <v>30.744</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.57</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5156911476223961</v>
+        <v>1.2744</v>
       </c>
       <c r="J124" t="n">
-        <v>9.28244065720313</v>
+        <v>22.9392</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1357410861293168</v>
+        <v>-0.6486</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.443339550327702</v>
+        <v>-11.6748</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2613003065402967</v>
+        <v>-0.8126</v>
       </c>
       <c r="J126" t="n">
-        <v>-4.703405517725341</v>
+        <v>-14.6268</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>0.99</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.2285436199454993</v>
+        <v>0.0867</v>
       </c>
       <c r="J127" t="n">
-        <v>-4.113785159018987</v>
+        <v>1.5606</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>0.89</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.3522836773935113</v>
+        <v>-0.1106</v>
       </c>
       <c r="J128" t="n">
-        <v>-6.341106193083204</v>
+        <v>-1.9908</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4061136036741976</v>
+        <v>-0.1781</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.310044866135557</v>
+        <v>-3.2058</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.54</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.9031947584253728</v>
+        <v>-0.6706</v>
       </c>
       <c r="J130" t="n">
-        <v>-16.25750565165671</v>
+        <v>-12.0708</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.43</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.015149066118547</v>
+        <v>-0.8087</v>
       </c>
       <c r="J131" t="n">
-        <v>-18.27268319013384</v>
+        <v>-14.5566</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>0.976018538927938</v>
+        <v>1.9742</v>
       </c>
       <c r="J132" t="n">
-        <v>14.64027808391907</v>
+        <v>29.613</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.58</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6767183973009873</v>
+        <v>1.2428</v>
       </c>
       <c r="J133" t="n">
-        <v>10.15077595951481</v>
+        <v>18.642</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.57</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6666634530073647</v>
+        <v>1.2224</v>
       </c>
       <c r="J134" t="n">
-        <v>9.999951795110471</v>
+        <v>18.336</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>1.35</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3917983102817214</v>
+        <v>0.7245</v>
       </c>
       <c r="J135" t="n">
-        <v>5.876974654225821</v>
+        <v>10.8675</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>0.07462749890848827</v>
+        <v>-0.4295</v>
       </c>
       <c r="J136" t="n">
-        <v>1.119412483627324</v>
+        <v>-6.4425</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.3352784645133336</v>
+        <v>-0.2118</v>
       </c>
       <c r="J137" t="n">
-        <v>-5.029176967700004</v>
+        <v>-3.177</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>0.73</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.385951180418568</v>
+        <v>-0.3051</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.789267706278521</v>
+        <v>-4.5765</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>0.63</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4927258416514604</v>
+        <v>-0.4682</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.390887624771906</v>
+        <v>-7.023</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.52</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6318876213072695</v>
+        <v>-0.6574</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.478314319609042</v>
+        <v>-9.861000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7115785252198719</v>
+        <v>-0.7935</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.67367787829808</v>
+        <v>-11.9025</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.09893546192771051</v>
+        <v>0.3029</v>
       </c>
       <c r="J142" t="n">
-        <v>2.869128395903605</v>
+        <v>8.7841</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.05750947771169238</v>
+        <v>0.271</v>
       </c>
       <c r="J143" t="n">
-        <v>1.667774853639079</v>
+        <v>7.859</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1713845079918543</v>
+        <v>-0.0766</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.970150731763774</v>
+        <v>-2.2214</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2705165330098296</v>
+        <v>-0.2191</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.844979457285058</v>
+        <v>-6.3539</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.74</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4238639470485208</v>
+        <v>-0.4618</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.2920544644071</v>
+        <v>-13.3922</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.29</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4040715520683198</v>
+        <v>0.4633</v>
       </c>
       <c r="J147" t="n">
-        <v>11.71807500998127</v>
+        <v>13.4357</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.25</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3594149128637011</v>
+        <v>0.4087</v>
       </c>
       <c r="J148" t="n">
-        <v>10.42303247304733</v>
+        <v>11.8523</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.14</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1994476960568168</v>
+        <v>0.2368</v>
       </c>
       <c r="J149" t="n">
-        <v>5.783983185647687</v>
+        <v>6.8672</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>1.01</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.02169713775002569</v>
+        <v>-0.0213</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.6292169947507449</v>
+        <v>-0.6177</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.98</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.06600600229024756</v>
+        <v>-0.1138</v>
       </c>
       <c r="J151" t="n">
-        <v>-1.914174066417179</v>
+        <v>-3.3002</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>2.44</v>
       </c>
       <c r="I152" t="n">
-        <v>1.05704321438871</v>
+        <v>2.0593</v>
       </c>
       <c r="J152" t="n">
-        <v>21.14086428777419</v>
+        <v>41.186</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.58</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5870869583028558</v>
+        <v>1.2912</v>
       </c>
       <c r="J153" t="n">
-        <v>11.74173916605712</v>
+        <v>25.824</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1416439577351815</v>
+        <v>0.4206</v>
       </c>
       <c r="J154" t="n">
-        <v>2.832879154703629</v>
+        <v>8.412000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.09612171808167946</v>
+        <v>-0.4094</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.922434361633589</v>
+        <v>-8.188000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2754176532080727</v>
+        <v>-0.8136</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.508353064161453</v>
+        <v>-16.272</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1404030808996986</v>
+        <v>0.6207</v>
       </c>
       <c r="J157" t="n">
-        <v>2.808061617993972</v>
+        <v>12.414</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2272359270570475</v>
+        <v>-0.0567</v>
       </c>
       <c r="J158" t="n">
-        <v>-4.54471854114095</v>
+        <v>-1.134</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>0.93</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2483718446001806</v>
+        <v>-0.0959</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.967436892003612</v>
+        <v>-1.918</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.6</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5948479941559663</v>
+        <v>-0.6224</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.89695988311933</v>
+        <v>-12.448</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.5</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.66015580755468</v>
+        <v>-0.7457</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.2031161510936</v>
+        <v>-14.914</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.56</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5307569694118842</v>
+        <v>1.3211</v>
       </c>
       <c r="J162" t="n">
-        <v>11.14589635764957</v>
+        <v>27.7431</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4956358862558615</v>
+        <v>1.2226</v>
       </c>
       <c r="J163" t="n">
-        <v>10.40835361137309</v>
+        <v>25.6746</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.381404789939245</v>
+        <v>0.9292</v>
       </c>
       <c r="J164" t="n">
-        <v>8.009500588724144</v>
+        <v>19.5132</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.004531860713067096</v>
+        <v>0.0994</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.09516907497440902</v>
+        <v>2.0874</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3775150108982548</v>
+        <v>-0.9631</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.927815228863352</v>
+        <v>-20.2251</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.36</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1498030579254266</v>
+        <v>0.5947</v>
       </c>
       <c r="J167" t="n">
-        <v>3.145864216433958</v>
+        <v>12.4887</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.04</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2511458153373535</v>
+        <v>0.1116</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.274062122084424</v>
+        <v>2.3436</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4439192583382015</v>
+        <v>-0.1171</v>
       </c>
       <c r="J169" t="n">
-        <v>-9.32230442510223</v>
+        <v>-2.4591</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6253060584936171</v>
+        <v>-0.3259</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.13142722836596</v>
+        <v>-6.8439</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.83</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6382110943721186</v>
+        <v>-0.341</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.40243298181449</v>
+        <v>-7.161</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4783128970792406</v>
+        <v>1.2185</v>
       </c>
       <c r="J172" t="n">
-        <v>13.87107401529798</v>
+        <v>35.3365</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.43</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4426563028819007</v>
+        <v>1.1161</v>
       </c>
       <c r="J173" t="n">
-        <v>12.83703278357512</v>
+        <v>32.3669</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>1.2</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2335164931772312</v>
+        <v>0.5887</v>
       </c>
       <c r="J174" t="n">
-        <v>6.771978302139705</v>
+        <v>17.0723</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.9</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2127357793178801</v>
+        <v>-0.4528</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.169337600218523</v>
+        <v>-13.1312</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4352172940810421</v>
+        <v>-1.0894</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.62130152835022</v>
+        <v>-31.5926</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.82</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4001571302471945</v>
+        <v>1.096</v>
       </c>
       <c r="J177" t="n">
-        <v>11.60455677716864</v>
+        <v>31.784</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.06</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1130708950769138</v>
+        <v>0.1395</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.2790559572305</v>
+        <v>4.0455</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>0.89</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4687927272933064</v>
+        <v>-0.2545</v>
       </c>
       <c r="J179" t="n">
-        <v>-13.59498909150589</v>
+        <v>-7.3805</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5770460164760134</v>
+        <v>-0.3768</v>
       </c>
       <c r="J180" t="n">
-        <v>-16.73433447780439</v>
+        <v>-10.9272</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.59</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8139681787444362</v>
+        <v>-0.6625</v>
       </c>
       <c r="J181" t="n">
-        <v>-23.60507718358865</v>
+        <v>-19.2125</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.43</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3396089423251532</v>
+        <v>0.6908</v>
       </c>
       <c r="J182" t="n">
-        <v>8.150614615803676</v>
+        <v>16.5792</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1096821014070692</v>
+        <v>0.0551</v>
       </c>
       <c r="J183" t="n">
-        <v>-2.632370433769661</v>
+        <v>1.3224</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2415519130306137</v>
+        <v>-0.1443</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.797245912734729</v>
+        <v>-3.4632</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3942330687560632</v>
+        <v>-0.3626</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.461593650145517</v>
+        <v>-8.702400000000001</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.68</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5097663099896952</v>
+        <v>-0.5415</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.23439143975268</v>
+        <v>-12.996</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.86</v>
       </c>
       <c r="I187" t="n">
-        <v>1.036928234332291</v>
+        <v>1.0887</v>
       </c>
       <c r="J187" t="n">
-        <v>24.88627762397499</v>
+        <v>26.1288</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.49</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7081055733898184</v>
+        <v>0.6949</v>
       </c>
       <c r="J188" t="n">
-        <v>16.99453376135564</v>
+        <v>16.6776</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3500611760366578</v>
+        <v>0.3608</v>
       </c>
       <c r="J189" t="n">
-        <v>8.401468224879785</v>
+        <v>8.6592</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3252543282350055</v>
+        <v>-0.4311</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.806103877640131</v>
+        <v>-10.3464</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4873166988847126</v>
+        <v>-0.7137</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.6956007732331</v>
+        <v>-17.1288</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.87</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7564663323070302</v>
+        <v>1.821</v>
       </c>
       <c r="J192" t="n">
-        <v>11.34699498460545</v>
+        <v>27.315</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.51</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5346448734594771</v>
+        <v>1.153</v>
       </c>
       <c r="J193" t="n">
-        <v>8.019673101892156</v>
+        <v>17.295</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.5</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5264719813713959</v>
+        <v>1.1323</v>
       </c>
       <c r="J194" t="n">
-        <v>7.89707972057094</v>
+        <v>16.9845</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>1.28</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2807427515321259</v>
+        <v>0.6109</v>
       </c>
       <c r="J195" t="n">
-        <v>4.211141272981888</v>
+        <v>9.163500000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2096132850237523</v>
+        <v>-0.8575</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.144199275356285</v>
+        <v>-12.8625</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.04</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.2402118455146691</v>
+        <v>0.171</v>
       </c>
       <c r="J197" t="n">
-        <v>-3.603177682720037</v>
+        <v>2.565</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>0.93</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3472664896588858</v>
+        <v>-0.0959</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.208997344883287</v>
+        <v>-1.4385</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.9</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3818605515116551</v>
+        <v>-0.1527</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.727908272674826</v>
+        <v>-2.2905</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4488569907994781</v>
+        <v>-0.2363</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.732854861992171</v>
+        <v>-3.5445</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.59</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.700962501128584</v>
+        <v>-0.6351</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.51443751692876</v>
+        <v>-9.5265</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4695192118549555</v>
+        <v>1.2111</v>
       </c>
       <c r="J202" t="n">
-        <v>15.96365320306849</v>
+        <v>41.1774</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3913325894820046</v>
+        <v>0.9819</v>
       </c>
       <c r="J203" t="n">
-        <v>13.30530804238816</v>
+        <v>33.3846</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1461257262630608</v>
+        <v>0.4192</v>
       </c>
       <c r="J204" t="n">
-        <v>4.968274692944067</v>
+        <v>14.2528</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.96</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1173662596220006</v>
+        <v>-0.2894</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.990452827148019</v>
+        <v>-9.839600000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.92</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1732061848667722</v>
+        <v>-0.414</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.889010285470254</v>
+        <v>-14.076</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.41</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4804517777654842</v>
+        <v>0.6681</v>
       </c>
       <c r="J207" t="n">
-        <v>16.33536044402646</v>
+        <v>22.7154</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>0.96</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2241123412956045</v>
+        <v>-0.0987</v>
       </c>
       <c r="J208" t="n">
-        <v>-7.619819604050554</v>
+        <v>-3.3558</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3374844315088649</v>
+        <v>-0.2684</v>
       </c>
       <c r="J209" t="n">
-        <v>-11.47447067130141</v>
+        <v>-9.1256</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>0.85</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3578382004080542</v>
+        <v>-0.3005</v>
       </c>
       <c r="J210" t="n">
-        <v>-12.16649881387384</v>
+        <v>-10.217</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.76</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4392849767706684</v>
+        <v>-0.4334</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.93568921020272</v>
+        <v>-14.7356</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.225012882784385</v>
+        <v>0.4482</v>
       </c>
       <c r="J212" t="n">
-        <v>5.40030918682524</v>
+        <v>10.7568</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.15</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1094124680287527</v>
+        <v>0.3032</v>
       </c>
       <c r="J213" t="n">
-        <v>2.625899232690066</v>
+        <v>7.2768</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>1.13</v>
       </c>
       <c r="I214" t="n">
-        <v>0.07827035007923214</v>
+        <v>0.2716</v>
       </c>
       <c r="J214" t="n">
-        <v>1.878488401901571</v>
+        <v>6.5184</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>1.07</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.02242835035454809</v>
+        <v>0.1675</v>
       </c>
       <c r="J215" t="n">
-        <v>-0.5382804085091542</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.48</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5962036001892745</v>
+        <v>-0.7883</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.30888640454259</v>
+        <v>-18.9192</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.55</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3878403847819821</v>
+        <v>1.3592</v>
       </c>
       <c r="J217" t="n">
-        <v>9.308169234767572</v>
+        <v>32.6208</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.12</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0769133288823716</v>
+        <v>0.3496</v>
       </c>
       <c r="J218" t="n">
-        <v>1.845919893176918</v>
+        <v>8.3904</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.05</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.009906429625094379</v>
+        <v>0.1205</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.2377543110022651</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>1.05</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.009906429625094379</v>
+        <v>0.1205</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.2377543110022651</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.85</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3589881297465122</v>
+        <v>-0.5855</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.615715113916291</v>
+        <v>-14.052</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.19</v>
       </c>
       <c r="I222" t="n">
-        <v>0.01842994116835422</v>
+        <v>0.462</v>
       </c>
       <c r="J222" t="n">
-        <v>0.3501688821987303</v>
+        <v>8.778</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>0.77</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.3606126522272809</v>
+        <v>-0.3253</v>
       </c>
       <c r="J223" t="n">
-        <v>-6.851640392318337</v>
+        <v>-6.1807</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.73</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.4295486037968027</v>
+        <v>-0.4055</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.161423472139251</v>
+        <v>-7.7045</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.63</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.5299665535585045</v>
+        <v>-0.5555</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.06936451761159</v>
+        <v>-10.5545</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.48</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6428203484934344</v>
+        <v>-0.7513</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.21358662137525</v>
+        <v>-14.2747</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.64</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4654712977492118</v>
+        <v>1.4135</v>
       </c>
       <c r="J227" t="n">
-        <v>8.843954657235024</v>
+        <v>26.8565</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.56</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4231598334819206</v>
+        <v>1.2593</v>
       </c>
       <c r="J228" t="n">
-        <v>8.040036836156492</v>
+        <v>23.9267</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1.28</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1942583492954557</v>
+        <v>0.6163</v>
       </c>
       <c r="J229" t="n">
-        <v>3.690908636613659</v>
+        <v>11.7097</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>1.26</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1800627923400271</v>
+        <v>0.5693</v>
       </c>
       <c r="J230" t="n">
-        <v>3.421193054460514</v>
+        <v>10.8167</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I231" t="n">
-        <v>0.0910134367046819</v>
+        <v>0.2251</v>
       </c>
       <c r="J231" t="n">
-        <v>1.729255297388956</v>
+        <v>4.2769</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.74</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6622018020440521</v>
+        <v>1.6918</v>
       </c>
       <c r="J232" t="n">
-        <v>14.56843964496915</v>
+        <v>37.2196</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.58</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5727278817639223</v>
+        <v>1.3948</v>
       </c>
       <c r="J233" t="n">
-        <v>12.60001339880629</v>
+        <v>30.6856</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>0.95</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.06694057550973778</v>
+        <v>-0.3175</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.472692661214231</v>
+        <v>-6.985</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2459342079866892</v>
+        <v>-0.6979</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.410552575707162</v>
+        <v>-15.3538</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2913689332599216</v>
+        <v>-0.8152</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.410116531718276</v>
+        <v>-17.9344</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1194308012914723</v>
+        <v>0.3669</v>
       </c>
       <c r="J237" t="n">
-        <v>2.627477628412392</v>
+        <v>8.0718</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.01476222829434062</v>
+        <v>0.2568</v>
       </c>
       <c r="J238" t="n">
-        <v>0.3247690224754936</v>
+        <v>5.6496</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.02092004867870162</v>
+        <v>0.2046</v>
       </c>
       <c r="J239" t="n">
-        <v>-0.4602410709314356</v>
+        <v>4.5012</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>0.86</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3087548648771341</v>
+        <v>-0.2686</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.792607027296951</v>
+        <v>-5.9092</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.42</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6474910433590487</v>
+        <v>-0.8464</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.24480295389907</v>
+        <v>-18.6208</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5454392064755572</v>
+        <v>1.2997</v>
       </c>
       <c r="J242" t="n">
-        <v>15.2722977813156</v>
+        <v>36.3916</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.372303678408787</v>
+        <v>0.8125</v>
       </c>
       <c r="J243" t="n">
-        <v>10.42450299544604</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.04733733337226305</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="J244" t="n">
-        <v>1.325445334423365</v>
+        <v>1.8396</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.04733733337226305</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="J245" t="n">
-        <v>1.325445334423365</v>
+        <v>1.8396</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.91</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1210300044284257</v>
+        <v>-0.4369</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.388840123995919</v>
+        <v>-12.2332</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I247" t="n">
-        <v>0.09113788376880778</v>
+        <v>0.3404</v>
       </c>
       <c r="J247" t="n">
-        <v>2.551860745526618</v>
+        <v>9.5312</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.01265867680292453</v>
+        <v>0.2084</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.3544429504818867</v>
+        <v>5.8352</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>0.98</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1169282543573938</v>
+        <v>-0.0138</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.273991122007028</v>
+        <v>-0.3864</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>0.8</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3639041251907205</v>
+        <v>-0.3603</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.18931550534017</v>
+        <v>-10.0884</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5495271386347697</v>
+        <v>-0.6691</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.38675988177355</v>
+        <v>-18.7348</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.96</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5756691365600654</v>
+        <v>1.9782</v>
       </c>
       <c r="J252" t="n">
-        <v>10.93771359464124</v>
+        <v>37.5858</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>1.61</v>
       </c>
       <c r="I253" t="n">
-        <v>0.446350819610622</v>
+        <v>1.3993</v>
       </c>
       <c r="J253" t="n">
-        <v>8.480665572601819</v>
+        <v>26.5867</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>1.14</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1258871539798099</v>
+        <v>0.3115</v>
       </c>
       <c r="J254" t="n">
-        <v>2.391855925616388</v>
+        <v>5.9185</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>0.96</v>
       </c>
       <c r="I255" t="n">
-        <v>0.01512970045216741</v>
+        <v>-0.3196</v>
       </c>
       <c r="J255" t="n">
-        <v>0.2874643085911808</v>
+        <v>-6.0724</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.72</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3407775150413994</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.474772785786588</v>
+        <v>-17.6111</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>0.99</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1302658927326389</v>
+        <v>0.0629</v>
       </c>
       <c r="J257" t="n">
-        <v>-2.475051961920138</v>
+        <v>1.1951</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2053076345663375</v>
+        <v>-0.1006</v>
       </c>
       <c r="J258" t="n">
-        <v>-3.900845056760412</v>
+        <v>-1.9114</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2356746002301354</v>
+        <v>-0.1534</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.477817404372572</v>
+        <v>-2.9146</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>0.73</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4378223389615962</v>
+        <v>-0.4224</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.318624440270327</v>
+        <v>-8.025600000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6536446746562048</v>
+        <v>-0.7821</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.41924881846789</v>
+        <v>-14.8599</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.56</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4097172256950874</v>
+        <v>1.3704</v>
       </c>
       <c r="J262" t="n">
-        <v>9.013778965291923</v>
+        <v>30.1488</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.25</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2462623742368932</v>
+        <v>0.7075</v>
       </c>
       <c r="J263" t="n">
-        <v>5.41777223321165</v>
+        <v>15.565</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>1.02</v>
       </c>
       <c r="I264" t="n">
-        <v>0.03662459347670907</v>
+        <v>0.003</v>
       </c>
       <c r="J264" t="n">
-        <v>0.8057410564875995</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.05587147782209957</v>
+        <v>-0.339</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.22917251208619</v>
+        <v>-7.458</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.93</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.0735256754294881</v>
+        <v>-0.3698</v>
       </c>
       <c r="J266" t="n">
-        <v>-1.617564859448738</v>
+        <v>-8.1356</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.1595884808283301</v>
+        <v>0.3646</v>
       </c>
       <c r="J267" t="n">
-        <v>3.510946578223263</v>
+        <v>8.0212</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>0.93</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1500478279458849</v>
+        <v>-0.1087</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.301052214809469</v>
+        <v>-2.3914</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>0.88</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2382688892611107</v>
+        <v>-0.2156</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.241915563744436</v>
+        <v>-4.7432</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3393732259991347</v>
+        <v>-0.3523</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.466210971980963</v>
+        <v>-7.7506</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4499715179172175</v>
+        <v>-0.5238</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.899373394178784</v>
+        <v>-11.5236</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>1.79</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6747685135518058</v>
+        <v>1.8315</v>
       </c>
       <c r="J272" t="n">
-        <v>16.19444432524334</v>
+        <v>43.956</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>0.93</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.1715432317898794</v>
+        <v>-0.3418</v>
       </c>
       <c r="J273" t="n">
-        <v>-4.117037562957105</v>
+        <v>-8.203200000000001</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1715432317898794</v>
+        <v>-0.3418</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.117037562957105</v>
+        <v>-8.203200000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2138330228869315</v>
+        <v>-0.4595</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.131992549286357</v>
+        <v>-11.028</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2797300519817328</v>
+        <v>-0.6443</v>
       </c>
       <c r="J276" t="n">
-        <v>-6.713521247561587</v>
+        <v>-15.4632</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>1.45</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3588339198531212</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J277" t="n">
-        <v>8.612014076474908</v>
+        <v>16.512</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>1.45</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3588339198531212</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J278" t="n">
-        <v>8.612014076474908</v>
+        <v>16.512</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.96</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2339306287771063</v>
+        <v>-0.1343</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.614335090650552</v>
+        <v>-3.2232</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4646478886001119</v>
+        <v>-0.4773</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.15154932640268</v>
+        <v>-11.4552</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5218260855815461</v>
+        <v>-0.5674</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.52382605395711</v>
+        <v>-13.6176</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>1.18</v>
       </c>
       <c r="I282" t="n">
-        <v>0.06891578275911421</v>
+        <v>0.3686</v>
       </c>
       <c r="J282" t="n">
-        <v>1.516147220700513</v>
+        <v>8.1092</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.03135519990171233</v>
+        <v>0.3235</v>
       </c>
       <c r="J283" t="n">
-        <v>0.6898143978376713</v>
+        <v>7.117</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2134068158226868</v>
+        <v>-0.0891</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.694949948099111</v>
+        <v>-1.9602</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>0.93</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2656275684995169</v>
+        <v>-0.1576</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.843806506989372</v>
+        <v>-3.4672</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>0.58</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5715601323201641</v>
+        <v>-0.6642</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.57432291104361</v>
+        <v>-14.6124</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>1.71</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5920562043973907</v>
+        <v>0.9315</v>
       </c>
       <c r="J287" t="n">
-        <v>13.0252364967426</v>
+        <v>20.493</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4699246000823068</v>
+        <v>0.7019</v>
       </c>
       <c r="J288" t="n">
-        <v>10.33834120181075</v>
+        <v>15.4418</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>1.14</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1080789426626011</v>
+        <v>0.2004</v>
       </c>
       <c r="J289" t="n">
-        <v>2.377736738577223</v>
+        <v>4.4088</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.85</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2557203358908926</v>
+        <v>-0.3496</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.625847389599637</v>
+        <v>-7.6912</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2949885259871304</v>
+        <v>-0.4061</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.489747571716868</v>
+        <v>-8.934200000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>1.44</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5182707888104942</v>
+        <v>1.1787</v>
       </c>
       <c r="J292" t="n">
-        <v>11.40195735383087</v>
+        <v>25.9314</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>1.2</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3138816386805275</v>
+        <v>0.6372</v>
       </c>
       <c r="J293" t="n">
-        <v>6.905396050971606</v>
+        <v>14.0184</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>1.04</v>
       </c>
       <c r="I294" t="n">
-        <v>0.06569629576615801</v>
+        <v>0.1393</v>
       </c>
       <c r="J294" t="n">
-        <v>1.445318506855476</v>
+        <v>3.0646</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.231338260664355</v>
+        <v>-0.6615</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.08944173461581</v>
+        <v>-14.553</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>0.76</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.274302292561989</v>
+        <v>-0.7825</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.034650436363757</v>
+        <v>-17.215</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>1.42</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3148557963992514</v>
+        <v>0.6575</v>
       </c>
       <c r="J297" t="n">
-        <v>6.92682752078353</v>
+        <v>14.465</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>1.12</v>
       </c>
       <c r="I298" t="n">
-        <v>0.05651967581674559</v>
+        <v>0.2468</v>
       </c>
       <c r="J298" t="n">
-        <v>1.243432867968403</v>
+        <v>5.4296</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>1.1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.03104594248153042</v>
+        <v>0.2127</v>
       </c>
       <c r="J299" t="n">
-        <v>0.6830107345936692</v>
+        <v>4.6794</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>0.97</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2376834856378932</v>
+        <v>-0.1078</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.22903668403365</v>
+        <v>-2.3716</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>0.58</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6190980803353241</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.62015776737713</v>
+        <v>-14.8478</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>1.67</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4835840198722737</v>
+        <v>1.4972</v>
       </c>
       <c r="J302" t="n">
-        <v>9.188096377573199</v>
+        <v>28.4468</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4013330147038635</v>
+        <v>1.1889</v>
       </c>
       <c r="J303" t="n">
-        <v>7.625327279373406</v>
+        <v>22.5891</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>1.44</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3583073250102101</v>
+        <v>1.0442</v>
       </c>
       <c r="J304" t="n">
-        <v>6.807839175193991</v>
+        <v>19.8398</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>0.99</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.006433524623731837</v>
+        <v>-0.2164</v>
       </c>
       <c r="J305" t="n">
-        <v>-0.1222369678509049</v>
+        <v>-4.1116</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.07356862604473118</v>
+        <v>-0.3912</v>
       </c>
       <c r="J306" t="n">
-        <v>-1.397803894849892</v>
+        <v>-7.4328</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>1.44</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3939848748571073</v>
+        <v>0.7371</v>
       </c>
       <c r="J307" t="n">
-        <v>7.485712622285038</v>
+        <v>14.0049</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.4303530653188941</v>
+        <v>-0.3329</v>
       </c>
       <c r="J308" t="n">
-        <v>-8.176708241058988</v>
+        <v>-6.3251</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>0.75</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4886008977411956</v>
+        <v>-0.4237</v>
       </c>
       <c r="J309" t="n">
-        <v>-9.283417057082715</v>
+        <v>-8.0503</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>0.71</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5230744150776837</v>
+        <v>-0.4804</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.93841388647599</v>
+        <v>-9.127599999999999</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5393466817399881</v>
+        <v>-0.5079</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.24758695305977</v>
+        <v>-9.6501</v>
       </c>
     </row>
     <row r="312">
@@ -14841,10 +14829,10 @@
         <v>1.43</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3641374126555257</v>
+        <v>1.0933</v>
       </c>
       <c r="J312" t="n">
-        <v>8.011023078421566</v>
+        <v>24.0526</v>
       </c>
     </row>
     <row r="313">
@@ -14881,10 +14869,10 @@
         <v>1.33</v>
       </c>
       <c r="I313" t="n">
-        <v>0.30442530138051</v>
+        <v>0.8767</v>
       </c>
       <c r="J313" t="n">
-        <v>6.69735663037122</v>
+        <v>19.2874</v>
       </c>
     </row>
     <row r="314">
@@ -14921,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1176436798420568</v>
+        <v>0.339</v>
       </c>
       <c r="J314" t="n">
-        <v>2.588160956525249</v>
+        <v>7.458</v>
       </c>
     </row>
     <row r="315">
@@ -14961,10 +14949,10 @@
         <v>1.06</v>
       </c>
       <c r="I315" t="n">
-        <v>0.05700975582820578</v>
+        <v>0.1284</v>
       </c>
       <c r="J315" t="n">
-        <v>1.254214628220527</v>
+        <v>2.8248</v>
       </c>
     </row>
     <row r="316">
@@ -15001,10 +14989,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1234437713404235</v>
+        <v>-0.4395</v>
       </c>
       <c r="J316" t="n">
-        <v>-2.715762969489318</v>
+        <v>-9.669</v>
       </c>
     </row>
     <row r="317">
@@ -15041,10 +15029,10 @@
         <v>1.07</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.001412537195095348</v>
+        <v>0.2186</v>
       </c>
       <c r="J317" t="n">
-        <v>-0.03107581829209766</v>
+        <v>4.8092</v>
       </c>
     </row>
     <row r="318">
@@ -15081,10 +15069,10 @@
         <v>1.04</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0339446147260144</v>
+        <v>0.1614</v>
       </c>
       <c r="J318" t="n">
-        <v>-0.7467815239723168</v>
+        <v>3.5508</v>
       </c>
     </row>
     <row r="319">
@@ -15121,10 +15109,10 @@
         <v>0.84</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3029882352300254</v>
+        <v>-0.2871</v>
       </c>
       <c r="J319" t="n">
-        <v>-6.66574117506056</v>
+        <v>-6.3162</v>
       </c>
     </row>
     <row r="320">
@@ -15161,10 +15149,10 @@
         <v>0.82</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3262673125363093</v>
+        <v>-0.32</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.177880875798803</v>
+        <v>-7.04</v>
       </c>
     </row>
     <row r="321">
@@ -15201,10 +15189,10 @@
         <v>0.67</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4655781461314795</v>
+        <v>-0.5367</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.24271921489255</v>
+        <v>-11.8074</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6975/event_6975_evp_summary.xlsx
+++ b/database/event/6975/event_6975_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.0084</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.2062</v>
       </c>
       <c r="D2" t="n">
         <v>2.4099</v>
@@ -545,7 +545,7 @@
         <v>6.523</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.0534</v>
       </c>
       <c r="D3" t="n">
         <v>2.2138</v>
@@ -591,7 +591,7 @@
         <v>6.3702</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.0053</v>
       </c>
       <c r="D4" t="n">
         <v>2.1521</v>
@@ -637,7 +637,7 @@
         <v>5.6307</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.7725</v>
       </c>
       <c r="D5" t="n">
         <v>1.8533</v>
@@ -683,7 +683,7 @@
         <v>5.6181</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.7685</v>
       </c>
       <c r="D6" t="n">
         <v>1.8482</v>
@@ -729,7 +729,7 @@
         <v>5.5371</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.743</v>
       </c>
       <c r="D7" t="n">
         <v>1.8155</v>
@@ -775,7 +775,7 @@
         <v>4.376</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.3775</v>
       </c>
       <c r="D8" t="n">
         <v>1.3464</v>
@@ -821,7 +821,7 @@
         <v>2.8676</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0.7371</v>
@@ -867,7 +867,7 @@
         <v>2.7621</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>0.6945</v>
@@ -913,7 +913,7 @@
         <v>2.7532</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.8667</v>
       </c>
       <c r="D11" t="n">
         <v>0.6909</v>
@@ -959,7 +959,7 @@
         <v>1.9353</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.6092</v>
       </c>
       <c r="D12" t="n">
         <v>0.3605</v>
@@ -1005,7 +1005,7 @@
         <v>1.8431</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.5802</v>
       </c>
       <c r="D13" t="n">
         <v>0.3232</v>
@@ -1051,7 +1051,7 @@
         <v>1.7889</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.5631</v>
       </c>
       <c r="D14" t="n">
         <v>0.3013</v>
@@ -1097,7 +1097,7 @@
         <v>1.6551</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="D15" t="n">
         <v>0.2473</v>
@@ -1143,7 +1143,7 @@
         <v>1.3605</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.4283</v>
       </c>
       <c r="D16" t="n">
         <v>0.1282</v>
@@ -1189,7 +1189,7 @@
         <v>1.0214</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.3215</v>
       </c>
       <c r="D17" t="n">
         <v>-0.008699999999999999</v>
@@ -1235,7 +1235,7 @@
         <v>1.0131</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.3189</v>
       </c>
       <c r="D18" t="n">
         <v>-0.0121</v>
@@ -1281,7 +1281,7 @@
         <v>0.9377</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.2952</v>
       </c>
       <c r="D19" t="n">
         <v>-0.0426</v>
@@ -1327,7 +1327,7 @@
         <v>0.5977</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.1881</v>
       </c>
       <c r="D20" t="n">
         <v>-0.1799</v>
@@ -1373,7 +1373,7 @@
         <v>0.1012</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.0319</v>
       </c>
       <c r="D21" t="n">
         <v>-0.3805</v>
@@ -1419,7 +1419,7 @@
         <v>0.0622</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.0196</v>
       </c>
       <c r="D22" t="n">
         <v>-0.3962</v>
@@ -1465,7 +1465,7 @@
         <v>0.0422</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.0133</v>
       </c>
       <c r="D23" t="n">
         <v>-0.4043</v>
@@ -1511,7 +1511,7 @@
         <v>0.0277</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D24" t="n">
         <v>-0.4102</v>
@@ -1557,7 +1557,7 @@
         <v>-0.0711</v>
       </c>
       <c r="C25" t="n">
-        <v>-0</v>
+        <v>-0.0224</v>
       </c>
       <c r="D25" t="n">
         <v>-0.4501</v>
@@ -1603,7 +1603,7 @@
         <v>-0.1871</v>
       </c>
       <c r="C26" t="n">
-        <v>-0</v>
+        <v>-0.0589</v>
       </c>
       <c r="D26" t="n">
         <v>-0.4969</v>
@@ -1649,7 +1649,7 @@
         <v>-0.3122</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>-0.0983</v>
       </c>
       <c r="D27" t="n">
         <v>-0.5475</v>
@@ -1695,7 +1695,7 @@
         <v>-0.3457</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.1088</v>
       </c>
       <c r="D28" t="n">
         <v>-0.5610000000000001</v>
@@ -1741,7 +1741,7 @@
         <v>-0.3949</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.1243</v>
       </c>
       <c r="D29" t="n">
         <v>-0.5809</v>
@@ -1787,7 +1787,7 @@
         <v>-0.4029</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.1268</v>
       </c>
       <c r="D30" t="n">
         <v>-0.5841</v>
@@ -1833,7 +1833,7 @@
         <v>-0.5314</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.1673</v>
       </c>
       <c r="D31" t="n">
         <v>-0.636</v>
@@ -1879,7 +1879,7 @@
         <v>-0.5759</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.1813</v>
       </c>
       <c r="D32" t="n">
         <v>-0.654</v>
@@ -1925,7 +1925,7 @@
         <v>-0.6511</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.205</v>
       </c>
       <c r="D33" t="n">
         <v>-0.6844</v>
@@ -1971,7 +1971,7 @@
         <v>-0.7000999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.2204</v>
       </c>
       <c r="D34" t="n">
         <v>-0.7042</v>
@@ -2017,7 +2017,7 @@
         <v>-1.0375</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.3266</v>
       </c>
       <c r="D35" t="n">
         <v>-0.8405</v>
@@ -2063,7 +2063,7 @@
         <v>-1.0514</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.331</v>
       </c>
       <c r="D36" t="n">
         <v>-0.8461</v>
@@ -2109,7 +2109,7 @@
         <v>-1.101</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.3466</v>
       </c>
       <c r="D37" t="n">
         <v>-0.8661</v>
@@ -2155,7 +2155,7 @@
         <v>-1.1916</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.3751</v>
       </c>
       <c r="D38" t="n">
         <v>-0.9026999999999999</v>
@@ -2201,7 +2201,7 @@
         <v>-1.238</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.3897</v>
       </c>
       <c r="D39" t="n">
         <v>-0.9215</v>
@@ -2247,7 +2247,7 @@
         <v>-2</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.6296</v>
       </c>
       <c r="D40" t="n">
         <v>-1.2293</v>
@@ -2293,7 +2293,7 @@
         <v>-3.2346</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-1.0182</v>
       </c>
       <c r="D41" t="n">
         <v>-1.7281</v>

--- a/database/event/6975/event_6975_evp_summary.xlsx
+++ b/database/event/6975/event_6975_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.2062</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4099</v>
+        <v>2.3482</v>
       </c>
       <c r="E2" t="n">
         <v>7.0084</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.523</v>
+        <v>6.5108</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0534</v>
+        <v>2.0495</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2138</v>
+        <v>2.15</v>
       </c>
       <c r="E3" t="n">
-        <v>6.523</v>
+        <v>6.5108</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2686</v>
+        <v>3.2564</v>
       </c>
       <c r="G3" t="n">
         <v>3.2544</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2686</v>
+        <v>3.2564</v>
       </c>
       <c r="I3" t="n">
         <v>3.2838</v>
@@ -594,7 +594,7 @@
         <v>2.0053</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1521</v>
+        <v>2.094</v>
       </c>
       <c r="E4" t="n">
         <v>6.3702</v>
@@ -640,7 +640,7 @@
         <v>1.7725</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8533</v>
+        <v>1.7994</v>
       </c>
       <c r="E5" t="n">
         <v>5.6307</v>
@@ -686,7 +686,7 @@
         <v>1.7685</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8482</v>
+        <v>1.7943</v>
       </c>
       <c r="E6" t="n">
         <v>5.6181</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.5371</v>
+        <v>5.5319</v>
       </c>
       <c r="C7" t="n">
-        <v>1.743</v>
+        <v>1.7414</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8155</v>
+        <v>1.76</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5371</v>
+        <v>5.5319</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3924</v>
+        <v>1.3872</v>
       </c>
       <c r="G7" t="n">
         <v>4.1447</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3924</v>
+        <v>1.3872</v>
       </c>
       <c r="I7" t="n">
         <v>1.3989</v>
@@ -778,7 +778,7 @@
         <v>1.3775</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3464</v>
+        <v>1.2995</v>
       </c>
       <c r="E8" t="n">
         <v>4.376</v>
@@ -824,7 +824,7 @@
         <v>0.9026999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7371</v>
+        <v>0.6985</v>
       </c>
       <c r="E9" t="n">
         <v>2.8676</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7621</v>
+        <v>2.7627</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8697</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6945</v>
+        <v>0.6567</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7621</v>
+        <v>2.7627</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1615</v>
+        <v>-0.1609</v>
       </c>
       <c r="G10" t="n">
         <v>2.9236</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1615</v>
+        <v>-0.1609</v>
       </c>
       <c r="I10" t="n">
         <v>-0.1623</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7532</v>
+        <v>2.7523</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8667</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6909</v>
+        <v>0.6526</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7532</v>
+        <v>2.7523</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2537</v>
+        <v>0.2528</v>
       </c>
       <c r="G11" t="n">
         <v>2.4995</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2537</v>
+        <v>0.2528</v>
       </c>
       <c r="I11" t="n">
         <v>0.2549</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9353</v>
+        <v>1.9257</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6092</v>
+        <v>0.6062</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3605</v>
+        <v>0.3233</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9353</v>
+        <v>1.9257</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5877</v>
+        <v>2.5781</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6524</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5877</v>
+        <v>2.5781</v>
       </c>
       <c r="I12" t="n">
         <v>2.5998</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8431</v>
+        <v>1.8405</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5802</v>
+        <v>0.5794</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3232</v>
+        <v>0.2893</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8431</v>
+        <v>1.8405</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6952</v>
+        <v>0.6926</v>
       </c>
       <c r="G13" t="n">
         <v>1.1479</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6952</v>
+        <v>0.6926</v>
       </c>
       <c r="I13" t="n">
         <v>0.6985</v>
@@ -1054,7 +1054,7 @@
         <v>0.5631</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3013</v>
+        <v>0.2688</v>
       </c>
       <c r="E14" t="n">
         <v>1.7889</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6551</v>
+        <v>1.6464</v>
       </c>
       <c r="C15" t="n">
-        <v>0.521</v>
+        <v>0.5183</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2473</v>
+        <v>0.212</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6551</v>
+        <v>1.6464</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3315</v>
+        <v>2.3228</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6764</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3315</v>
+        <v>2.3228</v>
       </c>
       <c r="I15" t="n">
         <v>2.3423</v>
@@ -1146,7 +1146,7 @@
         <v>0.4283</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1282</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>1.3605</v>
@@ -1192,7 +1192,7 @@
         <v>0.3215</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.037</v>
       </c>
       <c r="E17" t="n">
         <v>1.0214</v>
@@ -1238,7 +1238,7 @@
         <v>0.3189</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0121</v>
+        <v>-0.0403</v>
       </c>
       <c r="E18" t="n">
         <v>1.0131</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9377</v>
+        <v>0.9355</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2952</v>
+        <v>0.2945</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0426</v>
+        <v>-0.0712</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9377</v>
+        <v>0.9355</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5971</v>
       </c>
       <c r="G19" t="n">
         <v>0.3384</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5971</v>
       </c>
       <c r="I19" t="n">
         <v>0.6021</v>
@@ -1330,7 +1330,7 @@
         <v>0.1881</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1799</v>
+        <v>-0.2058</v>
       </c>
       <c r="E20" t="n">
         <v>0.5977</v>
@@ -1376,7 +1376,7 @@
         <v>0.0319</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3805</v>
+        <v>-0.4036</v>
       </c>
       <c r="E21" t="n">
         <v>0.1012</v>
@@ -1422,7 +1422,7 @@
         <v>0.0196</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3962</v>
+        <v>-0.4191</v>
       </c>
       <c r="E22" t="n">
         <v>0.0622</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0422</v>
+        <v>0.0401</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0133</v>
+        <v>0.0126</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4043</v>
+        <v>-0.4279</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0422</v>
+        <v>0.0401</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5565</v>
+        <v>0.5544</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5143</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5565</v>
+        <v>0.5544</v>
       </c>
       <c r="I23" t="n">
         <v>0.5591</v>
@@ -1514,7 +1514,7 @@
         <v>0.008699999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4102</v>
+        <v>-0.4329</v>
       </c>
       <c r="E24" t="n">
         <v>0.0277</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0224</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4501</v>
+        <v>-0.4722</v>
       </c>
       <c r="E25" t="n">
         <v>-0.0711</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0589</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4969</v>
+        <v>-0.5185</v>
       </c>
       <c r="E26" t="n">
         <v>-0.1871</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0983</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5475</v>
+        <v>-0.5683</v>
       </c>
       <c r="E27" t="n">
         <v>-0.3122</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3457</v>
+        <v>-0.3462</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1088</v>
+        <v>-0.109</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5818</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3457</v>
+        <v>-0.3462</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1352</v>
+        <v>0.1347</v>
       </c>
       <c r="G28" t="n">
         <v>-0.4809</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1352</v>
+        <v>0.1347</v>
       </c>
       <c r="I28" t="n">
         <v>0.1358</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1243</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5809</v>
+        <v>-0.6012</v>
       </c>
       <c r="E29" t="n">
         <v>-0.3949</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1268</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5841</v>
+        <v>-0.6044</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4029</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1673</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.636</v>
+        <v>-0.6556</v>
       </c>
       <c r="E31" t="n">
         <v>-0.5314</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5759</v>
+        <v>-0.5746</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1813</v>
+        <v>-0.1809</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.654</v>
+        <v>-0.6728</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5759</v>
+        <v>-0.5746</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3457</v>
+        <v>-0.3444</v>
       </c>
       <c r="G32" t="n">
         <v>-0.2302</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3457</v>
+        <v>-0.3444</v>
       </c>
       <c r="I32" t="n">
         <v>-0.3473</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6511</v>
+        <v>-0.6528</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.205</v>
+        <v>-0.2055</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6844</v>
+        <v>-0.704</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6511</v>
+        <v>-0.6528</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4675</v>
+        <v>0.4658</v>
       </c>
       <c r="G33" t="n">
         <v>-1.1186</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4675</v>
+        <v>0.4658</v>
       </c>
       <c r="I33" t="n">
         <v>0.4697</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.6986</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2204</v>
+        <v>-0.2199</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7042</v>
+        <v>-0.7222</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.6986</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3964</v>
+        <v>-0.3949</v>
       </c>
       <c r="G34" t="n">
         <v>-0.3037</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3964</v>
+        <v>-0.3949</v>
       </c>
       <c r="I34" t="n">
         <v>-0.3982</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3266</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8405</v>
+        <v>-0.8573</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0375</v>
@@ -2066,7 +2066,7 @@
         <v>-0.331</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8461</v>
+        <v>-0.8628</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0514</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3466</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8661</v>
+        <v>-0.8825</v>
       </c>
       <c r="E37" t="n">
         <v>-1.101</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1916</v>
+        <v>-1.1813</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3751</v>
+        <v>-0.3719</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.9145</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1916</v>
+        <v>-1.1813</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.7756</v>
+        <v>-2.7652</v>
       </c>
       <c r="G38" t="n">
         <v>1.5839</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.7756</v>
+        <v>-2.7652</v>
       </c>
       <c r="I38" t="n">
         <v>-2.7885</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3897</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9215</v>
+        <v>-0.9371</v>
       </c>
       <c r="E39" t="n">
         <v>-1.238</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6296</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E40" t="n">
         <v>-2</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2346</v>
+        <v>-3.2281</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0182</v>
+        <v>-1.0162</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7281</v>
+        <v>-1.73</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2346</v>
+        <v>-3.2281</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7443</v>
+        <v>-1.7378</v>
       </c>
       <c r="G41" t="n">
         <v>-1.4903</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7443</v>
+        <v>-1.7378</v>
       </c>
       <c r="I41" t="n">
         <v>-1.7524</v>

--- a/database/event/6975/event_6975_evp_summary.xlsx
+++ b/database/event/6975/event_6975_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0084</v>
+        <v>6.2967</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2062</v>
+        <v>1.9821</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3482</v>
+        <v>2.2046</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0084</v>
+        <v>6.2967</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1843</v>
+        <v>3.7859</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8241</v>
+        <v>2.5108</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2741</v>
+        <v>7.8527</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4642</v>
+        <v>4.0831</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8241</v>
+        <v>2.5108</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -529,7 +529,7 @@
         <v>115</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2883</v>
+        <v>6.5939</v>
       </c>
       <c r="N2" t="n">
         <v>220</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5108</v>
+        <v>6.1195</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0495</v>
+        <v>1.9264</v>
       </c>
       <c r="D3" t="n">
-        <v>2.15</v>
+        <v>2.1246</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5108</v>
+        <v>6.1195</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2564</v>
+        <v>3.5362</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2544</v>
+        <v>2.5833</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2564</v>
+        <v>4.405</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2838</v>
+        <v>4.5862</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2544</v>
+        <v>2.5833</v>
       </c>
       <c r="K3" t="n">
         <v>141</v>
@@ -575,7 +575,7 @@
         <v>117</v>
       </c>
       <c r="M3" t="n">
-        <v>6.5382</v>
+        <v>7.169499999999999</v>
       </c>
       <c r="N3" t="n">
         <v>258</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3702</v>
+        <v>5.6709</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0053</v>
+        <v>1.7851</v>
       </c>
       <c r="D4" t="n">
-        <v>2.094</v>
+        <v>1.9221</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3702</v>
+        <v>5.6709</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1142</v>
+        <v>3.1675</v>
       </c>
       <c r="G4" t="n">
-        <v>2.256</v>
+        <v>2.5034</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1142</v>
+        <v>5.6742</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3347</v>
+        <v>2.9503</v>
       </c>
       <c r="J4" t="n">
-        <v>2.256</v>
+        <v>2.5034</v>
       </c>
       <c r="K4" t="n">
         <v>105</v>
@@ -621,7 +621,7 @@
         <v>115</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5907</v>
+        <v>5.4537</v>
       </c>
       <c r="N4" t="n">
         <v>220</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6307</v>
+        <v>5.5282</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7725</v>
+        <v>1.7402</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7994</v>
+        <v>1.8577</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6307</v>
+        <v>5.5282</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9466</v>
+        <v>3.5432</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6841</v>
+        <v>1.985</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9466</v>
+        <v>6.9975</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3883</v>
+        <v>3.6384</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6841</v>
+        <v>1.985</v>
       </c>
       <c r="K5" t="n">
         <v>105</v>
@@ -667,7 +667,7 @@
         <v>115</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0724</v>
+        <v>5.6234</v>
       </c>
       <c r="N5" t="n">
         <v>220</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.6181</v>
+        <v>4.7635</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7685</v>
+        <v>1.4995</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7943</v>
+        <v>1.5125</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6181</v>
+        <v>4.7635</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0919</v>
+        <v>3.4154</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5262</v>
+        <v>1.3481</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0919</v>
+        <v>6.5473</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3166</v>
+        <v>3.4043</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5262</v>
+        <v>1.3481</v>
       </c>
       <c r="K6" t="n">
         <v>114</v>
@@ -713,7 +713,7 @@
         <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8428</v>
+        <v>4.7524</v>
       </c>
       <c r="N6" t="n">
         <v>215</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.5319</v>
+        <v>4.6421</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7414</v>
+        <v>1.4613</v>
       </c>
       <c r="D7" t="n">
-        <v>1.76</v>
+        <v>1.4577</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5319</v>
+        <v>4.6421</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3872</v>
+        <v>1.3122</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1447</v>
+        <v>3.3299</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3872</v>
+        <v>1.3122</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3989</v>
+        <v>1.3662</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1447</v>
+        <v>3.3299</v>
       </c>
       <c r="K7" t="n">
         <v>114</v>
@@ -759,7 +759,7 @@
         <v>126</v>
       </c>
       <c r="M7" t="n">
-        <v>5.543600000000001</v>
+        <v>4.696099999999999</v>
       </c>
       <c r="N7" t="n">
         <v>240</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.376</v>
+        <v>3.9331</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3775</v>
+        <v>1.2381</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2995</v>
+        <v>1.1376</v>
       </c>
       <c r="E8" t="n">
-        <v>4.376</v>
+        <v>3.9331</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5956</v>
+        <v>3.0674</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7804</v>
+        <v>0.8657</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5956</v>
+        <v>5.3212</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9143</v>
+        <v>2.7668</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7804</v>
+        <v>0.8657</v>
       </c>
       <c r="K8" t="n">
         <v>114</v>
@@ -805,7 +805,7 @@
         <v>101</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6947</v>
+        <v>3.6325</v>
       </c>
       <c r="N8" t="n">
         <v>215</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8676</v>
+        <v>3.5168</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9026999999999999</v>
+        <v>1.1071</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6985</v>
+        <v>0.9496</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8676</v>
+        <v>3.5168</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6303</v>
+        <v>2.7457</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2373</v>
+        <v>0.7711</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6303</v>
+        <v>4.1877</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1319</v>
+        <v>2.1774</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2373</v>
+        <v>0.7711</v>
       </c>
       <c r="K9" t="n">
         <v>114</v>
@@ -851,7 +851,7 @@
         <v>101</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3692</v>
+        <v>2.9485</v>
       </c>
       <c r="N9" t="n">
         <v>215</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7627</v>
+        <v>2.4719</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8697</v>
+        <v>0.7781</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6567</v>
+        <v>0.4779</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7627</v>
+        <v>2.4719</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1609</v>
+        <v>2.7064</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9236</v>
+        <v>-0.2345</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1609</v>
+        <v>4.0492</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1623</v>
+        <v>2.1054</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9236</v>
+        <v>-0.2345</v>
       </c>
       <c r="K10" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="L10" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7613</v>
+        <v>1.8709</v>
       </c>
       <c r="N10" t="n">
-        <v>258</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7523</v>
+        <v>2.4091</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.7584</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6526</v>
+        <v>0.4496</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7523</v>
+        <v>2.4091</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2528</v>
+        <v>0.2692</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4995</v>
+        <v>2.1399</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2528</v>
+        <v>0.2692</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2549</v>
+        <v>0.2803</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4995</v>
+        <v>2.1399</v>
       </c>
       <c r="K11" t="n">
         <v>114</v>
@@ -943,7 +943,7 @@
         <v>126</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7544</v>
+        <v>2.4202</v>
       </c>
       <c r="N11" t="n">
         <v>240</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9257</v>
+        <v>2.305</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6062</v>
+        <v>0.7256</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3233</v>
+        <v>0.4026</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9257</v>
+        <v>2.305</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5781</v>
+        <v>-0.0601</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6524</v>
+        <v>2.3651</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5781</v>
+        <v>-0.0601</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5998</v>
+        <v>-0.0626</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6524</v>
+        <v>2.3651</v>
       </c>
       <c r="K12" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="L12" t="n">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9474</v>
+        <v>2.3025</v>
       </c>
       <c r="N12" t="n">
-        <v>176</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8405</v>
+        <v>2.258</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5794</v>
+        <v>0.7108</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2893</v>
+        <v>0.3814</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8405</v>
+        <v>2.258</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6926</v>
+        <v>1.2141</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1479</v>
+        <v>1.0439</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6926</v>
+        <v>1.2141</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6985</v>
+        <v>1.264</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1479</v>
+        <v>1.0439</v>
       </c>
       <c r="K13" t="n">
         <v>111</v>
@@ -1035,7 +1035,7 @@
         <v>65</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8464</v>
+        <v>2.3079</v>
       </c>
       <c r="N13" t="n">
         <v>176</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7889</v>
+        <v>2.1507</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5631</v>
+        <v>0.677</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2688</v>
+        <v>0.3329</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7889</v>
+        <v>2.1507</v>
       </c>
       <c r="F14" t="n">
-        <v>2.41</v>
+        <v>2.5309</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6211</v>
+        <v>-0.3802</v>
       </c>
       <c r="H14" t="n">
-        <v>2.41</v>
+        <v>2.5309</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9534</v>
+        <v>2.635</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6211</v>
+        <v>-0.3802</v>
       </c>
       <c r="K14" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L14" t="n">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3323</v>
+        <v>2.2548</v>
       </c>
       <c r="N14" t="n">
-        <v>215</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6464</v>
+        <v>2.1039</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5183</v>
+        <v>0.6623</v>
       </c>
       <c r="D15" t="n">
-        <v>0.212</v>
+        <v>0.3118</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6464</v>
+        <v>2.1039</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3228</v>
+        <v>2.4694</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6764</v>
+        <v>-0.3655</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3228</v>
+        <v>2.4694</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3423</v>
+        <v>2.571</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6764</v>
+        <v>-0.3655</v>
       </c>
       <c r="K15" t="n">
         <v>111</v>
@@ -1127,7 +1127,7 @@
         <v>65</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6659</v>
+        <v>2.2055</v>
       </c>
       <c r="N15" t="n">
         <v>176</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3605</v>
+        <v>1.9871</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4283</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.2591</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3605</v>
+        <v>1.9871</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9955</v>
+        <v>2.3782</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.635</v>
+        <v>-0.3911</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9955</v>
+        <v>2.3782</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9955</v>
+        <v>2.3782</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.635</v>
+        <v>-0.3911</v>
       </c>
       <c r="K16" t="n">
         <v>91</v>
@@ -1173,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3605</v>
+        <v>1.9871</v>
       </c>
       <c r="N16" t="n">
         <v>133</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0214</v>
+        <v>1.3495</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3215</v>
+        <v>0.4248</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.037</v>
+        <v>-0.0288</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0214</v>
+        <v>1.3495</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0214</v>
+        <v>1.3495</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0214</v>
+        <v>1.3495</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0214</v>
+        <v>1.3495</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0214</v>
+        <v>1.3495</v>
       </c>
       <c r="N17" t="n">
         <v>84</v>
@@ -1228,645 +1228,645 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0131</v>
+        <v>1.3293</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3189</v>
+        <v>0.4184</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0403</v>
+        <v>-0.0379</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0131</v>
+        <v>1.3293</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0131</v>
+        <v>0.9644</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.3649</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0131</v>
+        <v>0.9644</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0131</v>
+        <v>1.0041</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.3649</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0131</v>
+        <v>1.369</v>
       </c>
       <c r="N18" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9355</v>
+        <v>1.3003</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2945</v>
+        <v>0.4093</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0712</v>
+        <v>-0.051</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9355</v>
+        <v>1.3003</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5971</v>
+        <v>1.3003</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3384</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5971</v>
+        <v>1.3003</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6021</v>
+        <v>1.3003</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3384</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9404999999999999</v>
+        <v>1.3003</v>
       </c>
       <c r="N19" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5977</v>
+        <v>0.8583</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1881</v>
+        <v>0.2702</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2058</v>
+        <v>-0.2505</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5977</v>
+        <v>0.8583</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5977</v>
+        <v>1.0492</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.1909</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5977</v>
+        <v>1.0492</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5977</v>
+        <v>1.0924</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.1909</v>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5977</v>
+        <v>0.9015000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1012</v>
+        <v>0.8554</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0319</v>
+        <v>0.2693</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4036</v>
+        <v>-0.2518</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1012</v>
+        <v>0.8554</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3277</v>
+        <v>1.2513</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4289</v>
+        <v>-0.3959</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3277</v>
+        <v>1.2513</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3277</v>
+        <v>0.6506</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4289</v>
+        <v>-0.3959</v>
       </c>
       <c r="K21" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="L21" t="n">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1012</v>
+        <v>0.2547</v>
       </c>
       <c r="N21" t="n">
-        <v>133</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0622</v>
+        <v>0.7343</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0196</v>
+        <v>0.2311</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4191</v>
+        <v>-0.3065</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0622</v>
+        <v>0.7343</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0622</v>
+        <v>0.8783</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.144</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0622</v>
+        <v>0.8783</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0622</v>
+        <v>0.4567</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.144</v>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0622</v>
+        <v>0.3127</v>
       </c>
       <c r="N22" t="n">
-        <v>100</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0401</v>
+        <v>0.7081</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0126</v>
+        <v>0.2229</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4279</v>
+        <v>-0.3183</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0401</v>
+        <v>0.7081</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5544</v>
+        <v>0.7081</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5143</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5544</v>
+        <v>0.7081</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5591</v>
+        <v>0.7081</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5143</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.04480000000000006</v>
+        <v>0.7081</v>
       </c>
       <c r="N23" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0277</v>
+        <v>0.4603</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.1449</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4329</v>
+        <v>-0.4302</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0277</v>
+        <v>0.4603</v>
       </c>
       <c r="F24" t="n">
-        <v>0.157</v>
+        <v>0.4603</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1293</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.157</v>
+        <v>0.4603</v>
       </c>
       <c r="I24" t="n">
-        <v>0.157</v>
+        <v>0.4603</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1293</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0277</v>
+        <v>0.4603</v>
       </c>
       <c r="N24" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0711</v>
+        <v>0.4536</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0224</v>
+        <v>0.1428</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4722</v>
+        <v>-0.4332</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0711</v>
+        <v>0.4536</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0711</v>
+        <v>0.3782</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0711</v>
+        <v>0.3782</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0711</v>
+        <v>0.3782</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0711</v>
+        <v>0.4536</v>
       </c>
       <c r="N25" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1871</v>
+        <v>0.4393</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0589</v>
+        <v>0.1383</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5185</v>
+        <v>-0.4397</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1871</v>
+        <v>0.4393</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0143</v>
+        <v>0.4449</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2014</v>
+        <v>-0.0056</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0143</v>
+        <v>0.4449</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0116</v>
+        <v>0.4632</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2014</v>
+        <v>-0.0056</v>
       </c>
       <c r="K26" t="n">
         <v>114</v>
       </c>
       <c r="L26" t="n">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1898</v>
+        <v>0.4576</v>
       </c>
       <c r="N26" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3122</v>
+        <v>0.1712</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0983</v>
+        <v>0.0539</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5683</v>
+        <v>-0.5607</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3122</v>
+        <v>0.1712</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.4212</v>
+        <v>0.1712</v>
       </c>
       <c r="G27" t="n">
-        <v>1.109</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.4212</v>
+        <v>0.1712</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.1519</v>
+        <v>0.1712</v>
       </c>
       <c r="J27" t="n">
-        <v>1.109</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.04289999999999994</v>
+        <v>0.1712</v>
       </c>
       <c r="N27" t="n">
-        <v>220</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3462</v>
+        <v>0.1619</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.109</v>
+        <v>0.051</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5818</v>
+        <v>-0.5649</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3462</v>
+        <v>0.1619</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1347</v>
+        <v>-0.2538</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4809</v>
+        <v>0.4157</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1347</v>
+        <v>-0.2538</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1358</v>
+        <v>-0.2538</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4809</v>
+        <v>0.4157</v>
       </c>
       <c r="K28" t="n">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="L28" t="n">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3451</v>
+        <v>0.1619</v>
       </c>
       <c r="N28" t="n">
-        <v>240</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3949</v>
+        <v>-0.0593</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1243</v>
+        <v>-0.0187</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6012</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3949</v>
+        <v>-0.0593</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1317</v>
+        <v>-0.0593</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2632</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1317</v>
+        <v>-0.0593</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1317</v>
+        <v>-0.0593</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2632</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L29" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3949</v>
+        <v>-0.0593</v>
       </c>
       <c r="N29" t="n">
-        <v>133</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4029</v>
+        <v>-0.1039</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1268</v>
+        <v>-0.0327</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6044</v>
+        <v>-0.6849</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4029</v>
+        <v>-0.1039</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3614</v>
+        <v>0.0639</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.7643</v>
+        <v>-0.1678</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3614</v>
+        <v>0.0639</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2929</v>
+        <v>0.0639</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7643</v>
+        <v>-0.1678</v>
       </c>
       <c r="K30" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="L30" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4714</v>
+        <v>-0.1039</v>
       </c>
       <c r="N30" t="n">
-        <v>220</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5314</v>
+        <v>-0.1561</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1673</v>
+        <v>-0.0491</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6556</v>
+        <v>-0.7085</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5314</v>
+        <v>-0.1561</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5314</v>
+        <v>0.5473</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.7034</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5314</v>
+        <v>0.5473</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5314</v>
+        <v>0.5698</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.7034</v>
       </c>
       <c r="K31" t="n">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5314</v>
+        <v>-0.1336000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>84</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5746</v>
+        <v>-0.2</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1809</v>
+        <v>-0.063</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6728</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5746</v>
+        <v>-0.2</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3444</v>
+        <v>-0.1455</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2302</v>
+        <v>-0.0545</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3444</v>
+        <v>-0.1455</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3473</v>
+        <v>-0.1515</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2302</v>
+        <v>-0.0545</v>
       </c>
       <c r="K32" t="n">
         <v>114</v>
@@ -1909,7 +1909,7 @@
         <v>126</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5775</v>
+        <v>-0.206</v>
       </c>
       <c r="N32" t="n">
         <v>240</v>
@@ -1918,170 +1918,170 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6528</v>
+        <v>-0.3666</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2055</v>
+        <v>-0.1154</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.704</v>
+        <v>-0.8035</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6528</v>
+        <v>-0.3666</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4658</v>
+        <v>-0.1892</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.1186</v>
+        <v>-0.1774</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4658</v>
+        <v>-0.1892</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4697</v>
+        <v>-0.197</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.1186</v>
+        <v>-0.1774</v>
       </c>
       <c r="K33" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="L33" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6489</v>
+        <v>-0.3744</v>
       </c>
       <c r="N33" t="n">
-        <v>258</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6986</v>
+        <v>-0.5577</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2199</v>
+        <v>-0.1756</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7222</v>
+        <v>-0.8898</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6986</v>
+        <v>-0.5577</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3949</v>
+        <v>-1.5088</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3037</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3949</v>
+        <v>-1.5088</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3982</v>
+        <v>-0.7845</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3037</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="L34" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7019</v>
+        <v>0.1666</v>
       </c>
       <c r="N34" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0375</v>
+        <v>-0.5659</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3266</v>
+        <v>-0.1781</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8573</v>
+        <v>-0.8935</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0375</v>
+        <v>-0.5659</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.216</v>
+        <v>-0.5659</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8215</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.216</v>
+        <v>-0.5659</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.216</v>
+        <v>-0.5659</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8215</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L35" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0375</v>
+        <v>-0.5659</v>
       </c>
       <c r="N35" t="n">
-        <v>133</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0514</v>
+        <v>-0.5897</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.331</v>
+        <v>-0.1856</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8628</v>
+        <v>-0.9042</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0514</v>
+        <v>-0.5897</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0514</v>
+        <v>-0.5897</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0514</v>
+        <v>-0.5897</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0514</v>
+        <v>-0.5897</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0514</v>
+        <v>-0.5897</v>
       </c>
       <c r="N36" t="n">
         <v>84</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.101</v>
+        <v>-0.7287</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3466</v>
+        <v>-0.2294</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8825</v>
+        <v>-0.967</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.101</v>
+        <v>-0.7287</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.101</v>
+        <v>-2.1597</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.431</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.101</v>
+        <v>-2.1597</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.101</v>
+        <v>-2.2485</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1.431</v>
       </c>
       <c r="K37" t="n">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.101</v>
+        <v>-0.8174999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>84</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1813</v>
+        <v>-0.7304</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3719</v>
+        <v>-0.2299</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9145</v>
+        <v>-0.9678</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1813</v>
+        <v>-0.7304</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.7652</v>
+        <v>-0.1415</v>
       </c>
       <c r="G38" t="n">
-        <v>1.5839</v>
+        <v>-0.5889</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.7652</v>
+        <v>-0.1415</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.7885</v>
+        <v>-0.1415</v>
       </c>
       <c r="J38" t="n">
-        <v>1.5839</v>
+        <v>-0.5889</v>
       </c>
       <c r="K38" t="n">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="L38" t="n">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2046</v>
+        <v>-0.7303999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>258</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.238</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3897</v>
+        <v>-0.2451</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9371</v>
+        <v>-0.9896</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.238</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.238</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.238</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.238</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.238</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>84</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2</v>
+        <v>-1.651</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6296</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2407</v>
+        <v>-1.3834</v>
       </c>
       <c r="E40" t="n">
-        <v>-2</v>
+        <v>-1.651</v>
       </c>
       <c r="F40" t="n">
-        <v>-2</v>
+        <v>-1.651</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2</v>
+        <v>-1.651</v>
       </c>
       <c r="I40" t="n">
-        <v>-2</v>
+        <v>-1.651</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2</v>
+        <v>-1.651</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2281</v>
+        <v>-2.8222</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0162</v>
+        <v>-0.8884</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.73</v>
+        <v>-1.9121</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2281</v>
+        <v>-2.8222</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7378</v>
+        <v>-1.5912</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.4903</v>
+        <v>-1.231</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7378</v>
+        <v>-1.5912</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7524</v>
+        <v>-1.6566</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.4903</v>
+        <v>-1.231</v>
       </c>
       <c r="K41" t="n">
         <v>141</v>
@@ -2323,7 +2323,7 @@
         <v>117</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.2427</v>
+        <v>-2.8876</v>
       </c>
       <c r="N41" t="n">
         <v>258</v>
@@ -2429,10 +2429,10 @@
         <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2614</v>
+        <v>1.8681</v>
       </c>
       <c r="J2" t="n">
-        <v>36.1824</v>
+        <v>29.8896</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.79</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5924</v>
+        <v>1.4116</v>
       </c>
       <c r="J3" t="n">
-        <v>25.4784</v>
+        <v>22.5856</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.51</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0159</v>
+        <v>1.0972</v>
       </c>
       <c r="J4" t="n">
-        <v>16.2544</v>
+        <v>17.5552</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.23</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4294</v>
+        <v>0.5526</v>
       </c>
       <c r="J5" t="n">
-        <v>6.8704</v>
+        <v>8.8416</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1687</v>
+        <v>0.2722</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6992</v>
+        <v>4.3552</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9721</v>
+        <v>1.2023</v>
       </c>
       <c r="J7" t="n">
-        <v>15.5536</v>
+        <v>19.2368</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.61</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5432</v>
+        <v>-0.3734</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.6912</v>
+        <v>-5.9744</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.57</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6031</v>
+        <v>-0.4104</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.6496</v>
+        <v>-6.5664</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.37</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8666</v>
+        <v>-0.5984</v>
       </c>
       <c r="J10" t="n">
-        <v>-13.8656</v>
+        <v>-9.574400000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0668</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.0688</v>
+        <v>-12.1376</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.28</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8316</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>19.9584</v>
+        <v>19.2216</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.393</v>
+        <v>0.3619</v>
       </c>
       <c r="J13" t="n">
-        <v>9.432</v>
+        <v>8.685600000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1541</v>
+        <v>-0.1051</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.6984</v>
+        <v>-2.5224</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1937</v>
+        <v>-0.1421</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.6488</v>
+        <v>-3.4104</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4206</v>
+        <v>-0.3626</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.0944</v>
+        <v>-8.702400000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.7977</v>
       </c>
       <c r="J17" t="n">
-        <v>15.6408</v>
+        <v>19.1448</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3641</v>
+        <v>0.4224</v>
       </c>
       <c r="J18" t="n">
-        <v>8.7384</v>
+        <v>10.1376</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1678</v>
+        <v>0.194</v>
       </c>
       <c r="J19" t="n">
-        <v>4.0272</v>
+        <v>4.656</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03</v>
+        <v>0.0588</v>
       </c>
       <c r="J20" t="n">
-        <v>0.72</v>
+        <v>1.4112</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7006</v>
+        <v>-0.4708</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.8144</v>
+        <v>-11.2992</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>1.035</v>
+        <v>0.7428</v>
       </c>
       <c r="J22" t="n">
-        <v>23.805</v>
+        <v>17.0844</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7422</v>
+        <v>0.5633</v>
       </c>
       <c r="J23" t="n">
-        <v>17.0706</v>
+        <v>12.9559</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4549</v>
+        <v>0.4026</v>
       </c>
       <c r="J24" t="n">
-        <v>10.4627</v>
+        <v>9.2598</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0907</v>
+        <v>-0.0286</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0861</v>
+        <v>-0.6578000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6849</v>
+        <v>-0.6296</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.7527</v>
+        <v>-14.4808</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.4928</v>
       </c>
       <c r="J27" t="n">
-        <v>11.7438</v>
+        <v>11.3344</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1398</v>
+        <v>0.1414</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2154</v>
+        <v>3.2522</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1099</v>
+        <v>-0.0623</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.5277</v>
+        <v>-1.4329</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2072</v>
+        <v>-0.122</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.7656</v>
+        <v>-2.806</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.74</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4652</v>
+        <v>-0.2968</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.6996</v>
+        <v>-6.8264</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.07</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2507</v>
+        <v>0.1916</v>
       </c>
       <c r="J32" t="n">
-        <v>4.5126</v>
+        <v>3.4488</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.76</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3815</v>
+        <v>-0.2543</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.867</v>
+        <v>-4.5774</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.76</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3815</v>
+        <v>-0.2543</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.867</v>
+        <v>-4.5774</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4282</v>
+        <v>-0.2831</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.7076</v>
+        <v>-5.0958</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4432</v>
+        <v>-0.2926</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.9776</v>
+        <v>-5.2668</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.92</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0933</v>
+        <v>0.7345</v>
       </c>
       <c r="J37" t="n">
-        <v>19.6794</v>
+        <v>13.221</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.53</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6833</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>12.2994</v>
+        <v>9.081</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.38</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4838</v>
+        <v>0.4131</v>
       </c>
       <c r="J39" t="n">
-        <v>8.708399999999999</v>
+        <v>7.4358</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.37</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4694</v>
+        <v>0.4069</v>
       </c>
       <c r="J40" t="n">
-        <v>8.449199999999999</v>
+        <v>7.3242</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.481</v>
+        <v>-0.3046</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.657999999999999</v>
+        <v>-5.4828</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.93</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8519</v>
+        <v>1.3618</v>
       </c>
       <c r="J42" t="n">
-        <v>37.038</v>
+        <v>27.236</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.32</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7719</v>
+        <v>0.6177</v>
       </c>
       <c r="J43" t="n">
-        <v>15.438</v>
+        <v>12.354</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6294</v>
+        <v>0.5532</v>
       </c>
       <c r="J44" t="n">
-        <v>12.588</v>
+        <v>11.064</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.03</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0211</v>
+        <v>0.0594</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.422</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2926</v>
+        <v>-0.2071</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.852</v>
+        <v>-4.142</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.611</v>
+        <v>0.5726</v>
       </c>
       <c r="J47" t="n">
-        <v>12.22</v>
+        <v>11.452</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.32</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5605</v>
+        <v>0.5316</v>
       </c>
       <c r="J48" t="n">
-        <v>11.21</v>
+        <v>10.632</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.87</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2644</v>
+        <v>-0.162</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.288</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5514</v>
+        <v>-0.3597</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.028</v>
+        <v>-7.194</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.676</v>
+        <v>-0.4522</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.52</v>
+        <v>-9.044</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.43</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1025</v>
+        <v>0.7881</v>
       </c>
       <c r="J52" t="n">
-        <v>31.9725</v>
+        <v>22.8549</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4549</v>
+        <v>0.4141</v>
       </c>
       <c r="J53" t="n">
-        <v>13.1921</v>
+        <v>12.0089</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3219</v>
+        <v>0.3539</v>
       </c>
       <c r="J54" t="n">
-        <v>9.335100000000001</v>
+        <v>10.2631</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1693</v>
+        <v>0.226</v>
       </c>
       <c r="J55" t="n">
-        <v>4.9097</v>
+        <v>6.554</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.164</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.756</v>
+        <v>-2.6622</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7543</v>
+        <v>0.6925</v>
       </c>
       <c r="J57" t="n">
-        <v>21.8747</v>
+        <v>20.0825</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.203</v>
+        <v>0.2028</v>
       </c>
       <c r="J58" t="n">
-        <v>5.887</v>
+        <v>5.8812</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.72</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4787</v>
+        <v>-0.3086</v>
       </c>
       <c r="J59" t="n">
-        <v>-13.8823</v>
+        <v>-8.949400000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4923</v>
+        <v>-0.3182</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.2767</v>
+        <v>-9.2278</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5455</v>
+        <v>-0.3561</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.8195</v>
+        <v>-10.3269</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3616</v>
+        <v>0.306</v>
       </c>
       <c r="J62" t="n">
-        <v>7.9552</v>
+        <v>6.732</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.04</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1574</v>
+        <v>0.109</v>
       </c>
       <c r="J63" t="n">
-        <v>3.4628</v>
+        <v>2.398</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0538</v>
+        <v>0.0163</v>
       </c>
       <c r="J64" t="n">
-        <v>1.1836</v>
+        <v>0.3586</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.539</v>
+        <v>-0.3524</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.858</v>
+        <v>-7.7528</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6038</v>
+        <v>-0.3992</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.2836</v>
+        <v>-8.782400000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.66</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8884</v>
+        <v>0.6111</v>
       </c>
       <c r="J67" t="n">
-        <v>19.5448</v>
+        <v>13.4442</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.27</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4249</v>
+        <v>0.3543</v>
       </c>
       <c r="J68" t="n">
-        <v>9.347799999999999</v>
+        <v>7.7946</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.09</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1283</v>
+        <v>0.1416</v>
       </c>
       <c r="J69" t="n">
-        <v>2.8226</v>
+        <v>3.1152</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0367</v>
+        <v>0.064</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8074</v>
+        <v>1.408</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.442</v>
+        <v>-0.2765</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.724</v>
+        <v>-6.083</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4923</v>
+        <v>1.0428</v>
       </c>
       <c r="J72" t="n">
-        <v>35.8152</v>
+        <v>25.0272</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.11</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3597</v>
+        <v>0.3436</v>
       </c>
       <c r="J73" t="n">
-        <v>8.6328</v>
+        <v>8.2464</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0203</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.7856</v>
+        <v>-0.4872</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3802</v>
+        <v>-0.3154</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.1248</v>
+        <v>-7.5696</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6751</v>
+        <v>-0.621</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.2024</v>
+        <v>-14.904</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.53</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8034</v>
+        <v>0.7326</v>
       </c>
       <c r="J77" t="n">
-        <v>19.2816</v>
+        <v>17.5824</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1424</v>
+        <v>0.1427</v>
       </c>
       <c r="J78" t="n">
-        <v>3.4176</v>
+        <v>3.4248</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3504</v>
+        <v>-0.217</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.409599999999999</v>
+        <v>-5.208</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4365</v>
+        <v>-0.2767</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.476</v>
+        <v>-6.6408</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4365</v>
+        <v>-0.2767</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.476</v>
+        <v>-6.6408</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5177</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
-        <v>11.9071</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.23</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3824</v>
+        <v>0.3242</v>
       </c>
       <c r="J83" t="n">
-        <v>8.795199999999999</v>
+        <v>7.4566</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2754</v>
+        <v>0.2387</v>
       </c>
       <c r="J84" t="n">
-        <v>6.3342</v>
+        <v>5.4901</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.15</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2585</v>
+        <v>0.2259</v>
       </c>
       <c r="J85" t="n">
-        <v>5.9455</v>
+        <v>5.1957</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4494</v>
+        <v>-0.2825</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.3362</v>
+        <v>-6.4975</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5265</v>
+        <v>0.418</v>
       </c>
       <c r="J87" t="n">
-        <v>12.1095</v>
+        <v>9.614000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0522</v>
+        <v>-0.0458</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.2006</v>
+        <v>-1.0534</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.95</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0988</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.2724</v>
+        <v>-1.6422</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1692</v>
+        <v>-0.1059</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.8916</v>
+        <v>-2.4357</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6495</v>
+        <v>-0.4324</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.9385</v>
+        <v>-9.9452</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4212</v>
+        <v>0.419</v>
       </c>
       <c r="J92" t="n">
-        <v>8.002800000000001</v>
+        <v>7.961</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2703</v>
+        <v>-0.2047</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.1357</v>
+        <v>-3.8893</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.74</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.403</v>
+        <v>-0.2706</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.657</v>
+        <v>-5.1414</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.67</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.508</v>
+        <v>-0.3369</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.651999999999999</v>
+        <v>-6.4011</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.54</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6818</v>
+        <v>-0.4585</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.9542</v>
+        <v>-8.711499999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.59</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3546</v>
+        <v>0.9591</v>
       </c>
       <c r="J97" t="n">
-        <v>25.7374</v>
+        <v>18.2229</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.42</v>
       </c>
       <c r="I98" t="n">
-        <v>1.0108</v>
+        <v>0.7471</v>
       </c>
       <c r="J98" t="n">
-        <v>19.2052</v>
+        <v>14.1949</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6118</v>
+        <v>0.541</v>
       </c>
       <c r="J99" t="n">
-        <v>11.6242</v>
+        <v>10.279</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2252</v>
+        <v>0.3087</v>
       </c>
       <c r="J100" t="n">
-        <v>4.2788</v>
+        <v>5.8653</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.08</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1406</v>
+        <v>0.2229</v>
       </c>
       <c r="J101" t="n">
-        <v>2.6714</v>
+        <v>4.2351</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.17</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3381</v>
+        <v>0.3622</v>
       </c>
       <c r="J102" t="n">
-        <v>7.7763</v>
+        <v>8.3306</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2263</v>
+        <v>0.2454</v>
       </c>
       <c r="J103" t="n">
-        <v>5.2049</v>
+        <v>5.6442</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.209</v>
+        <v>0.2249</v>
       </c>
       <c r="J104" t="n">
-        <v>4.807</v>
+        <v>5.1727</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.246</v>
+        <v>-0.1457</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.658</v>
+        <v>-3.3511</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4269</v>
+        <v>-0.2692</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.8187</v>
+        <v>-6.1916</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.93</v>
       </c>
       <c r="I107" t="n">
-        <v>1.8854</v>
+        <v>1.4078</v>
       </c>
       <c r="J107" t="n">
-        <v>43.3642</v>
+        <v>32.3794</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.6496</v>
       </c>
       <c r="J108" t="n">
-        <v>20.1135</v>
+        <v>14.9408</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.25</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6854</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="J109" t="n">
-        <v>15.7642</v>
+        <v>12.4154</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.71</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.9287</v>
+        <v>-0.8949</v>
       </c>
       <c r="J110" t="n">
-        <v>-21.3601</v>
+        <v>-20.5827</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.036</v>
+        <v>-1.0154</v>
       </c>
       <c r="J111" t="n">
-        <v>-23.828</v>
+        <v>-23.3542</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.3</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8338</v>
+        <v>0.6187</v>
       </c>
       <c r="J112" t="n">
-        <v>20.0112</v>
+        <v>14.8488</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7158</v>
+        <v>0.5484</v>
       </c>
       <c r="J113" t="n">
-        <v>17.1792</v>
+        <v>13.1616</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.12</v>
       </c>
       <c r="I114" t="n">
-        <v>0.347</v>
+        <v>0.3569</v>
       </c>
       <c r="J114" t="n">
-        <v>8.327999999999999</v>
+        <v>8.5656</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.05</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1194</v>
+        <v>0.1705</v>
       </c>
       <c r="J115" t="n">
-        <v>2.8656</v>
+        <v>4.092</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4236</v>
+        <v>-0.355</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.1664</v>
+        <v>-8.52</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.44</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6794</v>
+        <v>0.6293</v>
       </c>
       <c r="J117" t="n">
-        <v>16.3056</v>
+        <v>15.1032</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.607</v>
+        <v>0.571</v>
       </c>
       <c r="J118" t="n">
-        <v>14.568</v>
+        <v>13.704</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0356</v>
+        <v>0.0606</v>
       </c>
       <c r="J119" t="n">
-        <v>0.8544</v>
+        <v>1.4544</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.83</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3499</v>
+        <v>-0.2137</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.397600000000001</v>
+        <v>-5.1288</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7109</v>
+        <v>-0.4787</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.0616</v>
+        <v>-11.4888</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.9</v>
       </c>
       <c r="I122" t="n">
-        <v>1.8053</v>
+        <v>1.3049</v>
       </c>
       <c r="J122" t="n">
-        <v>32.4954</v>
+        <v>23.4882</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.81</v>
       </c>
       <c r="I123" t="n">
-        <v>1.708</v>
+        <v>1.2009</v>
       </c>
       <c r="J123" t="n">
-        <v>30.744</v>
+        <v>21.6162</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.57</v>
       </c>
       <c r="I124" t="n">
-        <v>1.2744</v>
+        <v>0.9175</v>
       </c>
       <c r="J124" t="n">
-        <v>22.9392</v>
+        <v>16.515</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6486</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.6748</v>
+        <v>-10.4976</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8126</v>
+        <v>-0.7644</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.6268</v>
+        <v>-13.7592</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>0.99</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0867</v>
+        <v>0.0459</v>
       </c>
       <c r="J127" t="n">
-        <v>1.5606</v>
+        <v>0.8262</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.89</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1106</v>
+        <v>-0.1102</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.9908</v>
+        <v>-1.9836</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1781</v>
+        <v>-0.1553</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.2058</v>
+        <v>-2.7954</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.54</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.6706</v>
+        <v>-0.4517</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.0708</v>
+        <v>-8.130599999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.43</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8087</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.5566</v>
+        <v>-9.9702</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>1.9742</v>
+        <v>1.6764</v>
       </c>
       <c r="J132" t="n">
-        <v>29.613</v>
+        <v>25.146</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.58</v>
       </c>
       <c r="I133" t="n">
-        <v>1.2428</v>
+        <v>1.1877</v>
       </c>
       <c r="J133" t="n">
-        <v>18.642</v>
+        <v>17.8155</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.57</v>
       </c>
       <c r="I134" t="n">
-        <v>1.2224</v>
+        <v>1.176</v>
       </c>
       <c r="J134" t="n">
-        <v>18.336</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.35</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7245</v>
+        <v>0.8497</v>
       </c>
       <c r="J135" t="n">
-        <v>10.8675</v>
+        <v>12.7455</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4295</v>
+        <v>-0.3458</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.4425</v>
+        <v>-5.187</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.2118</v>
+        <v>-0.1887</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.177</v>
+        <v>-2.8305</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.73</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.3051</v>
+        <v>-0.2528</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.5765</v>
+        <v>-3.792</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.63</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4682</v>
+        <v>-0.35</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.023</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.52</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6574</v>
+        <v>-0.4496</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.861000000000001</v>
+        <v>-6.744</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7935</v>
+        <v>-0.5441</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.9025</v>
+        <v>-8.1615</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3029</v>
+        <v>0.2551</v>
       </c>
       <c r="J142" t="n">
-        <v>8.7841</v>
+        <v>7.3979</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.271</v>
+        <v>0.2248</v>
       </c>
       <c r="J143" t="n">
-        <v>7.859</v>
+        <v>6.5192</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0766</v>
+        <v>-0.048</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.2214</v>
+        <v>-1.392</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2191</v>
+        <v>-0.1314</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.3539</v>
+        <v>-3.8106</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.74</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4618</v>
+        <v>-0.2949</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.3922</v>
+        <v>-8.552099999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.29</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4633</v>
+        <v>0.3977</v>
       </c>
       <c r="J147" t="n">
-        <v>13.4357</v>
+        <v>11.5333</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.25</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4087</v>
+        <v>0.3497</v>
       </c>
       <c r="J148" t="n">
-        <v>11.8523</v>
+        <v>10.1413</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.14</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2368</v>
+        <v>0.2126</v>
       </c>
       <c r="J149" t="n">
-        <v>6.8672</v>
+        <v>6.1654</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.01</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0213</v>
+        <v>0.0116</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.6177</v>
+        <v>0.3364</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.98</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1138</v>
+        <v>-0.0491</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.3002</v>
+        <v>-1.4239</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.44</v>
       </c>
       <c r="I152" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J152" t="n">
-        <v>41.186</v>
+        <v>36.676</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.58</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2912</v>
+        <v>1.2022</v>
       </c>
       <c r="J153" t="n">
-        <v>25.824</v>
+        <v>24.044</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4206</v>
+        <v>0.5226</v>
       </c>
       <c r="J154" t="n">
-        <v>8.412000000000001</v>
+        <v>10.452</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4094</v>
+        <v>-0.3258</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.188000000000001</v>
+        <v>-6.516</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8136</v>
+        <v>-0.7655</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.272</v>
+        <v>-15.31</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6207</v>
+        <v>0.7544</v>
       </c>
       <c r="J157" t="n">
-        <v>12.414</v>
+        <v>15.088</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0567</v>
+        <v>-0.0618</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.134</v>
+        <v>-1.236</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.93</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0959</v>
+        <v>-0.0866</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.918</v>
+        <v>-1.732</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.6</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6224</v>
+        <v>-0.4135</v>
       </c>
       <c r="J160" t="n">
-        <v>-12.448</v>
+        <v>-8.27</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7457</v>
+        <v>-0.5054</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.914</v>
+        <v>-10.108</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.56</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3211</v>
+        <v>1.2077</v>
       </c>
       <c r="J162" t="n">
-        <v>27.7431</v>
+        <v>25.3617</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2226</v>
+        <v>1.1448</v>
       </c>
       <c r="J163" t="n">
-        <v>25.6746</v>
+        <v>24.0408</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9292</v>
+        <v>0.9384</v>
       </c>
       <c r="J164" t="n">
-        <v>19.5132</v>
+        <v>19.7064</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0994</v>
+        <v>0.1744</v>
       </c>
       <c r="J165" t="n">
-        <v>2.0874</v>
+        <v>3.6624</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.9631</v>
+        <v>-0.9331</v>
       </c>
       <c r="J166" t="n">
-        <v>-20.2251</v>
+        <v>-19.5951</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.36</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5947</v>
+        <v>0.7178</v>
       </c>
       <c r="J167" t="n">
-        <v>12.4887</v>
+        <v>15.0738</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.04</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1116</v>
+        <v>0.115</v>
       </c>
       <c r="J168" t="n">
-        <v>2.3436</v>
+        <v>2.415</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1171</v>
+        <v>-0.0638</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.4591</v>
+        <v>-1.3398</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3259</v>
+        <v>-0.199</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.8439</v>
+        <v>-4.179</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.83</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.341</v>
+        <v>-0.2093</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.161</v>
+        <v>-4.3953</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2185</v>
+        <v>1.1347</v>
       </c>
       <c r="J172" t="n">
-        <v>35.3365</v>
+        <v>32.9063</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.43</v>
       </c>
       <c r="I173" t="n">
-        <v>1.1161</v>
+        <v>1.0686</v>
       </c>
       <c r="J173" t="n">
-        <v>32.3669</v>
+        <v>30.9894</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.2</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5887</v>
+        <v>0.575</v>
       </c>
       <c r="J174" t="n">
-        <v>17.0723</v>
+        <v>16.675</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.9</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4528</v>
+        <v>-0.3848</v>
       </c>
       <c r="J175" t="n">
-        <v>-13.1312</v>
+        <v>-11.1592</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.0894</v>
+        <v>-1.0759</v>
       </c>
       <c r="J176" t="n">
-        <v>-31.5926</v>
+        <v>-31.2011</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.82</v>
       </c>
       <c r="I177" t="n">
-        <v>1.096</v>
+        <v>1.2586</v>
       </c>
       <c r="J177" t="n">
-        <v>31.784</v>
+        <v>36.4994</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.06</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1395</v>
+        <v>0.1554</v>
       </c>
       <c r="J178" t="n">
-        <v>4.0455</v>
+        <v>4.5066</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.89</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2545</v>
+        <v>-0.1491</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.3805</v>
+        <v>-4.3239</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3768</v>
+        <v>-0.2329</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.9272</v>
+        <v>-6.7541</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.59</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6625</v>
+        <v>-0.4417</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.2125</v>
+        <v>-12.8093</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.43</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6908</v>
+        <v>0.6506</v>
       </c>
       <c r="J182" t="n">
-        <v>16.5792</v>
+        <v>15.6144</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0551</v>
+        <v>0.0321</v>
       </c>
       <c r="J183" t="n">
-        <v>1.3224</v>
+        <v>0.7704</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1443</v>
+        <v>-0.0856</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.4632</v>
+        <v>-2.0544</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3626</v>
+        <v>-0.2259</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.702400000000001</v>
+        <v>-5.4216</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.68</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5415</v>
+        <v>-0.3522</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.996</v>
+        <v>-8.4528</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.86</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0887</v>
+        <v>0.997</v>
       </c>
       <c r="J187" t="n">
-        <v>26.1288</v>
+        <v>23.928</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.49</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6949</v>
+        <v>0.6156</v>
       </c>
       <c r="J188" t="n">
-        <v>16.6776</v>
+        <v>14.7744</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3608</v>
+        <v>0.3186</v>
       </c>
       <c r="J189" t="n">
-        <v>8.6592</v>
+        <v>7.6464</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4311</v>
+        <v>-0.2684</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.3464</v>
+        <v>-6.4416</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7137</v>
+        <v>-0.4814</v>
       </c>
       <c r="J191" t="n">
-        <v>-17.1288</v>
+        <v>-11.5536</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.87</v>
       </c>
       <c r="I192" t="n">
-        <v>1.821</v>
+        <v>1.5436</v>
       </c>
       <c r="J192" t="n">
-        <v>27.315</v>
+        <v>23.154</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.51</v>
       </c>
       <c r="I193" t="n">
-        <v>1.153</v>
+        <v>1.1184</v>
       </c>
       <c r="J193" t="n">
-        <v>17.295</v>
+        <v>16.776</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.5</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1323</v>
+        <v>1.1063</v>
       </c>
       <c r="J194" t="n">
-        <v>16.9845</v>
+        <v>16.5945</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.28</v>
       </c>
       <c r="I195" t="n">
-        <v>0.6109</v>
+        <v>0.7137</v>
       </c>
       <c r="J195" t="n">
-        <v>9.163500000000001</v>
+        <v>10.7055</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8575</v>
+        <v>-0.8146</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.8625</v>
+        <v>-12.219</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.04</v>
       </c>
       <c r="I197" t="n">
-        <v>0.171</v>
+        <v>0.1543</v>
       </c>
       <c r="J197" t="n">
-        <v>2.565</v>
+        <v>2.3145</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.93</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0959</v>
+        <v>-0.0866</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.4385</v>
+        <v>-1.299</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.9</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1527</v>
+        <v>-0.121</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.2905</v>
+        <v>-1.815</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2363</v>
+        <v>-0.1626</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.5445</v>
+        <v>-2.439</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.59</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6351</v>
+        <v>-0.4227</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.5265</v>
+        <v>-6.3405</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2111</v>
+        <v>1.1331</v>
       </c>
       <c r="J202" t="n">
-        <v>41.1774</v>
+        <v>38.5254</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9819</v>
+        <v>0.9747</v>
       </c>
       <c r="J203" t="n">
-        <v>33.3846</v>
+        <v>33.1398</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4192</v>
+        <v>0.466</v>
       </c>
       <c r="J204" t="n">
-        <v>14.2528</v>
+        <v>15.844</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.96</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2894</v>
+        <v>-0.2125</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.839600000000001</v>
+        <v>-7.225</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.92</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.414</v>
+        <v>-0.3399</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.076</v>
+        <v>-11.5566</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.41</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6681</v>
+        <v>0.8186</v>
       </c>
       <c r="J207" t="n">
-        <v>22.7154</v>
+        <v>27.8324</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.96</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0987</v>
+        <v>-0.0606</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.3558</v>
+        <v>-2.0604</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2684</v>
+        <v>-0.1634</v>
       </c>
       <c r="J209" t="n">
-        <v>-9.1256</v>
+        <v>-5.5556</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.85</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3005</v>
+        <v>-0.1845</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.217</v>
+        <v>-6.273</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.76</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4334</v>
+        <v>-0.275</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.7356</v>
+        <v>-9.35</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4482</v>
+        <v>0.5236</v>
       </c>
       <c r="J212" t="n">
-        <v>10.7568</v>
+        <v>12.5664</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.15</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3032</v>
+        <v>0.3405</v>
       </c>
       <c r="J213" t="n">
-        <v>7.2768</v>
+        <v>8.172000000000001</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.13</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2716</v>
+        <v>0.302</v>
       </c>
       <c r="J214" t="n">
-        <v>6.5184</v>
+        <v>7.248</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.07</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1675</v>
+        <v>0.1802</v>
       </c>
       <c r="J215" t="n">
-        <v>4.02</v>
+        <v>4.3248</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.48</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7883</v>
+        <v>-0.5385</v>
       </c>
       <c r="J216" t="n">
-        <v>-18.9192</v>
+        <v>-12.924</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.55</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3592</v>
+        <v>1.2272</v>
       </c>
       <c r="J217" t="n">
-        <v>32.6208</v>
+        <v>29.4528</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.12</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3496</v>
+        <v>0.373</v>
       </c>
       <c r="J218" t="n">
-        <v>8.3904</v>
+        <v>8.952</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.05</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1205</v>
+        <v>0.171</v>
       </c>
       <c r="J219" t="n">
-        <v>2.892</v>
+        <v>4.104</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.05</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1205</v>
+        <v>0.171</v>
       </c>
       <c r="J220" t="n">
-        <v>2.892</v>
+        <v>4.104</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.85</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5855</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.052</v>
+        <v>-12.5688</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.19</v>
       </c>
       <c r="I222" t="n">
-        <v>0.462</v>
+        <v>0.5364</v>
       </c>
       <c r="J222" t="n">
-        <v>8.778</v>
+        <v>10.1916</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.77</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.3253</v>
+        <v>-0.2401</v>
       </c>
       <c r="J223" t="n">
-        <v>-6.1807</v>
+        <v>-4.5619</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.73</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.4055</v>
+        <v>-0.2767</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.7045</v>
+        <v>-5.2573</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.63</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.5555</v>
+        <v>-0.3707</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.5545</v>
+        <v>-7.0433</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.48</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7513</v>
+        <v>-0.5104</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.2747</v>
+        <v>-9.6976</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.64</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4135</v>
+        <v>1.2769</v>
       </c>
       <c r="J227" t="n">
-        <v>26.8565</v>
+        <v>24.2611</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.56</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2593</v>
+        <v>1.1809</v>
       </c>
       <c r="J228" t="n">
-        <v>23.9267</v>
+        <v>22.4371</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.28</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6163</v>
+        <v>0.716</v>
       </c>
       <c r="J229" t="n">
-        <v>11.7097</v>
+        <v>13.604</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.26</v>
       </c>
       <c r="I230" t="n">
-        <v>0.5693</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J230" t="n">
-        <v>10.8167</v>
+        <v>12.7281</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I231" t="n">
-        <v>0.2251</v>
+        <v>0.3186</v>
       </c>
       <c r="J231" t="n">
-        <v>4.2769</v>
+        <v>6.0534</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.74</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6918</v>
+        <v>1.4527</v>
       </c>
       <c r="J232" t="n">
-        <v>37.2196</v>
+        <v>31.9594</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.58</v>
       </c>
       <c r="I233" t="n">
-        <v>1.3948</v>
+        <v>1.2521</v>
       </c>
       <c r="J233" t="n">
-        <v>30.6856</v>
+        <v>27.5462</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.95</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3175</v>
+        <v>-0.2423</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.985</v>
+        <v>-5.3306</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6979</v>
+        <v>-0.6414</v>
       </c>
       <c r="J235" t="n">
-        <v>-15.3538</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8152</v>
+        <v>-0.7692</v>
       </c>
       <c r="J236" t="n">
-        <v>-17.9344</v>
+        <v>-16.9224</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3669</v>
+        <v>0.4092</v>
       </c>
       <c r="J237" t="n">
-        <v>8.0718</v>
+        <v>9.0024</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2568</v>
+        <v>0.2687</v>
       </c>
       <c r="J238" t="n">
-        <v>5.6496</v>
+        <v>5.9114</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2046</v>
+        <v>0.204</v>
       </c>
       <c r="J239" t="n">
-        <v>4.5012</v>
+        <v>4.488</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.86</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2686</v>
+        <v>-0.1687</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.9092</v>
+        <v>-3.7114</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.42</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8464</v>
+        <v>-0.5835</v>
       </c>
       <c r="J241" t="n">
-        <v>-18.6208</v>
+        <v>-12.837</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2997</v>
+        <v>1.1894</v>
       </c>
       <c r="J242" t="n">
-        <v>36.3916</v>
+        <v>33.3032</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.8125</v>
+        <v>0.8042</v>
       </c>
       <c r="J243" t="n">
-        <v>22.75</v>
+        <v>22.5176</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.1282</v>
       </c>
       <c r="J244" t="n">
-        <v>1.8396</v>
+        <v>3.5896</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.1282</v>
       </c>
       <c r="J245" t="n">
-        <v>1.8396</v>
+        <v>3.5896</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.91</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4369</v>
+        <v>-0.3651</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.2332</v>
+        <v>-10.2228</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3404</v>
+        <v>0.374</v>
       </c>
       <c r="J247" t="n">
-        <v>9.5312</v>
+        <v>10.472</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2084</v>
+        <v>0.2073</v>
       </c>
       <c r="J248" t="n">
-        <v>5.8352</v>
+        <v>5.8044</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.98</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0138</v>
+        <v>-0.028</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.3864</v>
+        <v>-0.784</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3603</v>
+        <v>-0.2286</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.0884</v>
+        <v>-6.4008</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6691</v>
+        <v>-0.4473</v>
       </c>
       <c r="J251" t="n">
-        <v>-18.7348</v>
+        <v>-12.5244</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.96</v>
       </c>
       <c r="I252" t="n">
-        <v>1.9782</v>
+        <v>1.679</v>
       </c>
       <c r="J252" t="n">
-        <v>37.5858</v>
+        <v>31.901</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.61</v>
       </c>
       <c r="I253" t="n">
-        <v>1.3993</v>
+        <v>1.2606</v>
       </c>
       <c r="J253" t="n">
-        <v>26.5867</v>
+        <v>23.9514</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.14</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3115</v>
+        <v>0.3937</v>
       </c>
       <c r="J254" t="n">
-        <v>5.9185</v>
+        <v>7.4803</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.96</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3196</v>
+        <v>-0.236</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.0724</v>
+        <v>-4.484</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.72</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.8924</v>
       </c>
       <c r="J256" t="n">
-        <v>-17.6111</v>
+        <v>-16.9556</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.99</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0629</v>
+        <v>0.0192</v>
       </c>
       <c r="J257" t="n">
-        <v>1.1951</v>
+        <v>0.3648</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1006</v>
+        <v>-0.0985</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.9114</v>
+        <v>-1.8715</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1534</v>
+        <v>-0.1327</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.9146</v>
+        <v>-2.5213</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.73</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4224</v>
+        <v>-0.2812</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.025600000000001</v>
+        <v>-5.3428</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7821</v>
+        <v>-0.5334</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.8599</v>
+        <v>-10.1346</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.56</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3704</v>
+        <v>1.2351</v>
       </c>
       <c r="J262" t="n">
-        <v>30.1488</v>
+        <v>27.1722</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.25</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7075</v>
+        <v>0.6934</v>
       </c>
       <c r="J263" t="n">
-        <v>15.565</v>
+        <v>15.2548</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.02</v>
       </c>
       <c r="I264" t="n">
-        <v>0.003</v>
+        <v>0.0625</v>
       </c>
       <c r="J264" t="n">
-        <v>0.066</v>
+        <v>1.375</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.339</v>
+        <v>-0.2672</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.458</v>
+        <v>-5.8784</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.93</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3698</v>
+        <v>-0.2984</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.1356</v>
+        <v>-6.5648</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3646</v>
+        <v>0.4036</v>
       </c>
       <c r="J267" t="n">
-        <v>8.0212</v>
+        <v>8.879200000000001</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.93</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1087</v>
+        <v>-0.09</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.3914</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.88</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2156</v>
+        <v>-0.1443</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.7432</v>
+        <v>-3.1746</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3523</v>
+        <v>-0.2256</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.7506</v>
+        <v>-4.9632</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5238</v>
+        <v>-0.3419</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.5236</v>
+        <v>-7.5218</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.79</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8315</v>
+        <v>1.5542</v>
       </c>
       <c r="J272" t="n">
-        <v>43.956</v>
+        <v>37.3008</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.93</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.3418</v>
+        <v>-0.2799</v>
       </c>
       <c r="J273" t="n">
-        <v>-8.203200000000001</v>
+        <v>-6.7176</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3418</v>
+        <v>-0.2799</v>
       </c>
       <c r="J274" t="n">
-        <v>-8.203200000000001</v>
+        <v>-6.7176</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4595</v>
+        <v>-0.3982</v>
       </c>
       <c r="J275" t="n">
-        <v>-11.028</v>
+        <v>-9.556800000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6443</v>
+        <v>-0.5897</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.4632</v>
+        <v>-14.1528</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.45</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.8475</v>
       </c>
       <c r="J277" t="n">
-        <v>16.512</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.45</v>
       </c>
       <c r="I278" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.8475</v>
       </c>
       <c r="J278" t="n">
-        <v>16.512</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.96</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1343</v>
+        <v>-0.0687</v>
       </c>
       <c r="J279" t="n">
-        <v>-3.2232</v>
+        <v>-1.6488</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4773</v>
+        <v>-0.304</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.4552</v>
+        <v>-7.296</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5674</v>
+        <v>-0.3702</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.6176</v>
+        <v>-8.8848</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.18</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3686</v>
+        <v>0.3175</v>
       </c>
       <c r="J282" t="n">
-        <v>8.1092</v>
+        <v>6.985</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3235</v>
+        <v>0.2734</v>
       </c>
       <c r="J283" t="n">
-        <v>7.117</v>
+        <v>6.0148</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0891</v>
+        <v>-0.0601</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.9602</v>
+        <v>-1.3222</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.93</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1576</v>
+        <v>-0.096</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.4672</v>
+        <v>-2.112</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.58</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6642</v>
+        <v>-0.4433</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.6124</v>
+        <v>-9.752599999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.71</v>
       </c>
       <c r="I287" t="n">
-        <v>0.9315</v>
+        <v>0.848</v>
       </c>
       <c r="J287" t="n">
-        <v>20.493</v>
+        <v>18.656</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>0.7019</v>
+        <v>0.6232</v>
       </c>
       <c r="J288" t="n">
-        <v>15.4418</v>
+        <v>13.7104</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.14</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2004</v>
+        <v>0.2065</v>
       </c>
       <c r="J289" t="n">
-        <v>4.4088</v>
+        <v>4.543</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.85</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3496</v>
+        <v>-0.2092</v>
       </c>
       <c r="J290" t="n">
-        <v>-7.6912</v>
+        <v>-4.6024</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4061</v>
+        <v>-0.25</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.934200000000001</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.44</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1787</v>
+        <v>1.1056</v>
       </c>
       <c r="J292" t="n">
-        <v>25.9314</v>
+        <v>24.3232</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.2</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6372</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>14.0184</v>
+        <v>13.2066</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.04</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1393</v>
+        <v>0.1547</v>
       </c>
       <c r="J294" t="n">
-        <v>3.0646</v>
+        <v>3.4034</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.6615</v>
+        <v>-0.6098</v>
       </c>
       <c r="J295" t="n">
-        <v>-14.553</v>
+        <v>-13.4156</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.76</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7825</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="J296" t="n">
-        <v>-17.215</v>
+        <v>-16.2448</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.42</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6575</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>14.465</v>
+        <v>17.7078</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.12</v>
       </c>
       <c r="I298" t="n">
-        <v>0.2468</v>
+        <v>0.2773</v>
       </c>
       <c r="J298" t="n">
-        <v>5.4296</v>
+        <v>6.1006</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2127</v>
+        <v>0.2378</v>
       </c>
       <c r="J299" t="n">
-        <v>4.6794</v>
+        <v>5.2316</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.97</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1078</v>
+        <v>-0.0537</v>
       </c>
       <c r="J300" t="n">
-        <v>-2.3716</v>
+        <v>-1.1814</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.58</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.4512</v>
       </c>
       <c r="J301" t="n">
-        <v>-14.8478</v>
+        <v>-9.926399999999999</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.67</v>
       </c>
       <c r="I302" t="n">
-        <v>1.4972</v>
+        <v>1.3261</v>
       </c>
       <c r="J302" t="n">
-        <v>28.4468</v>
+        <v>25.1959</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1889</v>
+        <v>1.1306</v>
       </c>
       <c r="J303" t="n">
-        <v>22.5891</v>
+        <v>21.4814</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.44</v>
       </c>
       <c r="I304" t="n">
-        <v>1.0442</v>
+        <v>1.0421</v>
       </c>
       <c r="J304" t="n">
-        <v>19.8398</v>
+        <v>19.7999</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.99</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2164</v>
+        <v>-0.13</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.1116</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3912</v>
+        <v>-0.3089</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.4328</v>
+        <v>-5.8691</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.44</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7371</v>
+        <v>0.9203</v>
       </c>
       <c r="J307" t="n">
-        <v>14.0049</v>
+        <v>17.4857</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.3329</v>
+        <v>-0.2144</v>
       </c>
       <c r="J308" t="n">
-        <v>-6.3251</v>
+        <v>-4.0736</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.75</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4237</v>
+        <v>-0.2735</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.0503</v>
+        <v>-5.1965</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.71</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4804</v>
+        <v>-0.312</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.127599999999999</v>
+        <v>-5.928</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5079</v>
+        <v>-0.3311</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.6501</v>
+        <v>-6.2909</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.43</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0933</v>
+        <v>1.0572</v>
       </c>
       <c r="J312" t="n">
-        <v>24.0526</v>
+        <v>23.2584</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.33</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8767</v>
+        <v>0.8711</v>
       </c>
       <c r="J313" t="n">
-        <v>19.2874</v>
+        <v>19.1642</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.339</v>
+        <v>0.3907</v>
       </c>
       <c r="J314" t="n">
-        <v>7.458</v>
+        <v>8.5954</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.06</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1284</v>
+        <v>0.191</v>
       </c>
       <c r="J315" t="n">
-        <v>2.8248</v>
+        <v>4.202</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4395</v>
+        <v>-0.3671</v>
       </c>
       <c r="J316" t="n">
-        <v>-9.669</v>
+        <v>-8.0762</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.07</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2186</v>
+        <v>0.2163</v>
       </c>
       <c r="J317" t="n">
-        <v>4.8092</v>
+        <v>4.7586</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.04</v>
       </c>
       <c r="I318" t="n">
-        <v>0.1614</v>
+        <v>0.1457</v>
       </c>
       <c r="J318" t="n">
-        <v>3.5508</v>
+        <v>3.2054</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.84</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2871</v>
+        <v>-0.1852</v>
       </c>
       <c r="J319" t="n">
-        <v>-6.3162</v>
+        <v>-4.0744</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.82</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.32</v>
+        <v>-0.2054</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.04</v>
+        <v>-4.5188</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.67</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5367</v>
+        <v>-0.3511</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.8074</v>
+        <v>-7.7242</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6975/event_6975_evp_summary.xlsx
+++ b/database/event/6975/event_6975_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2967</v>
+        <v>6.4653</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9821</v>
+        <v>2.0352</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2046</v>
+        <v>2.3189</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2967</v>
+        <v>6.4653</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7859</v>
+        <v>3.8891</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5108</v>
+        <v>2.5762</v>
       </c>
       <c r="H2" t="n">
-        <v>7.8527</v>
+        <v>7.9374</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0831</v>
+        <v>4.2861</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5108</v>
+        <v>2.5762</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -529,7 +529,7 @@
         <v>115</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5939</v>
+        <v>6.8623</v>
       </c>
       <c r="N2" t="n">
         <v>220</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1195</v>
+        <v>6.0957</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9264</v>
+        <v>1.9189</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1246</v>
+        <v>2.1507</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1195</v>
+        <v>6.0957</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5362</v>
+        <v>3.2228</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5833</v>
+        <v>2.8729</v>
       </c>
       <c r="H3" t="n">
-        <v>4.405</v>
+        <v>4.3288</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5862</v>
+        <v>4.4404</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5833</v>
+        <v>2.8729</v>
       </c>
       <c r="K3" t="n">
         <v>141</v>
@@ -575,7 +575,7 @@
         <v>117</v>
       </c>
       <c r="M3" t="n">
-        <v>7.169499999999999</v>
+        <v>7.3133</v>
       </c>
       <c r="N3" t="n">
         <v>258</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6709</v>
+        <v>5.7188</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7851</v>
+        <v>1.8002</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9221</v>
+        <v>1.9791</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6709</v>
+        <v>5.7188</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1675</v>
+        <v>3.1305</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5034</v>
+        <v>2.5883</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6742</v>
+        <v>5.4343</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9503</v>
+        <v>2.9345</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5034</v>
+        <v>2.5883</v>
       </c>
       <c r="K4" t="n">
         <v>105</v>
@@ -621,7 +621,7 @@
         <v>115</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4537</v>
+        <v>5.5228</v>
       </c>
       <c r="N4" t="n">
         <v>220</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5282</v>
+        <v>5.4655</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7402</v>
+        <v>1.7205</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8577</v>
+        <v>1.8638</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5282</v>
+        <v>5.4655</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5432</v>
+        <v>3.4931</v>
       </c>
       <c r="G5" t="n">
-        <v>1.985</v>
+        <v>1.9724</v>
       </c>
       <c r="H5" t="n">
-        <v>6.9975</v>
+        <v>6.6308</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6384</v>
+        <v>3.5806</v>
       </c>
       <c r="J5" t="n">
-        <v>1.985</v>
+        <v>1.9724</v>
       </c>
       <c r="K5" t="n">
         <v>105</v>
@@ -667,7 +667,7 @@
         <v>115</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6234</v>
+        <v>5.553</v>
       </c>
       <c r="N5" t="n">
         <v>220</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7635</v>
+        <v>4.976</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4995</v>
+        <v>1.5664</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5125</v>
+        <v>1.641</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7635</v>
+        <v>4.976</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4154</v>
+        <v>1.2953</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3481</v>
+        <v>3.6807</v>
       </c>
       <c r="H6" t="n">
-        <v>6.5473</v>
+        <v>1.2953</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4043</v>
+        <v>1.3287</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3481</v>
+        <v>3.6807</v>
       </c>
       <c r="K6" t="n">
         <v>114</v>
       </c>
       <c r="L6" t="n">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7524</v>
+        <v>5.009399999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6421</v>
+        <v>4.7994</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4613</v>
+        <v>1.5108</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4577</v>
+        <v>1.5606</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6421</v>
+        <v>4.7994</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3122</v>
+        <v>3.3437</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3299</v>
+        <v>1.4557</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3122</v>
+        <v>6.1381</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3662</v>
+        <v>3.3145</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3299</v>
+        <v>1.4557</v>
       </c>
       <c r="K7" t="n">
         <v>114</v>
       </c>
       <c r="L7" t="n">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="M7" t="n">
-        <v>4.696099999999999</v>
+        <v>4.7702</v>
       </c>
       <c r="N7" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9331</v>
+        <v>3.9957</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2381</v>
+        <v>1.2578</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1376</v>
+        <v>1.1947</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9331</v>
+        <v>3.9957</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0674</v>
+        <v>3.0138</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8657</v>
+        <v>0.9819</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3212</v>
+        <v>5.0493</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7668</v>
+        <v>2.7266</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8657</v>
+        <v>0.9819</v>
       </c>
       <c r="K8" t="n">
         <v>114</v>
@@ -805,7 +805,7 @@
         <v>101</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6325</v>
+        <v>3.7085</v>
       </c>
       <c r="N8" t="n">
         <v>215</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5168</v>
+        <v>3.4596</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1071</v>
+        <v>1.089</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9496</v>
+        <v>0.9507</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5168</v>
+        <v>3.4596</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7457</v>
+        <v>2.6712</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7711</v>
+        <v>0.7884</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1877</v>
+        <v>3.9189</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1774</v>
+        <v>2.1162</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7711</v>
+        <v>0.7884</v>
       </c>
       <c r="K9" t="n">
         <v>114</v>
@@ -851,7 +851,7 @@
         <v>101</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9485</v>
+        <v>2.9046</v>
       </c>
       <c r="N9" t="n">
         <v>215</v>
@@ -860,139 +860,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4719</v>
+        <v>2.6105</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7781</v>
+        <v>0.8218</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4779</v>
+        <v>0.5641</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4719</v>
+        <v>2.6105</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7064</v>
+        <v>0.2378</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2345</v>
+        <v>2.3728</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0492</v>
+        <v>0.2378</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1054</v>
+        <v>0.2439</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2345</v>
+        <v>2.3728</v>
       </c>
       <c r="K10" t="n">
         <v>114</v>
       </c>
       <c r="L10" t="n">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8709</v>
+        <v>2.6167</v>
       </c>
       <c r="N10" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4091</v>
+        <v>2.5648</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7584</v>
+        <v>0.8074</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4496</v>
+        <v>0.5433</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4091</v>
+        <v>2.5648</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2692</v>
+        <v>-0.0549</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1399</v>
+        <v>2.6197</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2692</v>
+        <v>-0.0549</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2803</v>
+        <v>-0.0563</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1399</v>
+        <v>2.6197</v>
       </c>
       <c r="K11" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="L11" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4202</v>
+        <v>2.5634</v>
       </c>
       <c r="N11" t="n">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.305</v>
+        <v>2.474</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7256</v>
+        <v>0.7788</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4026</v>
+        <v>0.502</v>
       </c>
       <c r="E12" t="n">
-        <v>2.305</v>
+        <v>2.474</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0601</v>
+        <v>2.62</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3651</v>
+        <v>-0.146</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0601</v>
+        <v>3.7502</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0626</v>
+        <v>2.0251</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3651</v>
+        <v>-0.146</v>
       </c>
       <c r="K12" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3025</v>
+        <v>1.8791</v>
       </c>
       <c r="N12" t="n">
-        <v>258</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.258</v>
+        <v>2.2827</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7108</v>
+        <v>0.7186</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3814</v>
+        <v>0.4149</v>
       </c>
       <c r="E13" t="n">
-        <v>2.258</v>
+        <v>2.2827</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2141</v>
+        <v>1.1536</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0439</v>
+        <v>1.1291</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2141</v>
+        <v>1.1536</v>
       </c>
       <c r="I13" t="n">
-        <v>1.264</v>
+        <v>1.1833</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0439</v>
+        <v>1.1291</v>
       </c>
       <c r="K13" t="n">
         <v>111</v>
@@ -1035,7 +1035,7 @@
         <v>65</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3079</v>
+        <v>2.3124</v>
       </c>
       <c r="N13" t="n">
         <v>176</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1507</v>
+        <v>2.0057</v>
       </c>
       <c r="C14" t="n">
-        <v>0.677</v>
+        <v>0.6314</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3329</v>
+        <v>0.2888</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1507</v>
+        <v>2.0057</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5309</v>
+        <v>2.3989</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3802</v>
+        <v>-0.3932</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5309</v>
+        <v>2.5254</v>
       </c>
       <c r="I14" t="n">
-        <v>2.635</v>
+        <v>2.5905</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3802</v>
+        <v>-0.3932</v>
       </c>
       <c r="K14" t="n">
         <v>111</v>
@@ -1081,7 +1081,7 @@
         <v>65</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2548</v>
+        <v>2.1973</v>
       </c>
       <c r="N14" t="n">
         <v>176</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1039</v>
+        <v>1.9978</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6623</v>
+        <v>0.6289</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3118</v>
+        <v>0.2852</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1039</v>
+        <v>1.9978</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4694</v>
+        <v>2.3706</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3655</v>
+        <v>-0.3728</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4694</v>
+        <v>2.4635</v>
       </c>
       <c r="I15" t="n">
-        <v>2.571</v>
+        <v>2.527</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3655</v>
+        <v>-0.3728</v>
       </c>
       <c r="K15" t="n">
         <v>111</v>
@@ -1127,7 +1127,7 @@
         <v>65</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2055</v>
+        <v>2.1542</v>
       </c>
       <c r="N15" t="n">
         <v>176</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9871</v>
+        <v>1.859</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2591</v>
+        <v>0.2221</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9871</v>
+        <v>1.859</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3782</v>
+        <v>2.2533</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3911</v>
+        <v>-0.3943</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3782</v>
+        <v>2.2533</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3782</v>
+        <v>2.2533</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3911</v>
+        <v>-0.3943</v>
       </c>
       <c r="K16" t="n">
         <v>91</v>
@@ -1173,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9871</v>
+        <v>1.859</v>
       </c>
       <c r="N16" t="n">
         <v>133</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3495</v>
+        <v>1.3023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4248</v>
+        <v>0.41</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0288</v>
+        <v>-0.0314</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3495</v>
+        <v>1.3023</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3495</v>
+        <v>0.9335</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.3688</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3495</v>
+        <v>0.9335</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3495</v>
+        <v>0.9576</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.3688</v>
       </c>
       <c r="K17" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3495</v>
+        <v>1.3264</v>
       </c>
       <c r="N17" t="n">
-        <v>84</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3293</v>
+        <v>1.2617</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4184</v>
+        <v>0.3972</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0379</v>
+        <v>-0.0499</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3293</v>
+        <v>1.2617</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9644</v>
+        <v>1.2617</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3649</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9644</v>
+        <v>1.2617</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0041</v>
+        <v>1.2617</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3649</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.369</v>
+        <v>1.2617</v>
       </c>
       <c r="N18" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3003</v>
+        <v>1.2598</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4093</v>
+        <v>0.3966</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.051</v>
+        <v>-0.0507</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3003</v>
+        <v>1.2598</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3003</v>
+        <v>1.2598</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3003</v>
+        <v>1.2598</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3003</v>
+        <v>1.2598</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3003</v>
+        <v>1.2598</v>
       </c>
       <c r="N19" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8583</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2702</v>
+        <v>0.2718</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2505</v>
+        <v>-0.2312</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8583</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0492</v>
+        <v>1.0641</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1909</v>
+        <v>-0.2007</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0492</v>
+        <v>1.0641</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0924</v>
+        <v>1.0915</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1909</v>
+        <v>-0.2007</v>
       </c>
       <c r="K20" t="n">
         <v>111</v>
@@ -1357,7 +1357,7 @@
         <v>65</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9015000000000001</v>
+        <v>0.8907999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>176</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8554</v>
+        <v>0.827</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2693</v>
+        <v>0.2603</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2518</v>
+        <v>-0.2477</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8554</v>
+        <v>0.827</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2513</v>
+        <v>1.2169</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3959</v>
+        <v>-0.3899</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2513</v>
+        <v>1.2169</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6506</v>
+        <v>0.6571</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3959</v>
+        <v>-0.3899</v>
       </c>
       <c r="K21" t="n">
         <v>105</v>
@@ -1403,7 +1403,7 @@
         <v>115</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2547</v>
+        <v>0.2672</v>
       </c>
       <c r="N21" t="n">
         <v>220</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7343</v>
+        <v>0.7538</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2311</v>
+        <v>0.2373</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3065</v>
+        <v>-0.2811</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7343</v>
+        <v>0.7538</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8783</v>
+        <v>0.8298</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.144</v>
+        <v>-0.076</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8783</v>
+        <v>0.8298</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4567</v>
+        <v>0.4481</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.144</v>
+        <v>-0.076</v>
       </c>
       <c r="K22" t="n">
         <v>114</v>
@@ -1449,7 +1449,7 @@
         <v>101</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3127</v>
+        <v>0.3721</v>
       </c>
       <c r="N22" t="n">
         <v>215</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7081</v>
+        <v>0.7024</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2229</v>
+        <v>0.2211</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3183</v>
+        <v>-0.3045</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7081</v>
+        <v>0.7024</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7081</v>
+        <v>0.7024</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7081</v>
+        <v>0.7024</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7081</v>
+        <v>0.7024</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7081</v>
+        <v>0.7024</v>
       </c>
       <c r="N23" t="n">
         <v>100</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4603</v>
+        <v>0.518</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1449</v>
+        <v>0.1631</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4302</v>
+        <v>-0.3884</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4603</v>
+        <v>0.518</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4603</v>
+        <v>0.4172</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1008</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4603</v>
+        <v>0.4172</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4603</v>
+        <v>0.428</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.1008</v>
       </c>
       <c r="K24" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4603</v>
+        <v>0.5287999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4536</v>
+        <v>0.4888</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1428</v>
+        <v>0.1539</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4332</v>
+        <v>-0.4017</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4536</v>
+        <v>0.4888</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3782</v>
+        <v>0.3451</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.1437</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3782</v>
+        <v>0.3451</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3782</v>
+        <v>0.3451</v>
       </c>
       <c r="J25" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.1437</v>
       </c>
       <c r="K25" t="n">
         <v>91</v>
@@ -1587,7 +1587,7 @@
         <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4536</v>
+        <v>0.4888</v>
       </c>
       <c r="N25" t="n">
         <v>133</v>
@@ -1596,323 +1596,323 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4393</v>
+        <v>0.4054</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1383</v>
+        <v>0.1276</v>
       </c>
       <c r="D26" t="n">
         <v>-0.4397</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4393</v>
+        <v>0.4054</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4449</v>
+        <v>0.4054</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0056</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4449</v>
+        <v>0.4054</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4632</v>
+        <v>0.4054</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0056</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4576</v>
+        <v>0.4054</v>
       </c>
       <c r="N26" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1712</v>
+        <v>0.2355</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0539</v>
+        <v>0.0741</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5607</v>
+        <v>-0.517</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1712</v>
+        <v>0.2355</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1712</v>
+        <v>-0.2259</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.4614</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1712</v>
+        <v>-0.2259</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1712</v>
+        <v>-0.2259</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.4614</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1712</v>
+        <v>0.2355</v>
       </c>
       <c r="N27" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1619</v>
+        <v>0.1459</v>
       </c>
       <c r="C28" t="n">
-        <v>0.051</v>
+        <v>0.0459</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5649</v>
+        <v>-0.5578</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1619</v>
+        <v>0.1459</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2538</v>
+        <v>0.1459</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4157</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2538</v>
+        <v>0.1459</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2538</v>
+        <v>0.1459</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4157</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1619</v>
+        <v>0.1459</v>
       </c>
       <c r="N28" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0593</v>
+        <v>-0.0112</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0187</v>
+        <v>-0.0035</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.6293</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0593</v>
+        <v>-0.0112</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0593</v>
+        <v>-0.1487</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.1375</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0593</v>
+        <v>-0.1487</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0593</v>
+        <v>-0.1525</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1375</v>
       </c>
       <c r="K29" t="n">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0593</v>
+        <v>-0.01499999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>84</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1039</v>
+        <v>-0.0757</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0327</v>
+        <v>-0.0238</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6849</v>
+        <v>-0.6587</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1039</v>
+        <v>-0.0757</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0639</v>
+        <v>-1.2471</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1678</v>
+        <v>1.1714</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0639</v>
+        <v>-1.2471</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0639</v>
+        <v>-0.6734</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1678</v>
+        <v>1.1714</v>
       </c>
       <c r="K30" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="L30" t="n">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1039</v>
+        <v>0.498</v>
       </c>
       <c r="N30" t="n">
-        <v>133</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1561</v>
+        <v>-0.1124</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0491</v>
+        <v>-0.0354</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7085</v>
+        <v>-0.6754</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1561</v>
+        <v>-0.1124</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5473</v>
+        <v>-0.1124</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.7034</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5473</v>
+        <v>-0.1124</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5698</v>
+        <v>-0.1124</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.7034</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L31" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1336000000000001</v>
+        <v>-0.1124</v>
       </c>
       <c r="N31" t="n">
-        <v>258</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2</v>
+        <v>-0.1389</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.063</v>
+        <v>-0.0437</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.6874</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2</v>
+        <v>-0.1389</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1455</v>
+        <v>0.5258</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0545</v>
+        <v>-0.6647</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1455</v>
+        <v>0.5258</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1515</v>
+        <v>0.5393</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0545</v>
+        <v>-0.6647</v>
       </c>
       <c r="K32" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="L32" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.206</v>
+        <v>-0.1254</v>
       </c>
       <c r="N32" t="n">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3666</v>
+        <v>-0.1632</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1154</v>
+        <v>-0.0514</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8035</v>
+        <v>-0.6985</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3666</v>
+        <v>-0.1632</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1892</v>
+        <v>-0.187</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1774</v>
+        <v>0.0238</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1892</v>
+        <v>-0.187</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.197</v>
+        <v>-0.1918</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1774</v>
+        <v>0.0238</v>
       </c>
       <c r="K33" t="n">
         <v>114</v>
@@ -1955,7 +1955,7 @@
         <v>126</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3744</v>
+        <v>-0.168</v>
       </c>
       <c r="N33" t="n">
         <v>240</v>
@@ -1964,124 +1964,124 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5577</v>
+        <v>-0.1799</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1756</v>
+        <v>-0.0566</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8898</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5577</v>
+        <v>-0.1799</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.5088</v>
+        <v>0.0286</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9510999999999999</v>
+        <v>-0.2085</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.5088</v>
+        <v>0.0286</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7845</v>
+        <v>0.0286</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9510999999999999</v>
+        <v>-0.2085</v>
       </c>
       <c r="K34" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="L34" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1666</v>
+        <v>-0.1799</v>
       </c>
       <c r="N34" t="n">
-        <v>220</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5659</v>
+        <v>-0.5703</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1781</v>
+        <v>-0.1795</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8935</v>
+        <v>-0.8838</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5659</v>
+        <v>-0.5703</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5659</v>
+        <v>-2.177</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.6067</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5659</v>
+        <v>-2.177</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5659</v>
+        <v>-2.2331</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1.6067</v>
       </c>
       <c r="K35" t="n">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5659</v>
+        <v>-0.6263999999999998</v>
       </c>
       <c r="N35" t="n">
-        <v>84</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5897</v>
+        <v>-0.6085</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1856</v>
+        <v>-0.1915</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9042</v>
+        <v>-0.9012</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5897</v>
+        <v>-0.6085</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5897</v>
+        <v>-0.6085</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5897</v>
+        <v>-0.6085</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5897</v>
+        <v>-0.6085</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5897</v>
+        <v>-0.6085</v>
       </c>
       <c r="N36" t="n">
         <v>84</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7287</v>
+        <v>-0.6288</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2294</v>
+        <v>-0.1979</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.967</v>
+        <v>-0.9104</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7287</v>
+        <v>-0.6288</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.1597</v>
+        <v>-0.6288</v>
       </c>
       <c r="G37" t="n">
-        <v>1.431</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.1597</v>
+        <v>-0.6288</v>
       </c>
       <c r="I37" t="n">
-        <v>-2.2485</v>
+        <v>-0.6288</v>
       </c>
       <c r="J37" t="n">
-        <v>1.431</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L37" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8174999999999999</v>
+        <v>-0.6288</v>
       </c>
       <c r="N37" t="n">
-        <v>258</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7304</v>
+        <v>-0.7588</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2299</v>
+        <v>-0.2389</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9678</v>
+        <v>-0.9696</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7304</v>
+        <v>-0.7588</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1415</v>
+        <v>-0.1439</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5889</v>
+        <v>-0.6149</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1415</v>
+        <v>-0.1439</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1415</v>
+        <v>-0.1439</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5889</v>
+        <v>-0.6149</v>
       </c>
       <c r="K38" t="n">
         <v>91</v>
@@ -2185,7 +2185,7 @@
         <v>42</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7303999999999999</v>
+        <v>-0.7588</v>
       </c>
       <c r="N38" t="n">
         <v>133</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.8165</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2451</v>
+        <v>-0.257</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9896</v>
+        <v>-0.9959</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.8165</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.8165</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.8165</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.8165</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.8165</v>
       </c>
       <c r="N39" t="n">
         <v>84</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.651</v>
+        <v>-1.6713</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5261</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3834</v>
+        <v>-1.385</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.651</v>
+        <v>-1.6713</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.651</v>
+        <v>-1.6713</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.651</v>
+        <v>-1.6713</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.651</v>
+        <v>-1.6713</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.651</v>
+        <v>-1.6713</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.8222</v>
+        <v>-2.8251</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8884</v>
+        <v>-0.8893</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9121</v>
+        <v>-1.9102</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.8222</v>
+        <v>-2.8251</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5912</v>
+        <v>-1.5956</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.231</v>
+        <v>-1.2295</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5912</v>
+        <v>-1.5956</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6566</v>
+        <v>-1.6367</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.231</v>
+        <v>-1.2295</v>
       </c>
       <c r="K41" t="n">
         <v>141</v>
@@ -2323,7 +2323,7 @@
         <v>117</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8876</v>
+        <v>-2.8662</v>
       </c>
       <c r="N41" t="n">
         <v>258</v>
@@ -2429,10 +2429,10 @@
         <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J2" t="n">
-        <v>29.8896</v>
+        <v>29.5248</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.79</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4116</v>
+        <v>1.5378</v>
       </c>
       <c r="J3" t="n">
-        <v>22.5856</v>
+        <v>24.6048</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.51</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0972</v>
+        <v>1.091</v>
       </c>
       <c r="J4" t="n">
-        <v>17.5552</v>
+        <v>17.456</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.23</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5526</v>
+        <v>0.5546</v>
       </c>
       <c r="J5" t="n">
-        <v>8.8416</v>
+        <v>8.8736</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2722</v>
+        <v>0.3013</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3552</v>
+        <v>4.8208</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2023</v>
+        <v>1.2014</v>
       </c>
       <c r="J7" t="n">
-        <v>19.2368</v>
+        <v>19.2224</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.61</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3734</v>
+        <v>-0.3919</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.9744</v>
+        <v>-6.2704</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.57</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4104</v>
+        <v>-0.4271</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.5664</v>
+        <v>-6.8336</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.37</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5984</v>
+        <v>-0.6024</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.574400000000001</v>
+        <v>-9.638400000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.7492</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.1376</v>
+        <v>-11.9872</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.28</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.7496</v>
       </c>
       <c r="J12" t="n">
-        <v>19.2216</v>
+        <v>17.9904</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3619</v>
+        <v>0.3574</v>
       </c>
       <c r="J13" t="n">
-        <v>8.685600000000001</v>
+        <v>8.5776</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1051</v>
+        <v>-0.1073</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.5224</v>
+        <v>-2.5752</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1421</v>
+        <v>-0.1437</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.4104</v>
+        <v>-3.4488</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3626</v>
+        <v>-0.3515</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.702400000000001</v>
+        <v>-8.436</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7977</v>
+        <v>0.7638</v>
       </c>
       <c r="J17" t="n">
-        <v>19.1448</v>
+        <v>18.3312</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4224</v>
+        <v>0.4218</v>
       </c>
       <c r="J18" t="n">
-        <v>10.1376</v>
+        <v>10.1232</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.194</v>
+        <v>0.2046</v>
       </c>
       <c r="J19" t="n">
-        <v>4.656</v>
+        <v>4.9104</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0588</v>
+        <v>0.0683</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4112</v>
+        <v>1.6392</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4708</v>
+        <v>-0.4761</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.2992</v>
+        <v>-11.4264</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7428</v>
+        <v>0.8184</v>
       </c>
       <c r="J22" t="n">
-        <v>17.0844</v>
+        <v>18.8232</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5633</v>
+        <v>0.622</v>
       </c>
       <c r="J23" t="n">
-        <v>12.9559</v>
+        <v>14.306</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4026</v>
+        <v>0.4392</v>
       </c>
       <c r="J24" t="n">
-        <v>9.2598</v>
+        <v>10.1016</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0286</v>
+        <v>-0.0196</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.4508</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6296</v>
+        <v>-0.5885</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.4808</v>
+        <v>-13.5355</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4928</v>
+        <v>0.5464</v>
       </c>
       <c r="J27" t="n">
-        <v>11.3344</v>
+        <v>12.5672</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1414</v>
+        <v>0.1494</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2522</v>
+        <v>3.4362</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0623</v>
+        <v>-0.0718</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.4329</v>
+        <v>-1.6514</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.122</v>
+        <v>-0.1346</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.806</v>
+        <v>-3.0958</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.74</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2968</v>
+        <v>-0.3095</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.8264</v>
+        <v>-7.1185</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.07</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1916</v>
+        <v>0.1883</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4488</v>
+        <v>3.3894</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.76</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2543</v>
+        <v>-0.2726</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.5774</v>
+        <v>-4.9068</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.76</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2543</v>
+        <v>-0.2726</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.5774</v>
+        <v>-4.9068</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2831</v>
+        <v>-0.3007</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.0958</v>
+        <v>-5.4126</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2926</v>
+        <v>-0.31</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.2668</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.92</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7345</v>
+        <v>0.8466</v>
       </c>
       <c r="J37" t="n">
-        <v>13.221</v>
+        <v>15.2388</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.53</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5804</v>
       </c>
       <c r="J38" t="n">
-        <v>9.081</v>
+        <v>10.4472</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.38</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4131</v>
+        <v>0.4717</v>
       </c>
       <c r="J39" t="n">
-        <v>7.4358</v>
+        <v>8.490600000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.37</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4069</v>
+        <v>0.464</v>
       </c>
       <c r="J40" t="n">
-        <v>7.3242</v>
+        <v>8.352</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3046</v>
+        <v>-0.31</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.4828</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.93</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3618</v>
+        <v>1.484</v>
       </c>
       <c r="J42" t="n">
-        <v>27.236</v>
+        <v>29.68</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.32</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6177</v>
+        <v>0.6887</v>
       </c>
       <c r="J43" t="n">
-        <v>12.354</v>
+        <v>13.774</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5532</v>
+        <v>0.6167</v>
       </c>
       <c r="J44" t="n">
-        <v>11.064</v>
+        <v>12.334</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.03</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0594</v>
+        <v>0.0866</v>
       </c>
       <c r="J45" t="n">
-        <v>1.188</v>
+        <v>1.732</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2071</v>
+        <v>-0.1891</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.142</v>
+        <v>-3.782</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5726</v>
+        <v>0.6352</v>
       </c>
       <c r="J47" t="n">
-        <v>11.452</v>
+        <v>12.704</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.32</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5316</v>
+        <v>0.5889</v>
       </c>
       <c r="J48" t="n">
-        <v>10.632</v>
+        <v>11.778</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.87</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.162</v>
+        <v>-0.1765</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.24</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3597</v>
+        <v>-0.3713</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.194</v>
+        <v>-7.426</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4522</v>
+        <v>-0.4598</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.044</v>
+        <v>-9.196</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.43</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7881</v>
+        <v>0.869</v>
       </c>
       <c r="J52" t="n">
-        <v>22.8549</v>
+        <v>25.201</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4141</v>
+        <v>0.455</v>
       </c>
       <c r="J53" t="n">
-        <v>12.0089</v>
+        <v>13.195</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3539</v>
+        <v>0.368</v>
       </c>
       <c r="J54" t="n">
-        <v>10.2631</v>
+        <v>10.672</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.226</v>
+        <v>0.2363</v>
       </c>
       <c r="J55" t="n">
-        <v>6.554</v>
+        <v>6.8527</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0852</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.6622</v>
+        <v>-2.4708</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6925</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>20.0825</v>
+        <v>22.2604</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2028</v>
+        <v>0.2055</v>
       </c>
       <c r="J58" t="n">
-        <v>5.8812</v>
+        <v>5.9595</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.72</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3086</v>
+        <v>-0.3224</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.949400000000001</v>
+        <v>-9.349600000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3182</v>
+        <v>-0.3317</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.2278</v>
+        <v>-9.619300000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3561</v>
+        <v>-0.3684</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.3269</v>
+        <v>-10.6836</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.306</v>
+        <v>0.3059</v>
       </c>
       <c r="J62" t="n">
-        <v>6.732</v>
+        <v>6.7298</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.04</v>
       </c>
       <c r="I63" t="n">
-        <v>0.109</v>
+        <v>0.1125</v>
       </c>
       <c r="J63" t="n">
-        <v>2.398</v>
+        <v>2.475</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0163</v>
+        <v>0.012</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3586</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3524</v>
+        <v>-0.3655</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.7528</v>
+        <v>-8.041</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3992</v>
+        <v>-0.4104</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.782400000000001</v>
+        <v>-9.0288</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.66</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6111</v>
+        <v>0.6992</v>
       </c>
       <c r="J67" t="n">
-        <v>13.4442</v>
+        <v>15.3824</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.27</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3543</v>
+        <v>0.3828</v>
       </c>
       <c r="J68" t="n">
-        <v>7.7946</v>
+        <v>8.4216</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.09</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1416</v>
+        <v>0.1586</v>
       </c>
       <c r="J69" t="n">
-        <v>3.1152</v>
+        <v>3.4892</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.064</v>
+        <v>0.0786</v>
       </c>
       <c r="J70" t="n">
-        <v>1.408</v>
+        <v>1.7292</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2765</v>
+        <v>-0.2859</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.083</v>
+        <v>-6.2898</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0428</v>
+        <v>1.1374</v>
       </c>
       <c r="J72" t="n">
-        <v>25.0272</v>
+        <v>27.2976</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.11</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3436</v>
+        <v>0.3504</v>
       </c>
       <c r="J73" t="n">
-        <v>8.2464</v>
+        <v>8.409599999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0203</v>
+        <v>-0.0139</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.4872</v>
+        <v>-0.3336</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3154</v>
+        <v>-0.3052</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.5696</v>
+        <v>-7.3248</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.621</v>
+        <v>-0.5824</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.904</v>
+        <v>-13.9776</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.53</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7326</v>
+        <v>0.8153</v>
       </c>
       <c r="J77" t="n">
-        <v>17.5824</v>
+        <v>19.5672</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1427</v>
+        <v>0.1503</v>
       </c>
       <c r="J78" t="n">
-        <v>3.4248</v>
+        <v>3.6072</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.217</v>
+        <v>-0.2309</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.208</v>
+        <v>-5.5416</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2767</v>
+        <v>-0.2899</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.6408</v>
+        <v>-6.9576</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2767</v>
+        <v>-0.2899</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.6408</v>
+        <v>-6.9576</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="J82" t="n">
-        <v>9.199999999999999</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.23</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3242</v>
+        <v>0.3407</v>
       </c>
       <c r="J83" t="n">
-        <v>7.4566</v>
+        <v>7.8361</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2387</v>
+        <v>0.255</v>
       </c>
       <c r="J84" t="n">
-        <v>5.4901</v>
+        <v>5.865</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.15</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2259</v>
+        <v>0.2423</v>
       </c>
       <c r="J85" t="n">
-        <v>5.1957</v>
+        <v>5.5729</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2825</v>
+        <v>-0.2925</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.4975</v>
+        <v>-6.7275</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.418</v>
+        <v>0.4606</v>
       </c>
       <c r="J87" t="n">
-        <v>9.614000000000001</v>
+        <v>10.5938</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0458</v>
+        <v>-0.055</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.0534</v>
+        <v>-1.265</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.95</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.6422</v>
+        <v>-1.8998</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1059</v>
+        <v>-0.1192</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.4357</v>
+        <v>-2.7416</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4324</v>
+        <v>-0.4412</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.9452</v>
+        <v>-10.1476</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.419</v>
+        <v>0.4471</v>
       </c>
       <c r="J92" t="n">
-        <v>7.961</v>
+        <v>8.494899999999999</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2047</v>
+        <v>-0.2237</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.8893</v>
+        <v>-4.2503</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.74</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2706</v>
+        <v>-0.2891</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.1414</v>
+        <v>-5.4929</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.67</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3369</v>
+        <v>-0.3534</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.4011</v>
+        <v>-6.7146</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.54</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4585</v>
+        <v>-0.4692</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.711499999999999</v>
+        <v>-8.9148</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.59</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9591</v>
+        <v>1.0588</v>
       </c>
       <c r="J97" t="n">
-        <v>18.2229</v>
+        <v>20.1172</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.42</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7471</v>
+        <v>0.8304</v>
       </c>
       <c r="J98" t="n">
-        <v>14.1949</v>
+        <v>15.7776</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.541</v>
+        <v>0.6028</v>
       </c>
       <c r="J99" t="n">
-        <v>10.279</v>
+        <v>11.4532</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3087</v>
+        <v>0.3211</v>
       </c>
       <c r="J100" t="n">
-        <v>5.8653</v>
+        <v>6.1009</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.08</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2229</v>
+        <v>0.2414</v>
       </c>
       <c r="J101" t="n">
-        <v>4.2351</v>
+        <v>4.5866</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.17</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3622</v>
+        <v>0.3809</v>
       </c>
       <c r="J102" t="n">
-        <v>8.3306</v>
+        <v>8.7607</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2454</v>
+        <v>0.2518</v>
       </c>
       <c r="J103" t="n">
-        <v>5.6442</v>
+        <v>5.7914</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2249</v>
+        <v>0.232</v>
       </c>
       <c r="J104" t="n">
-        <v>5.1727</v>
+        <v>5.336</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1457</v>
+        <v>-0.1586</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.3511</v>
+        <v>-3.6478</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2692</v>
+        <v>-0.2821</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.1916</v>
+        <v>-6.4883</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.93</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4078</v>
+        <v>1.5251</v>
       </c>
       <c r="J107" t="n">
-        <v>32.3794</v>
+        <v>35.0773</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6496</v>
+        <v>0.7195</v>
       </c>
       <c r="J108" t="n">
-        <v>14.9408</v>
+        <v>16.5485</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.25</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5982</v>
       </c>
       <c r="J109" t="n">
-        <v>12.4154</v>
+        <v>13.7586</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.71</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.8949</v>
+        <v>-0.8199</v>
       </c>
       <c r="J110" t="n">
-        <v>-20.5827</v>
+        <v>-18.8577</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.0154</v>
+        <v>-0.9247</v>
       </c>
       <c r="J111" t="n">
-        <v>-23.3542</v>
+        <v>-21.2681</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.3</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6187</v>
+        <v>0.6832</v>
       </c>
       <c r="J112" t="n">
-        <v>14.8488</v>
+        <v>16.3968</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5484</v>
+        <v>0.6056</v>
       </c>
       <c r="J113" t="n">
-        <v>13.1616</v>
+        <v>14.5344</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.12</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3569</v>
+        <v>0.3713</v>
       </c>
       <c r="J114" t="n">
-        <v>8.5656</v>
+        <v>8.911199999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.05</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1705</v>
+        <v>0.1821</v>
       </c>
       <c r="J115" t="n">
-        <v>4.092</v>
+        <v>4.3704</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.355</v>
+        <v>-0.3397</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.52</v>
+        <v>-8.152799999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.44</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6293</v>
+        <v>0.7033</v>
       </c>
       <c r="J117" t="n">
-        <v>15.1032</v>
+        <v>16.8792</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.571</v>
+        <v>0.6378</v>
       </c>
       <c r="J118" t="n">
-        <v>13.704</v>
+        <v>15.3072</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0606</v>
+        <v>0.0696</v>
       </c>
       <c r="J119" t="n">
-        <v>1.4544</v>
+        <v>1.6704</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.83</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2137</v>
+        <v>-0.2261</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.1288</v>
+        <v>-5.4264</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4787</v>
+        <v>-0.4837</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.4888</v>
+        <v>-11.6088</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.9</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3049</v>
+        <v>1.428</v>
       </c>
       <c r="J122" t="n">
-        <v>23.4882</v>
+        <v>25.704</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.81</v>
       </c>
       <c r="I123" t="n">
-        <v>1.2009</v>
+        <v>1.3188</v>
       </c>
       <c r="J123" t="n">
-        <v>21.6162</v>
+        <v>23.7384</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.57</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9175</v>
+        <v>1.0176</v>
       </c>
       <c r="J124" t="n">
-        <v>16.515</v>
+        <v>18.3168</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.5355</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.4976</v>
+        <v>-9.638999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7644</v>
+        <v>-0.6977</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.7592</v>
+        <v>-12.5586</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>0.99</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0459</v>
+        <v>0.0176</v>
       </c>
       <c r="J127" t="n">
-        <v>0.8262</v>
+        <v>0.3168</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.89</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1102</v>
+        <v>-0.1312</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.9836</v>
+        <v>-2.3616</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1553</v>
+        <v>-0.1764</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.7954</v>
+        <v>-3.1752</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.54</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4517</v>
+        <v>-0.4639</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.130599999999999</v>
+        <v>-8.350199999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.43</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5596</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.9702</v>
+        <v>-10.0728</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6764</v>
+        <v>1.6819</v>
       </c>
       <c r="J132" t="n">
-        <v>25.146</v>
+        <v>25.2285</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.58</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1877</v>
+        <v>1.1642</v>
       </c>
       <c r="J133" t="n">
-        <v>17.8155</v>
+        <v>17.463</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.57</v>
       </c>
       <c r="I134" t="n">
-        <v>1.176</v>
+        <v>1.1516</v>
       </c>
       <c r="J134" t="n">
-        <v>17.64</v>
+        <v>17.274</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.35</v>
       </c>
       <c r="I135" t="n">
-        <v>0.8497</v>
+        <v>0.8131</v>
       </c>
       <c r="J135" t="n">
-        <v>12.7455</v>
+        <v>12.1965</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3458</v>
+        <v>-0.3122</v>
       </c>
       <c r="J136" t="n">
-        <v>-5.187</v>
+        <v>-4.683</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1887</v>
+        <v>-0.2156</v>
       </c>
       <c r="J137" t="n">
-        <v>-2.8305</v>
+        <v>-3.234</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.73</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2528</v>
+        <v>-0.2774</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.792</v>
+        <v>-4.161</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.63</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.35</v>
+        <v>-0.3706</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.25</v>
+        <v>-5.559</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.52</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4496</v>
+        <v>-0.4652</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.744</v>
+        <v>-6.978</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5441</v>
+        <v>-0.5532</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.1615</v>
+        <v>-8.298</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2551</v>
+        <v>0.2613</v>
       </c>
       <c r="J142" t="n">
-        <v>7.3979</v>
+        <v>7.5777</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2248</v>
+        <v>0.232</v>
       </c>
       <c r="J143" t="n">
-        <v>6.5192</v>
+        <v>6.728</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.048</v>
+        <v>-0.0567</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.392</v>
+        <v>-1.6443</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1314</v>
+        <v>-0.1447</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.8106</v>
+        <v>-4.1963</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.74</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2949</v>
+        <v>-0.308</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.552099999999999</v>
+        <v>-8.932</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.29</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3977</v>
+        <v>0.4097</v>
       </c>
       <c r="J147" t="n">
-        <v>11.5333</v>
+        <v>11.8813</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.25</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3497</v>
+        <v>0.3636</v>
       </c>
       <c r="J148" t="n">
-        <v>10.1413</v>
+        <v>10.5444</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.14</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2126</v>
+        <v>0.2292</v>
       </c>
       <c r="J149" t="n">
-        <v>6.1654</v>
+        <v>6.6468</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.01</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0116</v>
+        <v>0.0208</v>
       </c>
       <c r="J150" t="n">
-        <v>0.3364</v>
+        <v>0.6032</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.98</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.0491</v>
+        <v>-0.0529</v>
       </c>
       <c r="J151" t="n">
-        <v>-1.4239</v>
+        <v>-1.5341</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.44</v>
       </c>
       <c r="I152" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J152" t="n">
-        <v>36.676</v>
+        <v>38.744</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.58</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2022</v>
+        <v>1.1769</v>
       </c>
       <c r="J153" t="n">
-        <v>24.044</v>
+        <v>23.538</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5226</v>
+        <v>0.5194</v>
       </c>
       <c r="J154" t="n">
-        <v>10.452</v>
+        <v>10.388</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3258</v>
+        <v>-0.2981</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.516</v>
+        <v>-5.962</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7655</v>
+        <v>-0.6985</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.31</v>
+        <v>-13.97</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7544</v>
+        <v>0.7104</v>
       </c>
       <c r="J157" t="n">
-        <v>15.088</v>
+        <v>14.208</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0618</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.236</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.93</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0866</v>
+        <v>-0.1012</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.732</v>
+        <v>-2.024</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.6</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4135</v>
+        <v>-0.4248</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.27</v>
+        <v>-8.496</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5054</v>
+        <v>-0.5119</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.108</v>
+        <v>-10.238</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.56</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2077</v>
+        <v>1.177</v>
       </c>
       <c r="J162" t="n">
-        <v>25.3617</v>
+        <v>24.717</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1448</v>
+        <v>1.1096</v>
       </c>
       <c r="J163" t="n">
-        <v>24.0408</v>
+        <v>23.3016</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9384</v>
+        <v>0.8834</v>
       </c>
       <c r="J164" t="n">
-        <v>19.7064</v>
+        <v>18.5514</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1744</v>
+        <v>0.1929</v>
       </c>
       <c r="J165" t="n">
-        <v>3.6624</v>
+        <v>4.0509</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.9331</v>
+        <v>-0.851</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.5951</v>
+        <v>-17.871</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.36</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7178</v>
+        <v>0.6888</v>
       </c>
       <c r="J167" t="n">
-        <v>15.0738</v>
+        <v>14.4648</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.04</v>
       </c>
       <c r="I168" t="n">
-        <v>0.115</v>
+        <v>0.1238</v>
       </c>
       <c r="J168" t="n">
-        <v>2.415</v>
+        <v>2.5998</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0638</v>
+        <v>-0.073</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.3398</v>
+        <v>-1.533</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.199</v>
+        <v>-0.2124</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.179</v>
+        <v>-4.4604</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.83</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2093</v>
+        <v>-0.2227</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.3953</v>
+        <v>-4.6767</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1347</v>
+        <v>1.0933</v>
       </c>
       <c r="J172" t="n">
-        <v>32.9063</v>
+        <v>31.7057</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.43</v>
       </c>
       <c r="I173" t="n">
-        <v>1.0686</v>
+        <v>1.0187</v>
       </c>
       <c r="J173" t="n">
-        <v>30.9894</v>
+        <v>29.5423</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.2</v>
       </c>
       <c r="I174" t="n">
-        <v>0.575</v>
+        <v>0.5553</v>
       </c>
       <c r="J174" t="n">
-        <v>16.675</v>
+        <v>16.1037</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.9</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3848</v>
+        <v>-0.367</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.1592</v>
+        <v>-10.643</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.0759</v>
+        <v>-0.9787</v>
       </c>
       <c r="J176" t="n">
-        <v>-31.2011</v>
+        <v>-28.3823</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.82</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2586</v>
+        <v>1.2421</v>
       </c>
       <c r="J177" t="n">
-        <v>36.4994</v>
+        <v>36.0209</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.06</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1554</v>
+        <v>0.1656</v>
       </c>
       <c r="J178" t="n">
-        <v>4.5066</v>
+        <v>4.8024</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.89</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1491</v>
+        <v>-0.1612</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.3239</v>
+        <v>-4.6748</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2329</v>
+        <v>-0.2455</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.7541</v>
+        <v>-7.1195</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.59</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4417</v>
+        <v>-0.4486</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.8093</v>
+        <v>-13.0094</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.43</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6506</v>
+        <v>0.6307</v>
       </c>
       <c r="J182" t="n">
-        <v>15.6144</v>
+        <v>15.1368</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0321</v>
+        <v>0.0363</v>
       </c>
       <c r="J183" t="n">
-        <v>0.7704</v>
+        <v>0.8712</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0856</v>
+        <v>-0.097</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.0544</v>
+        <v>-2.328</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2259</v>
+        <v>-0.2401</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.4216</v>
+        <v>-5.7624</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.68</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3522</v>
+        <v>-0.3636</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.4528</v>
+        <v>-8.7264</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.86</v>
       </c>
       <c r="I187" t="n">
-        <v>0.997</v>
+        <v>0.9751</v>
       </c>
       <c r="J187" t="n">
-        <v>23.928</v>
+        <v>23.4024</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.49</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6156</v>
+        <v>0.6172</v>
       </c>
       <c r="J188" t="n">
-        <v>14.7744</v>
+        <v>14.8128</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3186</v>
+        <v>0.335</v>
       </c>
       <c r="J189" t="n">
-        <v>7.6464</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2684</v>
+        <v>-0.2775</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.4416</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4814</v>
+        <v>-0.4844</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.5536</v>
+        <v>-11.6256</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.87</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5436</v>
+        <v>1.5387</v>
       </c>
       <c r="J192" t="n">
-        <v>23.154</v>
+        <v>23.0805</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.51</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1184</v>
+        <v>1.0865</v>
       </c>
       <c r="J193" t="n">
-        <v>16.776</v>
+        <v>16.2975</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.5</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1063</v>
+        <v>1.0732</v>
       </c>
       <c r="J194" t="n">
-        <v>16.5945</v>
+        <v>16.098</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.28</v>
       </c>
       <c r="I195" t="n">
-        <v>0.7137</v>
+        <v>0.6893</v>
       </c>
       <c r="J195" t="n">
-        <v>10.7055</v>
+        <v>10.3395</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8146</v>
+        <v>-0.7422</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.219</v>
+        <v>-11.133</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.04</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1543</v>
+        <v>0.1524</v>
       </c>
       <c r="J197" t="n">
-        <v>2.3145</v>
+        <v>2.286</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.93</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0866</v>
+        <v>-0.1012</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.299</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.9</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.121</v>
+        <v>-0.1368</v>
       </c>
       <c r="J199" t="n">
-        <v>-1.815</v>
+        <v>-2.052</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1626</v>
+        <v>-0.1795</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.439</v>
+        <v>-2.6925</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.59</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4227</v>
+        <v>-0.4336</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.3405</v>
+        <v>-6.504</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1331</v>
+        <v>1.0944</v>
       </c>
       <c r="J202" t="n">
-        <v>38.5254</v>
+        <v>37.2096</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9747</v>
+        <v>0.9157</v>
       </c>
       <c r="J203" t="n">
-        <v>33.1398</v>
+        <v>31.1338</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.466</v>
+        <v>0.4591</v>
       </c>
       <c r="J204" t="n">
-        <v>15.844</v>
+        <v>15.6094</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.96</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2125</v>
+        <v>-0.2022</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.225</v>
+        <v>-6.8748</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.92</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3399</v>
+        <v>-0.3223</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.5566</v>
+        <v>-10.9582</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.41</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8186</v>
+        <v>0.7766</v>
       </c>
       <c r="J207" t="n">
-        <v>27.8324</v>
+        <v>26.4044</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.96</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0606</v>
+        <v>-0.0706</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.0604</v>
+        <v>-2.4004</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1634</v>
+        <v>-0.1775</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.5556</v>
+        <v>-6.035</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.85</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1845</v>
+        <v>-0.1988</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.273</v>
+        <v>-6.7592</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.76</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.275</v>
+        <v>-0.2886</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.35</v>
+        <v>-9.8124</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5236</v>
+        <v>0.5131</v>
       </c>
       <c r="J212" t="n">
-        <v>12.5664</v>
+        <v>12.3144</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.15</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3405</v>
+        <v>0.3429</v>
       </c>
       <c r="J213" t="n">
-        <v>8.172000000000001</v>
+        <v>8.2296</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.13</v>
       </c>
       <c r="I214" t="n">
-        <v>0.302</v>
+        <v>0.3066</v>
       </c>
       <c r="J214" t="n">
-        <v>7.248</v>
+        <v>7.3584</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.07</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1802</v>
+        <v>0.1892</v>
       </c>
       <c r="J215" t="n">
-        <v>4.3248</v>
+        <v>4.5408</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.48</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5385</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.924</v>
+        <v>-12.9792</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.55</v>
       </c>
       <c r="I217" t="n">
-        <v>1.2272</v>
+        <v>1.1919</v>
       </c>
       <c r="J217" t="n">
-        <v>29.4528</v>
+        <v>28.6056</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.12</v>
       </c>
       <c r="I218" t="n">
-        <v>0.373</v>
+        <v>0.3715</v>
       </c>
       <c r="J218" t="n">
-        <v>8.952</v>
+        <v>8.916</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.05</v>
       </c>
       <c r="I219" t="n">
-        <v>0.171</v>
+        <v>0.1824</v>
       </c>
       <c r="J219" t="n">
-        <v>4.104</v>
+        <v>4.3776</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.05</v>
       </c>
       <c r="I220" t="n">
-        <v>0.171</v>
+        <v>0.1824</v>
       </c>
       <c r="J220" t="n">
-        <v>4.104</v>
+        <v>4.3776</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.85</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.4936</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.5688</v>
+        <v>-11.8464</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.19</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5364</v>
+        <v>0.5023</v>
       </c>
       <c r="J222" t="n">
-        <v>10.1916</v>
+        <v>9.543699999999999</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.77</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2401</v>
+        <v>-0.2596</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.5619</v>
+        <v>-4.9324</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.73</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2767</v>
+        <v>-0.2958</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.2573</v>
+        <v>-5.6202</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.63</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3707</v>
+        <v>-0.3865</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.0433</v>
+        <v>-7.3435</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.48</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5104</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.6976</v>
+        <v>-9.853400000000001</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.64</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2769</v>
+        <v>1.2562</v>
       </c>
       <c r="J227" t="n">
-        <v>24.2611</v>
+        <v>23.8678</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.56</v>
       </c>
       <c r="I228" t="n">
-        <v>1.1809</v>
+        <v>1.1534</v>
       </c>
       <c r="J228" t="n">
-        <v>22.4371</v>
+        <v>21.9146</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.28</v>
       </c>
       <c r="I229" t="n">
-        <v>0.716</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J229" t="n">
-        <v>13.604</v>
+        <v>13.129</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.26</v>
       </c>
       <c r="I230" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="J230" t="n">
-        <v>12.7281</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I231" t="n">
-        <v>0.3186</v>
+        <v>0.3339</v>
       </c>
       <c r="J231" t="n">
-        <v>6.0534</v>
+        <v>6.3441</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.74</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4527</v>
+        <v>1.4328</v>
       </c>
       <c r="J232" t="n">
-        <v>31.9594</v>
+        <v>31.5216</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.58</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2521</v>
+        <v>1.2209</v>
       </c>
       <c r="J233" t="n">
-        <v>27.5462</v>
+        <v>26.8598</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.95</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2423</v>
+        <v>-0.2316</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.3306</v>
+        <v>-5.0952</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6414</v>
+        <v>-0.5968</v>
       </c>
       <c r="J235" t="n">
-        <v>-14.1108</v>
+        <v>-13.1296</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7692</v>
+        <v>-0.7101</v>
       </c>
       <c r="J236" t="n">
-        <v>-16.9224</v>
+        <v>-15.6222</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4092</v>
+        <v>0.401</v>
       </c>
       <c r="J237" t="n">
-        <v>9.0024</v>
+        <v>8.821999999999999</v>
       </c>
     </row>
     <row r="238">
@@ -11909,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I239" t="n">
-        <v>0.204</v>
+        <v>0.2064</v>
       </c>
       <c r="J239" t="n">
-        <v>4.488</v>
+        <v>4.5408</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.86</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1687</v>
+        <v>-0.1841</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.7114</v>
+        <v>-4.0502</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.42</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5835</v>
+        <v>-0.5843</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.837</v>
+        <v>-12.8546</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1894</v>
+        <v>1.1538</v>
       </c>
       <c r="J242" t="n">
-        <v>33.3032</v>
+        <v>32.3064</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.8042</v>
+        <v>0.7604</v>
       </c>
       <c r="J243" t="n">
-        <v>22.5176</v>
+        <v>21.2912</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1282</v>
+        <v>0.144</v>
       </c>
       <c r="J244" t="n">
-        <v>3.5896</v>
+        <v>4.032</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1282</v>
+        <v>0.144</v>
       </c>
       <c r="J245" t="n">
-        <v>3.5896</v>
+        <v>4.032</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.91</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3651</v>
+        <v>-0.3467</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.2228</v>
+        <v>-9.707599999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I247" t="n">
-        <v>0.374</v>
+        <v>0.3674</v>
       </c>
       <c r="J247" t="n">
-        <v>10.472</v>
+        <v>10.2872</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2073</v>
+        <v>0.2088</v>
       </c>
       <c r="J248" t="n">
-        <v>5.8044</v>
+        <v>5.8464</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.98</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.028</v>
+        <v>-0.0367</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.784</v>
+        <v>-1.0276</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2286</v>
+        <v>-0.2443</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.4008</v>
+        <v>-6.8404</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4473</v>
+        <v>-0.456</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.5244</v>
+        <v>-12.768</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.96</v>
       </c>
       <c r="I252" t="n">
-        <v>1.679</v>
+        <v>1.6754</v>
       </c>
       <c r="J252" t="n">
-        <v>31.901</v>
+        <v>31.8326</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.61</v>
       </c>
       <c r="I253" t="n">
-        <v>1.2606</v>
+        <v>1.2351</v>
       </c>
       <c r="J253" t="n">
-        <v>23.9514</v>
+        <v>23.4669</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.14</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3937</v>
+        <v>0.3979</v>
       </c>
       <c r="J254" t="n">
-        <v>7.4803</v>
+        <v>7.5601</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.96</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.236</v>
+        <v>-0.2187</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.484</v>
+        <v>-4.1553</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.72</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8924</v>
+        <v>-0.8141</v>
       </c>
       <c r="J256" t="n">
-        <v>-16.9556</v>
+        <v>-15.4679</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.99</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0192</v>
+        <v>-0.0012</v>
       </c>
       <c r="J257" t="n">
-        <v>0.3648</v>
+        <v>-0.0228</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0985</v>
+        <v>-0.1165</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.8715</v>
+        <v>-2.2135</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1327</v>
+        <v>-0.1514</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.5213</v>
+        <v>-2.8766</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.73</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2812</v>
+        <v>-0.2992</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.3428</v>
+        <v>-5.6848</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5334</v>
+        <v>-0.5394</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.1346</v>
+        <v>-10.2486</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.56</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2351</v>
+        <v>1.2012</v>
       </c>
       <c r="J262" t="n">
-        <v>27.1722</v>
+        <v>26.4264</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.25</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6934</v>
+        <v>0.6614</v>
       </c>
       <c r="J263" t="n">
-        <v>15.2548</v>
+        <v>14.5508</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.02</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0625</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="J264" t="n">
-        <v>1.375</v>
+        <v>1.7204</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2672</v>
+        <v>-0.2569</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.8784</v>
+        <v>-5.6518</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.93</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2984</v>
+        <v>-0.2863</v>
       </c>
       <c r="J266" t="n">
-        <v>-6.5648</v>
+        <v>-6.2986</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4036</v>
+        <v>0.3931</v>
       </c>
       <c r="J267" t="n">
-        <v>8.879200000000001</v>
+        <v>8.648199999999999</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.93</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.09</v>
+        <v>-0.1039</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.98</v>
+        <v>-2.2858</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.88</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1443</v>
+        <v>-0.1602</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.1746</v>
+        <v>-3.5244</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2256</v>
+        <v>-0.242</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.9632</v>
+        <v>-5.324</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3419</v>
+        <v>-0.3556</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.5218</v>
+        <v>-7.8232</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.79</v>
       </c>
       <c r="I272" t="n">
-        <v>1.5542</v>
+        <v>1.5331</v>
       </c>
       <c r="J272" t="n">
-        <v>37.3008</v>
+        <v>36.7944</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.93</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.2799</v>
+        <v>-0.2734</v>
       </c>
       <c r="J273" t="n">
-        <v>-6.7176</v>
+        <v>-6.5616</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2799</v>
+        <v>-0.2734</v>
       </c>
       <c r="J274" t="n">
-        <v>-6.7176</v>
+        <v>-6.5616</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3982</v>
+        <v>-0.3827</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.556800000000001</v>
+        <v>-9.184799999999999</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5897</v>
+        <v>-0.5555</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.1528</v>
+        <v>-13.332</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.45</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8475</v>
+        <v>0.8081</v>
       </c>
       <c r="J277" t="n">
-        <v>20.34</v>
+        <v>19.3944</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.45</v>
       </c>
       <c r="I278" t="n">
-        <v>0.8475</v>
+        <v>0.8081</v>
       </c>
       <c r="J278" t="n">
-        <v>20.34</v>
+        <v>19.3944</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.96</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0687</v>
+        <v>-0.0767</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.6488</v>
+        <v>-1.8408</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.304</v>
+        <v>-0.3151</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.296</v>
+        <v>-7.5624</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3702</v>
+        <v>-0.3795</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.8848</v>
+        <v>-9.108000000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.18</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3175</v>
+        <v>0.3203</v>
       </c>
       <c r="J282" t="n">
-        <v>6.985</v>
+        <v>7.0466</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2734</v>
+        <v>0.2782</v>
       </c>
       <c r="J283" t="n">
-        <v>6.0148</v>
+        <v>6.1204</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0601</v>
+        <v>-0.0701</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.3222</v>
+        <v>-1.5422</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.93</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.096</v>
+        <v>-0.1084</v>
       </c>
       <c r="J285" t="n">
-        <v>-2.112</v>
+        <v>-2.3848</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.58</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4433</v>
+        <v>-0.4513</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.752599999999999</v>
+        <v>-9.928599999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.71</v>
       </c>
       <c r="I287" t="n">
-        <v>0.848</v>
+        <v>0.8325</v>
       </c>
       <c r="J287" t="n">
-        <v>18.656</v>
+        <v>18.315</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>0.6232</v>
+        <v>0.6248</v>
       </c>
       <c r="J288" t="n">
-        <v>13.7104</v>
+        <v>13.7456</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.14</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2065</v>
+        <v>0.2247</v>
       </c>
       <c r="J289" t="n">
-        <v>4.543</v>
+        <v>4.9434</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.85</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2092</v>
+        <v>-0.2181</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.6024</v>
+        <v>-4.7982</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.25</v>
+        <v>-0.259</v>
       </c>
       <c r="J291" t="n">
-        <v>-5.5</v>
+        <v>-5.698</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.44</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1056</v>
+        <v>1.0569</v>
       </c>
       <c r="J292" t="n">
-        <v>24.3232</v>
+        <v>23.2518</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.2</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5729</v>
       </c>
       <c r="J293" t="n">
-        <v>13.2066</v>
+        <v>12.6038</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.04</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1547</v>
+        <v>0.1622</v>
       </c>
       <c r="J294" t="n">
-        <v>3.4034</v>
+        <v>3.5684</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.6098</v>
+        <v>-0.5746</v>
       </c>
       <c r="J295" t="n">
-        <v>-13.4156</v>
+        <v>-12.6412</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.76</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.6884</v>
       </c>
       <c r="J296" t="n">
-        <v>-16.2448</v>
+        <v>-15.1448</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.42</v>
       </c>
       <c r="I297" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.7691</v>
       </c>
       <c r="J297" t="n">
-        <v>17.7078</v>
+        <v>16.9202</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.12</v>
       </c>
       <c r="I298" t="n">
-        <v>0.2773</v>
+        <v>0.2842</v>
       </c>
       <c r="J298" t="n">
-        <v>6.1006</v>
+        <v>6.2524</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2378</v>
+        <v>0.2463</v>
       </c>
       <c r="J299" t="n">
-        <v>5.2316</v>
+        <v>5.4186</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.97</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0537</v>
+        <v>-0.061</v>
       </c>
       <c r="J300" t="n">
-        <v>-1.1814</v>
+        <v>-1.342</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.58</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4512</v>
+        <v>-0.4576</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.926399999999999</v>
+        <v>-10.0672</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.67</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3261</v>
+        <v>1.3061</v>
       </c>
       <c r="J302" t="n">
-        <v>25.1959</v>
+        <v>24.8159</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1306</v>
+        <v>1.0972</v>
       </c>
       <c r="J303" t="n">
-        <v>21.4814</v>
+        <v>20.8468</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.44</v>
       </c>
       <c r="I304" t="n">
-        <v>1.0421</v>
+        <v>0.996</v>
       </c>
       <c r="J304" t="n">
-        <v>19.7999</v>
+        <v>18.924</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.99</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.13</v>
+        <v>-0.112</v>
       </c>
       <c r="J305" t="n">
-        <v>-2.47</v>
+        <v>-2.128</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3089</v>
+        <v>-0.2862</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.8691</v>
+        <v>-5.4378</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.44</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9203</v>
+        <v>0.8602</v>
       </c>
       <c r="J307" t="n">
-        <v>17.4857</v>
+        <v>16.3438</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2144</v>
+        <v>-0.2312</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.0736</v>
+        <v>-4.3928</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.75</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2735</v>
+        <v>-0.2893</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.1965</v>
+        <v>-5.4967</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.71</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.312</v>
+        <v>-0.3269</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.928</v>
+        <v>-6.2111</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3311</v>
+        <v>-0.3454</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.2909</v>
+        <v>-6.5626</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.43</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0572</v>
+        <v>1.0075</v>
       </c>
       <c r="J312" t="n">
-        <v>23.2584</v>
+        <v>22.165</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.33</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8711</v>
+        <v>0.8193</v>
       </c>
       <c r="J313" t="n">
-        <v>19.1642</v>
+        <v>18.0246</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3907</v>
+        <v>0.3899</v>
       </c>
       <c r="J314" t="n">
-        <v>8.5954</v>
+        <v>8.5778</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.06</v>
       </c>
       <c r="I315" t="n">
-        <v>0.191</v>
+        <v>0.2044</v>
       </c>
       <c r="J315" t="n">
-        <v>4.202</v>
+        <v>4.4968</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3671</v>
+        <v>-0.3482</v>
       </c>
       <c r="J316" t="n">
-        <v>-8.0762</v>
+        <v>-7.6604</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.07</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2163</v>
+        <v>0.2154</v>
       </c>
       <c r="J317" t="n">
-        <v>4.7586</v>
+        <v>4.7388</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.04</v>
       </c>
       <c r="I318" t="n">
-        <v>0.1457</v>
+        <v>0.1461</v>
       </c>
       <c r="J318" t="n">
-        <v>3.2054</v>
+        <v>3.2142</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.84</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1852</v>
+        <v>-0.2017</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.0744</v>
+        <v>-4.4374</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.82</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2054</v>
+        <v>-0.2219</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.5188</v>
+        <v>-4.8818</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.67</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3511</v>
+        <v>-0.3645</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.7242</v>
+        <v>-8.019</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6975/event_6975_evp_summary.xlsx
+++ b/database/event/6975/event_6975_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.4653</v>
+        <v>6.8065</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0352</v>
+        <v>2.1426</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3189</v>
+        <v>2.4265</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4653</v>
+        <v>6.8065</v>
       </c>
       <c r="F2" t="n">
         <v>3.8891</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0957</v>
+        <v>6.496</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9189</v>
+        <v>2.0449</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1507</v>
+        <v>2.2878</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0957</v>
+        <v>6.496</v>
       </c>
       <c r="F3" t="n">
         <v>3.2228</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7188</v>
+        <v>5.954</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8002</v>
+        <v>1.8743</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9791</v>
+        <v>2.0457</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7188</v>
+        <v>5.954</v>
       </c>
       <c r="F4" t="n">
         <v>3.1305</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4655</v>
+        <v>5.4963</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7205</v>
+        <v>1.7302</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8638</v>
+        <v>1.8413</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4655</v>
+        <v>5.4963</v>
       </c>
       <c r="F5" t="n">
         <v>3.4931</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.976</v>
+        <v>5.3618</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5664</v>
+        <v>1.6878</v>
       </c>
       <c r="D6" t="n">
-        <v>1.641</v>
+        <v>1.7812</v>
       </c>
       <c r="E6" t="n">
-        <v>4.976</v>
+        <v>5.3618</v>
       </c>
       <c r="F6" t="n">
         <v>1.2953</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7994</v>
+        <v>4.8332</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5108</v>
+        <v>1.5214</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5606</v>
+        <v>1.5451</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7994</v>
+        <v>4.8332</v>
       </c>
       <c r="F7" t="n">
         <v>3.3437</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9957</v>
+        <v>4.1896</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2578</v>
+        <v>1.3188</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1947</v>
+        <v>1.2576</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9957</v>
+        <v>4.1896</v>
       </c>
       <c r="F8" t="n">
         <v>3.0138</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4596</v>
+        <v>3.4935</v>
       </c>
       <c r="C9" t="n">
-        <v>1.089</v>
+        <v>1.0997</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9507</v>
+        <v>0.9466</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4596</v>
+        <v>3.4935</v>
       </c>
       <c r="F9" t="n">
         <v>2.6712</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6105</v>
+        <v>2.609</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8218</v>
+        <v>0.8213</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5641</v>
+        <v>0.5516</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6105</v>
+        <v>2.609</v>
       </c>
       <c r="F10" t="n">
         <v>0.2378</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5648</v>
+        <v>2.5307</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8074</v>
+        <v>0.7966</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5433</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5648</v>
+        <v>2.5307</v>
       </c>
       <c r="F11" t="n">
         <v>-0.0549</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.474</v>
+        <v>2.462</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7788</v>
+        <v>0.775</v>
       </c>
       <c r="D12" t="n">
-        <v>0.502</v>
+        <v>0.4859</v>
       </c>
       <c r="E12" t="n">
-        <v>2.474</v>
+        <v>2.462</v>
       </c>
       <c r="F12" t="n">
         <v>2.62</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2827</v>
+        <v>2.3819</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7186</v>
+        <v>0.7498</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4149</v>
+        <v>0.4501</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2827</v>
+        <v>2.3819</v>
       </c>
       <c r="F13" t="n">
         <v>1.1536</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0057</v>
+        <v>2.1232</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6314</v>
+        <v>0.6684</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2888</v>
+        <v>0.3346</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0057</v>
+        <v>2.1232</v>
       </c>
       <c r="F14" t="n">
         <v>2.3989</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9978</v>
+        <v>1.8971</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6289</v>
+        <v>0.5972</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2852</v>
+        <v>0.2336</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9978</v>
+        <v>1.8971</v>
       </c>
       <c r="F15" t="n">
         <v>2.3706</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.859</v>
+        <v>1.8611</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5859</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2221</v>
+        <v>0.2175</v>
       </c>
       <c r="E16" t="n">
-        <v>1.859</v>
+        <v>1.8611</v>
       </c>
       <c r="F16" t="n">
         <v>2.2533</v>
@@ -1182,461 +1182,461 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3023</v>
+        <v>1.5928</v>
       </c>
       <c r="C17" t="n">
-        <v>0.41</v>
+        <v>0.5014</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0314</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3023</v>
+        <v>1.5928</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9335</v>
+        <v>1.2598</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3688</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9335</v>
+        <v>1.2598</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9576</v>
+        <v>1.2598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3688</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L17" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3264</v>
+        <v>1.2598</v>
       </c>
       <c r="N17" t="n">
-        <v>176</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2617</v>
+        <v>1.3979</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3972</v>
+        <v>0.44</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0499</v>
+        <v>0.0106</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2617</v>
+        <v>1.3979</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2617</v>
+        <v>0.9335</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.3688</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2617</v>
+        <v>0.9335</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2617</v>
+        <v>0.9576</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.3688</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2617</v>
+        <v>1.3264</v>
       </c>
       <c r="N18" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2598</v>
+        <v>1.3367</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3966</v>
+        <v>0.4208</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0507</v>
+        <v>-0.0167</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2598</v>
+        <v>1.3367</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2598</v>
+        <v>1.2617</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2598</v>
+        <v>1.2617</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2598</v>
+        <v>1.2617</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2598</v>
+        <v>1.2617</v>
       </c>
       <c r="N19" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8202</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2718</v>
+        <v>0.2582</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2312</v>
+        <v>-0.2475</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8202</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0641</v>
+        <v>0.7024</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2007</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0641</v>
+        <v>0.7024</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0915</v>
+        <v>0.7024</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2007</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8907999999999999</v>
+        <v>0.7024</v>
       </c>
       <c r="N20" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.827</v>
+        <v>0.6785</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2603</v>
+        <v>0.2136</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2477</v>
+        <v>-0.3107</v>
       </c>
       <c r="E21" t="n">
-        <v>0.827</v>
+        <v>0.6785</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2169</v>
+        <v>0.3451</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3899</v>
+        <v>0.1437</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2169</v>
+        <v>0.3451</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6571</v>
+        <v>0.3451</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3899</v>
+        <v>0.1437</v>
       </c>
       <c r="K21" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="L21" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2672</v>
+        <v>0.4888</v>
       </c>
       <c r="N21" t="n">
-        <v>220</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7538</v>
+        <v>0.6675</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2373</v>
+        <v>0.2101</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2811</v>
+        <v>-0.3157</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7538</v>
+        <v>0.6675</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8298</v>
+        <v>1.0641</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.076</v>
+        <v>-0.2007</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8298</v>
+        <v>1.0641</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4481</v>
+        <v>1.0915</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.076</v>
+        <v>-0.2007</v>
       </c>
       <c r="K22" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L22" t="n">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3721</v>
+        <v>0.8907999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>215</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7024</v>
+        <v>0.5787</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2211</v>
+        <v>0.1822</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3045</v>
+        <v>-0.3553</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7024</v>
+        <v>0.5787</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7024</v>
+        <v>1.2169</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.3899</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7024</v>
+        <v>1.2169</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7024</v>
+        <v>0.6571</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.3899</v>
       </c>
       <c r="K23" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7024</v>
+        <v>0.2672</v>
       </c>
       <c r="N23" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.518</v>
+        <v>0.5258</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1631</v>
+        <v>0.1655</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3884</v>
+        <v>-0.379</v>
       </c>
       <c r="E24" t="n">
-        <v>0.518</v>
+        <v>0.5258</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4172</v>
+        <v>0.4054</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1008</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4172</v>
+        <v>0.4054</v>
       </c>
       <c r="I24" t="n">
-        <v>0.428</v>
+        <v>0.4054</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1008</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5287999999999999</v>
+        <v>0.4054</v>
       </c>
       <c r="N24" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4888</v>
+        <v>0.5064</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1539</v>
+        <v>0.1594</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4017</v>
+        <v>-0.3876</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4888</v>
+        <v>0.5064</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3451</v>
+        <v>0.8298</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1437</v>
+        <v>-0.076</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3451</v>
+        <v>0.8298</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3451</v>
+        <v>0.4481</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1437</v>
+        <v>-0.076</v>
       </c>
       <c r="K25" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="L25" t="n">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4888</v>
+        <v>0.3721</v>
       </c>
       <c r="N25" t="n">
-        <v>133</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4054</v>
+        <v>0.3933</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1276</v>
+        <v>0.1238</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4397</v>
+        <v>-0.4381</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4054</v>
+        <v>0.3933</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4054</v>
+        <v>0.4172</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.1008</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4054</v>
+        <v>0.4172</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4054</v>
+        <v>0.428</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.1008</v>
       </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4054</v>
+        <v>0.5287999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
@@ -1646,16 +1646,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2355</v>
+        <v>0.3154</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0741</v>
+        <v>0.0993</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.517</v>
+        <v>-0.4729</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2355</v>
+        <v>0.3154</v>
       </c>
       <c r="F27" t="n">
         <v>-0.2259</v>
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1459</v>
+        <v>0.1474</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0459</v>
+        <v>0.0464</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5578</v>
+        <v>-0.548</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1459</v>
+        <v>0.1474</v>
       </c>
       <c r="F28" t="n">
         <v>0.1459</v>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0112</v>
+        <v>0.0218</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0035</v>
+        <v>0.0069</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6293</v>
+        <v>-0.6041</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0112</v>
+        <v>0.0218</v>
       </c>
       <c r="F29" t="n">
         <v>-0.1487</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0757</v>
+        <v>-0.0576</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0238</v>
+        <v>-0.0181</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6587</v>
+        <v>-0.6395</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0757</v>
+        <v>-0.0576</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.2471</v>
+        <v>-0.1124</v>
       </c>
       <c r="G30" t="n">
-        <v>1.1714</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.2471</v>
+        <v>-0.1124</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6734</v>
+        <v>-0.1124</v>
       </c>
       <c r="J30" t="n">
-        <v>1.1714</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L30" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.498</v>
+        <v>-0.1124</v>
       </c>
       <c r="N30" t="n">
-        <v>220</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1124</v>
+        <v>-0.2204</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0354</v>
+        <v>-0.0694</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6754</v>
+        <v>-0.7123</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1124</v>
+        <v>-0.2204</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1124</v>
+        <v>0.5258</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.6647</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1124</v>
+        <v>0.5258</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1124</v>
+        <v>0.5393</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.6647</v>
       </c>
       <c r="K31" t="n">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1124</v>
+        <v>-0.1254</v>
       </c>
       <c r="N31" t="n">
-        <v>84</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1389</v>
+        <v>-0.2417</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0437</v>
+        <v>-0.0761</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6874</v>
+        <v>-0.7218</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1389</v>
+        <v>-0.2417</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5258</v>
+        <v>-1.2471</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6647</v>
+        <v>1.1714</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5258</v>
+        <v>-1.2471</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5393</v>
+        <v>-0.6734</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6647</v>
+        <v>1.1714</v>
       </c>
       <c r="K32" t="n">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="L32" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1254</v>
+        <v>0.498</v>
       </c>
       <c r="N32" t="n">
-        <v>258</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1632</v>
+        <v>-0.2926</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0514</v>
+        <v>-0.0921</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6985</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1632</v>
+        <v>-0.2926</v>
       </c>
       <c r="F33" t="n">
         <v>-0.187</v>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1799</v>
+        <v>-0.3639</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0566</v>
+        <v>-0.1146</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7764</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1799</v>
+        <v>-0.3639</v>
       </c>
       <c r="F34" t="n">
         <v>0.0286</v>
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5703</v>
+        <v>-0.7318</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1795</v>
+        <v>-0.2304</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8838</v>
+        <v>-0.9407</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5703</v>
+        <v>-0.7318</v>
       </c>
       <c r="F35" t="n">
         <v>-2.177</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6085</v>
+        <v>-0.74</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1915</v>
+        <v>-0.2329</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9012</v>
+        <v>-0.9444</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6085</v>
+        <v>-0.74</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6085</v>
+        <v>-0.6288</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6085</v>
+        <v>-0.6288</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6085</v>
+        <v>-0.6288</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6085</v>
+        <v>-0.6288</v>
       </c>
       <c r="N36" t="n">
         <v>84</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6288</v>
+        <v>-0.7972</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1979</v>
+        <v>-0.2509</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9104</v>
+        <v>-0.9699</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6288</v>
+        <v>-0.7972</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6288</v>
+        <v>-0.8165</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6288</v>
+        <v>-0.8165</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6288</v>
+        <v>-0.8165</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6288</v>
+        <v>-0.8165</v>
       </c>
       <c r="N37" t="n">
         <v>84</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7588</v>
+        <v>-0.8318</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2389</v>
+        <v>-0.2618</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9696</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7588</v>
+        <v>-0.8318</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1439</v>
+        <v>-0.6085</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.6149</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1439</v>
+        <v>-0.6085</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1439</v>
+        <v>-0.6085</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6149</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L38" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7588</v>
+        <v>-0.6085</v>
       </c>
       <c r="N38" t="n">
-        <v>133</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8165</v>
+        <v>-0.9187</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.257</v>
+        <v>-0.2892</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9959</v>
+        <v>-1.0242</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8165</v>
+        <v>-0.9187</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8165</v>
+        <v>-0.1439</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.6149</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8165</v>
+        <v>-0.1439</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8165</v>
+        <v>-0.1439</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.6149</v>
       </c>
       <c r="K39" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.8165</v>
+        <v>-0.7588</v>
       </c>
       <c r="N39" t="n">
-        <v>84</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40">
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6713</v>
+        <v>-2.2325</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5261</v>
+        <v>-0.7028</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.385</v>
+        <v>-1.611</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6713</v>
+        <v>-2.2325</v>
       </c>
       <c r="F40" t="n">
         <v>-1.6713</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.8251</v>
+        <v>-3.0762</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8893</v>
+        <v>-0.9684</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9102</v>
+        <v>-1.9879</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.8251</v>
+        <v>-3.0762</v>
       </c>
       <c r="F41" t="n">
         <v>-1.5956</v>

--- a/database/event/6975/event_6975_evp_summary.xlsx
+++ b/database/event/6975/event_6975_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8065</v>
+        <v>6.5735</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1426</v>
+        <v>2.0693</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4265</v>
+        <v>2.3888</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8065</v>
+        <v>6.5735</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8891</v>
+        <v>3.7865</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5762</v>
+        <v>2.4458</v>
       </c>
       <c r="H2" t="n">
-        <v>7.9374</v>
+        <v>7.7737</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2861</v>
+        <v>4.3647</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5762</v>
+        <v>2.4458</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -529,7 +529,7 @@
         <v>115</v>
       </c>
       <c r="M2" t="n">
-        <v>6.8623</v>
+        <v>6.8105</v>
       </c>
       <c r="N2" t="n">
         <v>220</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.496</v>
+        <v>6.3204</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0449</v>
+        <v>1.9896</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2878</v>
+        <v>2.2735</v>
       </c>
       <c r="E3" t="n">
-        <v>6.496</v>
+        <v>6.3204</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2228</v>
+        <v>3.1499</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8729</v>
+        <v>2.7701</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3288</v>
+        <v>4.2686</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4404</v>
+        <v>4.3827</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8729</v>
+        <v>2.7701</v>
       </c>
       <c r="K3" t="n">
         <v>141</v>
@@ -575,7 +575,7 @@
         <v>117</v>
       </c>
       <c r="M3" t="n">
-        <v>7.3133</v>
+        <v>7.152799999999999</v>
       </c>
       <c r="N3" t="n">
         <v>258</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.954</v>
+        <v>5.927</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8743</v>
+        <v>1.8658</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0457</v>
+        <v>2.0942</v>
       </c>
       <c r="E4" t="n">
-        <v>5.954</v>
+        <v>5.927</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1305</v>
+        <v>3.1514</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5883</v>
+        <v>2.5404</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4343</v>
+        <v>5.3891</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9345</v>
+        <v>3.0258</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5883</v>
+        <v>2.5404</v>
       </c>
       <c r="K4" t="n">
         <v>105</v>
@@ -621,7 +621,7 @@
         <v>115</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5228</v>
+        <v>5.5662</v>
       </c>
       <c r="N4" t="n">
         <v>220</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4963</v>
+        <v>5.586</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7302</v>
+        <v>1.7584</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8413</v>
+        <v>1.9389</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4963</v>
+        <v>5.586</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4931</v>
+        <v>3.4496</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9724</v>
+        <v>2.1056</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6308</v>
+        <v>6.5088</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5806</v>
+        <v>3.6545</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9724</v>
+        <v>2.1056</v>
       </c>
       <c r="K5" t="n">
         <v>105</v>
@@ -667,7 +667,7 @@
         <v>115</v>
       </c>
       <c r="M5" t="n">
-        <v>5.553</v>
+        <v>5.7601</v>
       </c>
       <c r="N5" t="n">
         <v>220</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3618</v>
+        <v>5.2695</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6878</v>
+        <v>1.6588</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7812</v>
+        <v>1.7947</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3618</v>
+        <v>5.2695</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2953</v>
+        <v>1.2458</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6807</v>
+        <v>3.6379</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2953</v>
+        <v>1.2458</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3287</v>
+        <v>1.2791</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6807</v>
+        <v>3.6379</v>
       </c>
       <c r="K6" t="n">
         <v>114</v>
@@ -713,7 +713,7 @@
         <v>126</v>
       </c>
       <c r="M6" t="n">
-        <v>5.009399999999999</v>
+        <v>4.917</v>
       </c>
       <c r="N6" t="n">
         <v>240</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8332</v>
+        <v>4.7899</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5214</v>
+        <v>1.5078</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5451</v>
+        <v>1.5762</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8332</v>
+        <v>4.7899</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3437</v>
+        <v>3.3014</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4557</v>
+        <v>1.4547</v>
       </c>
       <c r="H7" t="n">
-        <v>6.1381</v>
+        <v>5.9522</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3145</v>
+        <v>3.342</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4557</v>
+        <v>1.4547</v>
       </c>
       <c r="K7" t="n">
         <v>114</v>
@@ -759,7 +759,7 @@
         <v>101</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7702</v>
+        <v>4.7967</v>
       </c>
       <c r="N7" t="n">
         <v>215</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1896</v>
+        <v>4.1401</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3188</v>
+        <v>1.3033</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2576</v>
+        <v>1.2802</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1896</v>
+        <v>4.1401</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0138</v>
+        <v>3.0389</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9819</v>
+        <v>0.9073</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0493</v>
+        <v>4.9666</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7266</v>
+        <v>2.7886</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9819</v>
+        <v>0.9073</v>
       </c>
       <c r="K8" t="n">
         <v>114</v>
@@ -805,7 +805,7 @@
         <v>101</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7085</v>
+        <v>3.6959</v>
       </c>
       <c r="N8" t="n">
         <v>215</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4935</v>
+        <v>3.7096</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0997</v>
+        <v>1.1677</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9466</v>
+        <v>1.0841</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4935</v>
+        <v>3.7096</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6712</v>
+        <v>2.7774</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7884</v>
+        <v>0.8983</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9189</v>
+        <v>3.9849</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1162</v>
+        <v>2.2374</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7884</v>
+        <v>0.8983</v>
       </c>
       <c r="K9" t="n">
         <v>114</v>
@@ -851,7 +851,7 @@
         <v>101</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9046</v>
+        <v>3.1357</v>
       </c>
       <c r="N9" t="n">
         <v>215</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.609</v>
+        <v>2.688</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8213</v>
+        <v>0.8462</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5516</v>
+        <v>0.6187</v>
       </c>
       <c r="E10" t="n">
-        <v>2.609</v>
+        <v>2.688</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2378</v>
+        <v>0.3313</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3728</v>
+        <v>2.3582</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2378</v>
+        <v>0.3313</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2439</v>
+        <v>0.3402</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3728</v>
+        <v>2.3582</v>
       </c>
       <c r="K10" t="n">
         <v>114</v>
@@ -897,7 +897,7 @@
         <v>126</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6167</v>
+        <v>2.6984</v>
       </c>
       <c r="N10" t="n">
         <v>240</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5307</v>
+        <v>2.4051</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7966</v>
+        <v>0.7571</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.4898</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5307</v>
+        <v>2.4051</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0549</v>
+        <v>2.6625</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6197</v>
+        <v>-0.2454</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0549</v>
+        <v>3.5537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0563</v>
+        <v>1.9953</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6197</v>
+        <v>-0.2454</v>
       </c>
       <c r="K11" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="L11" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5634</v>
+        <v>1.7499</v>
       </c>
       <c r="N11" t="n">
-        <v>258</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.462</v>
+        <v>2.3987</v>
       </c>
       <c r="C12" t="n">
-        <v>0.775</v>
+        <v>0.7551</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4859</v>
+        <v>0.4869</v>
       </c>
       <c r="E12" t="n">
-        <v>2.462</v>
+        <v>2.3987</v>
       </c>
       <c r="F12" t="n">
-        <v>2.62</v>
+        <v>-0.0725</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.146</v>
+        <v>2.5053</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7502</v>
+        <v>-0.0725</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0251</v>
+        <v>-0.0745</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.146</v>
+        <v>2.5053</v>
       </c>
       <c r="K12" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="L12" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8791</v>
+        <v>2.4308</v>
       </c>
       <c r="N12" t="n">
-        <v>215</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3819</v>
+        <v>2.2629</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7498</v>
+        <v>0.7123</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4501</v>
+        <v>0.4251</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3819</v>
+        <v>2.2629</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1536</v>
+        <v>1.1884</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1291</v>
+        <v>0.9752</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1536</v>
+        <v>1.1884</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1833</v>
+        <v>1.2202</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1291</v>
+        <v>0.9752</v>
       </c>
       <c r="K13" t="n">
         <v>111</v>
@@ -1035,7 +1035,7 @@
         <v>65</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3124</v>
+        <v>2.1954</v>
       </c>
       <c r="N13" t="n">
         <v>176</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1232</v>
+        <v>1.999</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6684</v>
+        <v>0.6293</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3346</v>
+        <v>0.3049</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1232</v>
+        <v>1.999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3989</v>
+        <v>2.2889</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3932</v>
+        <v>-0.4074</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5254</v>
+        <v>2.2953</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5905</v>
+        <v>2.3566</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3932</v>
+        <v>-0.4074</v>
       </c>
       <c r="K14" t="n">
         <v>111</v>
@@ -1081,7 +1081,7 @@
         <v>65</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1973</v>
+        <v>1.9492</v>
       </c>
       <c r="N14" t="n">
         <v>176</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8971</v>
+        <v>1.8089</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5972</v>
+        <v>0.5694</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2336</v>
+        <v>0.2183</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8971</v>
+        <v>1.8089</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3706</v>
+        <v>2.3068</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3728</v>
+        <v>-0.3972</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4635</v>
+        <v>2.3363</v>
       </c>
       <c r="I15" t="n">
-        <v>2.527</v>
+        <v>2.3988</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3728</v>
+        <v>-0.3972</v>
       </c>
       <c r="K15" t="n">
         <v>111</v>
@@ -1127,7 +1127,7 @@
         <v>65</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1542</v>
+        <v>2.0016</v>
       </c>
       <c r="N15" t="n">
         <v>176</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8611</v>
+        <v>1.8012</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5859</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2175</v>
+        <v>0.2147</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8611</v>
+        <v>1.8012</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2533</v>
+        <v>2.2066</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3943</v>
+        <v>-0.4075</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2533</v>
+        <v>2.2066</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2533</v>
+        <v>2.2066</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3943</v>
+        <v>-0.4075</v>
       </c>
       <c r="K16" t="n">
         <v>91</v>
@@ -1173,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.859</v>
+        <v>1.7991</v>
       </c>
       <c r="N16" t="n">
         <v>133</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5928</v>
+        <v>1.4711</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5014</v>
+        <v>0.4631</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0644</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5928</v>
+        <v>1.4711</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2598</v>
+        <v>1.1381</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2598</v>
+        <v>1.1381</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2598</v>
+        <v>1.1381</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2598</v>
+        <v>1.1381</v>
       </c>
       <c r="N17" t="n">
         <v>84</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3979</v>
+        <v>1.3439</v>
       </c>
       <c r="C18" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0106</v>
+        <v>0.0064</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3979</v>
+        <v>1.3439</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9335</v>
+        <v>0.9694</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3688</v>
+        <v>0.279</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9335</v>
+        <v>0.9694</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9576</v>
+        <v>0.9953</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3688</v>
+        <v>0.279</v>
       </c>
       <c r="K18" t="n">
         <v>111</v>
@@ -1265,7 +1265,7 @@
         <v>65</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3264</v>
+        <v>1.2743</v>
       </c>
       <c r="N18" t="n">
         <v>176</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3367</v>
+        <v>1.305</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4208</v>
+        <v>0.4108</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0167</v>
+        <v>-0.0113</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3367</v>
+        <v>1.305</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2617</v>
+        <v>1.23</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2617</v>
+        <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2617</v>
+        <v>1.23</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2617</v>
+        <v>1.23</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
@@ -1320,369 +1320,369 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8202</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2582</v>
+        <v>0.2344</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2475</v>
+        <v>-0.2666</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8202</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7024</v>
+        <v>1.3073</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.3145</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7024</v>
+        <v>1.3073</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7024</v>
+        <v>0.734</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.3145</v>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7024</v>
+        <v>0.4195</v>
       </c>
       <c r="N20" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6785</v>
+        <v>0.6975</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2136</v>
+        <v>0.2196</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3107</v>
+        <v>-0.288</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6785</v>
+        <v>0.6975</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3451</v>
+        <v>0.5797</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1437</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3451</v>
+        <v>0.5797</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3451</v>
+        <v>0.5797</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1437</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4888</v>
+        <v>0.5797</v>
       </c>
       <c r="N21" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6675</v>
+        <v>0.6037</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2101</v>
+        <v>0.19</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3157</v>
+        <v>-0.3308</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6675</v>
+        <v>0.6037</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0641</v>
+        <v>0.3114</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2007</v>
+        <v>0.1026</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0641</v>
+        <v>0.3114</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0915</v>
+        <v>0.3114</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2007</v>
+        <v>0.1026</v>
       </c>
       <c r="K22" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L22" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8907999999999999</v>
+        <v>0.414</v>
       </c>
       <c r="N22" t="n">
-        <v>176</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5787</v>
+        <v>0.4986</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1822</v>
+        <v>0.157</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3553</v>
+        <v>-0.3787</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5787</v>
+        <v>0.4986</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2169</v>
+        <v>0.841</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3899</v>
+        <v>-0.095</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2169</v>
+        <v>0.841</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6571</v>
+        <v>0.4722</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3899</v>
+        <v>-0.095</v>
       </c>
       <c r="K23" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="L23" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2672</v>
+        <v>0.3772</v>
       </c>
       <c r="N23" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5258</v>
+        <v>0.4925</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1655</v>
+        <v>0.155</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.379</v>
+        <v>-0.3814</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5258</v>
+        <v>0.4925</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4054</v>
+        <v>0.9104</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.222</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4054</v>
+        <v>0.9104</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4054</v>
+        <v>0.9348</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.222</v>
       </c>
       <c r="K24" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4054</v>
+        <v>0.7128</v>
       </c>
       <c r="N24" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5064</v>
+        <v>0.4637</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1594</v>
+        <v>0.146</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3876</v>
+        <v>-0.3946</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5064</v>
+        <v>0.4637</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8298</v>
+        <v>0.3433</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.076</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8298</v>
+        <v>0.3433</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4481</v>
+        <v>0.3433</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.076</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3721</v>
+        <v>0.3433</v>
       </c>
       <c r="N25" t="n">
-        <v>215</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3933</v>
+        <v>0.334</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1238</v>
+        <v>0.1051</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4381</v>
+        <v>-0.4536</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3933</v>
+        <v>0.334</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4172</v>
+        <v>-0.1892</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1008</v>
+        <v>0.4433</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4172</v>
+        <v>-0.1892</v>
       </c>
       <c r="I26" t="n">
-        <v>0.428</v>
+        <v>-0.1892</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1008</v>
+        <v>0.4433</v>
       </c>
       <c r="K26" t="n">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="L26" t="n">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5287999999999999</v>
+        <v>0.2541</v>
       </c>
       <c r="N26" t="n">
-        <v>240</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3154</v>
+        <v>0.3009</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0993</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4729</v>
+        <v>-0.4687</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3154</v>
+        <v>0.3009</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2259</v>
+        <v>0.389</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4614</v>
+        <v>0.0366</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2259</v>
+        <v>0.389</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2259</v>
+        <v>0.3994</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4614</v>
+        <v>0.0366</v>
       </c>
       <c r="K27" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="L27" t="n">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2355</v>
+        <v>0.436</v>
       </c>
       <c r="N27" t="n">
-        <v>133</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1474</v>
+        <v>0.1026</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0464</v>
+        <v>0.0323</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.548</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1474</v>
+        <v>0.1026</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1459</v>
+        <v>0.1011</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1459</v>
+        <v>0.1011</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1459</v>
+        <v>0.1011</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1459</v>
+        <v>0.1011</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0218</v>
+        <v>-0.0649</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0069</v>
+        <v>-0.0204</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6041</v>
+        <v>-0.6354</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0218</v>
+        <v>-0.0649</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1487</v>
+        <v>-0.1874</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1375</v>
+        <v>0.0895</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1487</v>
+        <v>-0.1874</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1525</v>
+        <v>-0.1924</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1375</v>
+        <v>0.0895</v>
       </c>
       <c r="K29" t="n">
         <v>114</v>
@@ -1771,7 +1771,7 @@
         <v>126</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.01499999999999999</v>
+        <v>-0.1029</v>
       </c>
       <c r="N29" t="n">
         <v>240</v>
@@ -1780,231 +1780,231 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0576</v>
+        <v>-0.0888</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0181</v>
+        <v>-0.028</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6395</v>
+        <v>-0.6462</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0576</v>
+        <v>-0.0888</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1124</v>
+        <v>-1.162</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.2392</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1124</v>
+        <v>-1.162</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1124</v>
+        <v>-0.6524</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.2392</v>
       </c>
       <c r="K30" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1124</v>
+        <v>0.5868000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>84</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2204</v>
+        <v>-0.1323</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0694</v>
+        <v>-0.0416</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7123</v>
+        <v>-0.6661</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2204</v>
+        <v>-0.1323</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5258</v>
+        <v>-0.1871</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6647</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5258</v>
+        <v>-0.1871</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5393</v>
+        <v>-0.1871</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6647</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L31" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1254</v>
+        <v>-0.1871</v>
       </c>
       <c r="N31" t="n">
-        <v>258</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2417</v>
+        <v>-0.2626</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0761</v>
+        <v>-0.0827</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7218</v>
+        <v>-0.7254</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2417</v>
+        <v>-0.2626</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.2471</v>
+        <v>0.0998</v>
       </c>
       <c r="G32" t="n">
-        <v>1.1714</v>
+        <v>-0.1784</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.2471</v>
+        <v>0.0998</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6734</v>
+        <v>0.0998</v>
       </c>
       <c r="J32" t="n">
-        <v>1.1714</v>
+        <v>-0.1784</v>
       </c>
       <c r="K32" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="L32" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="M32" t="n">
-        <v>0.498</v>
+        <v>-0.0786</v>
       </c>
       <c r="N32" t="n">
-        <v>220</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2926</v>
+        <v>-0.2774</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0921</v>
+        <v>-0.0873</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7322</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2926</v>
+        <v>-0.2774</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.187</v>
+        <v>0.4681</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0238</v>
+        <v>-0.664</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.187</v>
+        <v>0.4681</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1918</v>
+        <v>0.4806</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0238</v>
+        <v>-0.664</v>
       </c>
       <c r="K33" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="L33" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.168</v>
+        <v>-0.1834</v>
       </c>
       <c r="N33" t="n">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3639</v>
+        <v>-0.3188</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1146</v>
+        <v>-0.1004</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7764</v>
+        <v>-0.751</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3639</v>
+        <v>-0.3188</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0286</v>
+        <v>-0.1785</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2085</v>
+        <v>-0.0108</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0286</v>
+        <v>-0.1785</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0286</v>
+        <v>-0.1833</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2085</v>
+        <v>-0.0108</v>
       </c>
       <c r="K34" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="L34" t="n">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1799</v>
+        <v>-0.1941</v>
       </c>
       <c r="N34" t="n">
-        <v>133</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7318</v>
+        <v>-0.6213</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2304</v>
+        <v>-0.1956</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9407</v>
+        <v>-0.8888</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7318</v>
+        <v>-0.6213</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.177</v>
+        <v>-2.0646</v>
       </c>
       <c r="G35" t="n">
-        <v>1.6067</v>
+        <v>1.6048</v>
       </c>
       <c r="H35" t="n">
-        <v>-2.177</v>
+        <v>-2.0646</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.2331</v>
+        <v>-2.1198</v>
       </c>
       <c r="J35" t="n">
-        <v>1.6067</v>
+        <v>1.6048</v>
       </c>
       <c r="K35" t="n">
         <v>141</v>
@@ -2047,7 +2047,7 @@
         <v>117</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6263999999999998</v>
+        <v>-0.5150000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>258</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.74</v>
+        <v>-0.7553</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2329</v>
+        <v>-0.2378</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9444</v>
+        <v>-0.9499</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.74</v>
+        <v>-0.7553</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6288</v>
+        <v>-0.6441</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6288</v>
+        <v>-0.6441</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6288</v>
+        <v>-0.6441</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6288</v>
+        <v>-0.6441</v>
       </c>
       <c r="N36" t="n">
         <v>84</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7972</v>
+        <v>-0.7906</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2509</v>
+        <v>-0.2489</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9699</v>
+        <v>-0.9659</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7972</v>
+        <v>-0.7906</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8165</v>
+        <v>-0.8099</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8165</v>
+        <v>-0.8099</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8165</v>
+        <v>-0.8099</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8165</v>
+        <v>-0.8099</v>
       </c>
       <c r="N37" t="n">
         <v>84</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8318</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2618</v>
+        <v>-0.2626</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.9858</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8318</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6085</v>
+        <v>-0.6109</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6085</v>
+        <v>-0.6109</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6085</v>
+        <v>-0.6109</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6085</v>
+        <v>-0.6109</v>
       </c>
       <c r="N38" t="n">
         <v>84</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9187</v>
+        <v>-0.8552</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2892</v>
+        <v>-0.2692</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0242</v>
+        <v>-0.9954</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9187</v>
+        <v>-0.8552</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.1439</v>
+        <v>-0.0956</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.6149</v>
+        <v>-0.5997</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.1439</v>
+        <v>-0.0956</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1439</v>
+        <v>-0.0956</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6149</v>
+        <v>-0.5997</v>
       </c>
       <c r="K39" t="n">
         <v>91</v>
@@ -2231,7 +2231,7 @@
         <v>42</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7588</v>
+        <v>-0.6953</v>
       </c>
       <c r="N39" t="n">
         <v>133</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2325</v>
+        <v>-2.2075</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7028</v>
+        <v>-0.6949</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.611</v>
+        <v>-1.6114</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2325</v>
+        <v>-2.2075</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6713</v>
+        <v>-1.6463</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6713</v>
+        <v>-1.6463</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6713</v>
+        <v>-1.6463</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6713</v>
+        <v>-1.6463</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0762</v>
+        <v>-2.9591</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9684</v>
+        <v>-0.9315</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9879</v>
+        <v>-1.9538</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0762</v>
+        <v>-2.9591</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5956</v>
+        <v>-1.4807</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.2295</v>
+        <v>-1.2273</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5956</v>
+        <v>-1.4807</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6367</v>
+        <v>-1.5203</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.2295</v>
+        <v>-1.2273</v>
       </c>
       <c r="K41" t="n">
         <v>141</v>
@@ -2323,7 +2323,7 @@
         <v>117</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8662</v>
+        <v>-2.7476</v>
       </c>
       <c r="N41" t="n">
         <v>258</v>
@@ -2429,10 +2429,10 @@
         <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J2" t="n">
-        <v>29.5248</v>
+        <v>31.7152</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.79</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5378</v>
+        <v>1.5709</v>
       </c>
       <c r="J3" t="n">
-        <v>24.6048</v>
+        <v>25.1344</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.51</v>
       </c>
       <c r="I4" t="n">
-        <v>1.091</v>
+        <v>1.1077</v>
       </c>
       <c r="J4" t="n">
-        <v>17.456</v>
+        <v>17.7232</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.23</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5546</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>8.8736</v>
+        <v>8.443199999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3013</v>
+        <v>0.2654</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8208</v>
+        <v>4.2464</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2014</v>
+        <v>1.2771</v>
       </c>
       <c r="J7" t="n">
-        <v>19.2224</v>
+        <v>20.4336</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.61</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3919</v>
+        <v>-0.3815</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.2704</v>
+        <v>-6.104</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.57</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4271</v>
+        <v>-0.4186</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.8336</v>
+        <v>-6.6976</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.37</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6024</v>
+        <v>-0.615</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.638400000000001</v>
+        <v>-9.84</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7492</v>
+        <v>-0.7917</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.9872</v>
+        <v>-12.6672</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.28</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7496</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>17.9904</v>
+        <v>17.2632</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3574</v>
+        <v>0.3167</v>
       </c>
       <c r="J13" t="n">
-        <v>8.5776</v>
+        <v>7.6008</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1073</v>
+        <v>-0.082</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.5752</v>
+        <v>-1.968</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1437</v>
+        <v>-0.1137</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.4488</v>
+        <v>-2.7288</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3515</v>
+        <v>-0.309</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.436</v>
+        <v>-7.416</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7638</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>18.3312</v>
+        <v>16.9968</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4218</v>
+        <v>0.365</v>
       </c>
       <c r="J18" t="n">
-        <v>10.1232</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2046</v>
+        <v>0.1647</v>
       </c>
       <c r="J19" t="n">
-        <v>4.9104</v>
+        <v>3.9528</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0683</v>
+        <v>0.05</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6392</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4761</v>
+        <v>-0.4753</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.4264</v>
+        <v>-11.4072</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8184</v>
+        <v>0.8024</v>
       </c>
       <c r="J22" t="n">
-        <v>18.8232</v>
+        <v>18.4552</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.622</v>
+        <v>0.609</v>
       </c>
       <c r="J23" t="n">
-        <v>14.306</v>
+        <v>14.007</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4392</v>
+        <v>0.4039</v>
       </c>
       <c r="J24" t="n">
-        <v>10.1016</v>
+        <v>9.2897</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0196</v>
+        <v>-0.0146</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4508</v>
+        <v>-0.3358</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5885</v>
+        <v>-0.5508</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.5355</v>
+        <v>-12.6684</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5464</v>
+        <v>0.5198</v>
       </c>
       <c r="J27" t="n">
-        <v>12.5672</v>
+        <v>11.9554</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1494</v>
+        <v>0.1149</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4362</v>
+        <v>2.6427</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0718</v>
+        <v>-0.0578</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.6514</v>
+        <v>-1.3294</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1346</v>
+        <v>-0.1156</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.0958</v>
+        <v>-2.6588</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.74</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3095</v>
+        <v>-0.2921</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.1185</v>
+        <v>-6.7183</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.07</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1883</v>
+        <v>0.1754</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3894</v>
+        <v>3.1572</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.76</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2726</v>
+        <v>-0.2548</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.9068</v>
+        <v>-4.5864</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.76</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2726</v>
+        <v>-0.2548</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.9068</v>
+        <v>-4.5864</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3007</v>
+        <v>-0.2835</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.4126</v>
+        <v>-5.103</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.31</v>
+        <v>-0.2931</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.58</v>
+        <v>-5.2758</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.92</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8466</v>
+        <v>0.7924</v>
       </c>
       <c r="J37" t="n">
-        <v>15.2388</v>
+        <v>14.2632</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.53</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5804</v>
+        <v>0.5461</v>
       </c>
       <c r="J38" t="n">
-        <v>10.4472</v>
+        <v>9.829800000000001</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.38</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4717</v>
+        <v>0.4204</v>
       </c>
       <c r="J39" t="n">
-        <v>8.490600000000001</v>
+        <v>7.5672</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.37</v>
       </c>
       <c r="I40" t="n">
-        <v>0.464</v>
+        <v>0.411</v>
       </c>
       <c r="J40" t="n">
-        <v>8.352</v>
+        <v>7.398</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.31</v>
+        <v>-0.297</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.58</v>
+        <v>-5.346</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.93</v>
       </c>
       <c r="I42" t="n">
-        <v>1.484</v>
+        <v>1.5034</v>
       </c>
       <c r="J42" t="n">
-        <v>29.68</v>
+        <v>30.068</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.32</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6887</v>
+        <v>0.6785</v>
       </c>
       <c r="J43" t="n">
-        <v>13.774</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6167</v>
+        <v>0.6097</v>
       </c>
       <c r="J44" t="n">
-        <v>12.334</v>
+        <v>12.194</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.03</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0866</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>1.732</v>
+        <v>1.314</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1891</v>
+        <v>-0.1594</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.782</v>
+        <v>-3.188</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6352</v>
+        <v>0.607</v>
       </c>
       <c r="J47" t="n">
-        <v>12.704</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.32</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5889</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>11.778</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.87</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1765</v>
+        <v>-0.1564</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.53</v>
+        <v>-3.128</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3713</v>
+        <v>-0.358</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.426</v>
+        <v>-7.16</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4598</v>
+        <v>-0.4557</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.196</v>
+        <v>-9.114000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.43</v>
       </c>
       <c r="I52" t="n">
-        <v>0.869</v>
+        <v>0.8534</v>
       </c>
       <c r="J52" t="n">
-        <v>25.201</v>
+        <v>24.7486</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.455</v>
+        <v>0.4247</v>
       </c>
       <c r="J53" t="n">
-        <v>13.195</v>
+        <v>12.3163</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.368</v>
+        <v>0.3322</v>
       </c>
       <c r="J54" t="n">
-        <v>10.672</v>
+        <v>9.633800000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2363</v>
+        <v>0.2056</v>
       </c>
       <c r="J55" t="n">
-        <v>6.8527</v>
+        <v>5.9624</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0852</v>
+        <v>-0.0643</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.4708</v>
+        <v>-1.8647</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7378</v>
       </c>
       <c r="J57" t="n">
-        <v>22.2604</v>
+        <v>21.3962</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.07</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2055</v>
+        <v>0.1634</v>
       </c>
       <c r="J58" t="n">
-        <v>5.9595</v>
+        <v>4.7386</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.72</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3224</v>
+        <v>-0.3055</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.349600000000001</v>
+        <v>-8.859500000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3317</v>
+        <v>-0.3154</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.619300000000001</v>
+        <v>-9.146599999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3684</v>
+        <v>-0.3548</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.6836</v>
+        <v>-10.2892</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3059</v>
+        <v>0.2958</v>
       </c>
       <c r="J62" t="n">
-        <v>6.7298</v>
+        <v>6.5076</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.04</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1125</v>
+        <v>0.0965</v>
       </c>
       <c r="J63" t="n">
-        <v>2.475</v>
+        <v>2.123</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.012</v>
+        <v>0.0094</v>
       </c>
       <c r="J64" t="n">
-        <v>0.264</v>
+        <v>0.2068</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3655</v>
+        <v>-0.3514</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.041</v>
+        <v>-7.7308</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.62</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4104</v>
+        <v>-0.4003</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.0288</v>
+        <v>-8.8066</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.66</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6992</v>
+        <v>0.6549</v>
       </c>
       <c r="J67" t="n">
-        <v>15.3824</v>
+        <v>14.4078</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.27</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3828</v>
+        <v>0.3216</v>
       </c>
       <c r="J68" t="n">
-        <v>8.4216</v>
+        <v>7.0752</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.09</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1586</v>
+        <v>0.1236</v>
       </c>
       <c r="J69" t="n">
-        <v>3.4892</v>
+        <v>2.7192</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0786</v>
+        <v>0.0576</v>
       </c>
       <c r="J70" t="n">
-        <v>1.7292</v>
+        <v>1.2672</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2859</v>
+        <v>-0.2687</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.2898</v>
+        <v>-5.9114</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.61</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1374</v>
+        <v>1.1352</v>
       </c>
       <c r="J72" t="n">
-        <v>27.2976</v>
+        <v>27.2448</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.11</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3504</v>
+        <v>0.3119</v>
       </c>
       <c r="J73" t="n">
-        <v>8.409599999999999</v>
+        <v>7.4856</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0139</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.3336</v>
+        <v>-0.2304</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3052</v>
+        <v>-0.2639</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.3248</v>
+        <v>-6.3336</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5824</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.9776</v>
+        <v>-13.0536</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.53</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8153</v>
+        <v>0.7819</v>
       </c>
       <c r="J77" t="n">
-        <v>19.5672</v>
+        <v>18.7656</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.05</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1503</v>
+        <v>0.1156</v>
       </c>
       <c r="J78" t="n">
-        <v>3.6072</v>
+        <v>2.7744</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.82</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2309</v>
+        <v>-0.2105</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.5416</v>
+        <v>-5.052</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2899</v>
+        <v>-0.2715</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.9576</v>
+        <v>-6.516</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2899</v>
+        <v>-0.2715</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.9576</v>
+        <v>-6.516</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.45</v>
+        <v>0.3891</v>
       </c>
       <c r="J82" t="n">
-        <v>10.35</v>
+        <v>8.949299999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.23</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3407</v>
+        <v>0.2824</v>
       </c>
       <c r="J83" t="n">
-        <v>7.8361</v>
+        <v>6.4952</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.255</v>
+        <v>0.2058</v>
       </c>
       <c r="J84" t="n">
-        <v>5.865</v>
+        <v>4.7334</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.15</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2423</v>
+        <v>0.1947</v>
       </c>
       <c r="J85" t="n">
-        <v>5.5729</v>
+        <v>4.4781</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2925</v>
+        <v>-0.2753</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.7275</v>
+        <v>-6.3319</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.29</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4606</v>
+        <v>0.4758</v>
       </c>
       <c r="J87" t="n">
-        <v>10.5938</v>
+        <v>10.9434</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.055</v>
+        <v>-0.044</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.265</v>
+        <v>-1.012</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.95</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0684</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.8998</v>
+        <v>-1.5732</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1192</v>
+        <v>-0.1019</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.7416</v>
+        <v>-2.3437</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4412</v>
+        <v>-0.4348</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.1476</v>
+        <v>-10.0004</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4471</v>
+        <v>0.4053</v>
       </c>
       <c r="J92" t="n">
-        <v>8.494899999999999</v>
+        <v>7.7007</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2237</v>
+        <v>-0.2069</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.2503</v>
+        <v>-3.9311</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.74</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2891</v>
+        <v>-0.2721</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.4929</v>
+        <v>-5.1699</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.67</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3534</v>
+        <v>-0.3387</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.7146</v>
+        <v>-6.4353</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.54</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4692</v>
+        <v>-0.4645</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.9148</v>
+        <v>-8.8255</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.59</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0588</v>
+        <v>1.0484</v>
       </c>
       <c r="J97" t="n">
-        <v>20.1172</v>
+        <v>19.9196</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.42</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8304</v>
+        <v>0.8165</v>
       </c>
       <c r="J98" t="n">
-        <v>15.7776</v>
+        <v>15.5135</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6028</v>
+        <v>0.5961</v>
       </c>
       <c r="J99" t="n">
-        <v>11.4532</v>
+        <v>11.3259</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.11</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3211</v>
+        <v>0.2892</v>
       </c>
       <c r="J100" t="n">
-        <v>6.1009</v>
+        <v>5.4948</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.08</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2414</v>
+        <v>0.2112</v>
       </c>
       <c r="J101" t="n">
-        <v>4.5866</v>
+        <v>4.0128</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.17</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3809</v>
+        <v>0.3254</v>
       </c>
       <c r="J102" t="n">
-        <v>8.7607</v>
+        <v>7.4842</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2518</v>
+        <v>0.2054</v>
       </c>
       <c r="J103" t="n">
-        <v>5.7914</v>
+        <v>4.7242</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.232</v>
+        <v>0.1876</v>
       </c>
       <c r="J104" t="n">
-        <v>5.336</v>
+        <v>4.3148</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1586</v>
+        <v>-0.1385</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.6478</v>
+        <v>-3.1855</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2821</v>
+        <v>-0.2634</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.4883</v>
+        <v>-6.0582</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.93</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5251</v>
+        <v>1.5559</v>
       </c>
       <c r="J107" t="n">
-        <v>35.0773</v>
+        <v>35.7857</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7195</v>
+        <v>0.7046</v>
       </c>
       <c r="J108" t="n">
-        <v>16.5485</v>
+        <v>16.2058</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.25</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5982</v>
+        <v>0.5876</v>
       </c>
       <c r="J109" t="n">
-        <v>13.7586</v>
+        <v>13.5148</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.71</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.8199</v>
+        <v>-0.8008</v>
       </c>
       <c r="J110" t="n">
-        <v>-18.8577</v>
+        <v>-18.4184</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.9247</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>-21.2681</v>
+        <v>-21.0864</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.3</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6832</v>
+        <v>0.6684</v>
       </c>
       <c r="J112" t="n">
-        <v>16.3968</v>
+        <v>16.0416</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6056</v>
+        <v>0.5934</v>
       </c>
       <c r="J113" t="n">
-        <v>14.5344</v>
+        <v>14.2416</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.12</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3713</v>
+        <v>0.3341</v>
       </c>
       <c r="J114" t="n">
-        <v>8.911199999999999</v>
+        <v>8.0184</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.05</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1821</v>
+        <v>0.1543</v>
       </c>
       <c r="J115" t="n">
-        <v>4.3704</v>
+        <v>3.7032</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3397</v>
+        <v>-0.2978</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.152799999999999</v>
+        <v>-7.1472</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.44</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7033</v>
+        <v>0.6697</v>
       </c>
       <c r="J117" t="n">
-        <v>16.8792</v>
+        <v>16.0728</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6378</v>
+        <v>0.6071</v>
       </c>
       <c r="J118" t="n">
-        <v>15.3072</v>
+        <v>14.5704</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0696</v>
+        <v>0.0508</v>
       </c>
       <c r="J119" t="n">
-        <v>1.6704</v>
+        <v>1.2192</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.83</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2261</v>
+        <v>-0.2057</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.4264</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4837</v>
+        <v>-0.4838</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.6088</v>
+        <v>-11.6112</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.9</v>
       </c>
       <c r="I122" t="n">
-        <v>1.428</v>
+        <v>1.4402</v>
       </c>
       <c r="J122" t="n">
-        <v>25.704</v>
+        <v>25.9236</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.81</v>
       </c>
       <c r="I123" t="n">
-        <v>1.3188</v>
+        <v>1.3224</v>
       </c>
       <c r="J123" t="n">
-        <v>23.7384</v>
+        <v>23.8032</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.57</v>
       </c>
       <c r="I124" t="n">
-        <v>1.0176</v>
+        <v>1.0072</v>
       </c>
       <c r="J124" t="n">
-        <v>18.3168</v>
+        <v>18.1296</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5355</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.638999999999999</v>
+        <v>-9.045</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6977</v>
+        <v>-0.6741</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.5586</v>
+        <v>-12.1338</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>0.99</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0176</v>
+        <v>0.0273</v>
       </c>
       <c r="J127" t="n">
-        <v>0.3168</v>
+        <v>0.4914</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.89</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1312</v>
+        <v>-0.1159</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.3616</v>
+        <v>-2.0862</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1764</v>
+        <v>-0.1607</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.1752</v>
+        <v>-2.8926</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.54</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4639</v>
+        <v>-0.4583</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.350199999999999</v>
+        <v>-8.2494</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.43</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5596</v>
+        <v>-0.5664</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.0728</v>
+        <v>-10.1952</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6819</v>
+        <v>1.728</v>
       </c>
       <c r="J132" t="n">
-        <v>25.2285</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.58</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1642</v>
+        <v>1.1822</v>
       </c>
       <c r="J133" t="n">
-        <v>17.463</v>
+        <v>17.733</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.57</v>
       </c>
       <c r="I134" t="n">
-        <v>1.1516</v>
+        <v>1.1695</v>
       </c>
       <c r="J134" t="n">
-        <v>17.274</v>
+        <v>17.5425</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.35</v>
       </c>
       <c r="I135" t="n">
-        <v>0.8131</v>
+        <v>0.8023</v>
       </c>
       <c r="J135" t="n">
-        <v>12.1965</v>
+        <v>12.0345</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3122</v>
+        <v>-0.2817</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.683</v>
+        <v>-4.2255</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.2156</v>
+        <v>-0.1999</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.234</v>
+        <v>-2.9985</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.73</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2774</v>
+        <v>-0.2648</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.161</v>
+        <v>-3.972</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.63</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3706</v>
+        <v>-0.3612</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.559</v>
+        <v>-5.418</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.52</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4652</v>
+        <v>-0.4601</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.978</v>
+        <v>-6.9015</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5532</v>
+        <v>-0.5578</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.298</v>
+        <v>-8.367000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2613</v>
+        <v>0.2467</v>
       </c>
       <c r="J142" t="n">
-        <v>7.5777</v>
+        <v>7.1543</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.232</v>
+        <v>0.2161</v>
       </c>
       <c r="J143" t="n">
-        <v>6.728</v>
+        <v>6.2669</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0567</v>
+        <v>-0.0448</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.6443</v>
+        <v>-1.2992</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1447</v>
+        <v>-0.1254</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.1963</v>
+        <v>-3.6366</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.74</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.308</v>
+        <v>-0.2905</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.932</v>
+        <v>-8.4245</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.29</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4097</v>
+        <v>0.346</v>
       </c>
       <c r="J147" t="n">
-        <v>11.8813</v>
+        <v>10.034</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.25</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3636</v>
+        <v>0.3034</v>
       </c>
       <c r="J148" t="n">
-        <v>10.5444</v>
+        <v>8.7986</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.14</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2292</v>
+        <v>0.1834</v>
       </c>
       <c r="J149" t="n">
-        <v>6.6468</v>
+        <v>5.3186</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.01</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0208</v>
+        <v>0.0133</v>
       </c>
       <c r="J150" t="n">
-        <v>0.6032</v>
+        <v>0.3857</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.98</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.0529</v>
+        <v>-0.0407</v>
       </c>
       <c r="J151" t="n">
-        <v>-1.5341</v>
+        <v>-1.1803</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.44</v>
       </c>
       <c r="I152" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J152" t="n">
-        <v>38.744</v>
+        <v>39.636</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.58</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1769</v>
+        <v>1.1924</v>
       </c>
       <c r="J153" t="n">
-        <v>23.538</v>
+        <v>23.848</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5194</v>
+        <v>0.4907</v>
       </c>
       <c r="J154" t="n">
-        <v>10.388</v>
+        <v>9.814</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2981</v>
+        <v>-0.2644</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.962</v>
+        <v>-5.288</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6985</v>
+        <v>-0.6752</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.97</v>
+        <v>-13.504</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7104</v>
+        <v>0.664</v>
       </c>
       <c r="J157" t="n">
-        <v>14.208</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0631</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.506</v>
+        <v>-1.262</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.93</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1012</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.024</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.6</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4248</v>
+        <v>-0.4158</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.496</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5119</v>
+        <v>-0.5133</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.238</v>
+        <v>-10.266</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.56</v>
       </c>
       <c r="I162" t="n">
-        <v>1.177</v>
+        <v>1.1909</v>
       </c>
       <c r="J162" t="n">
-        <v>24.717</v>
+        <v>25.0089</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1096</v>
+        <v>1.1214</v>
       </c>
       <c r="J163" t="n">
-        <v>23.3016</v>
+        <v>23.5494</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8834</v>
+        <v>0.8663</v>
       </c>
       <c r="J164" t="n">
-        <v>18.5514</v>
+        <v>18.1923</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1929</v>
+        <v>0.1651</v>
       </c>
       <c r="J165" t="n">
-        <v>4.0509</v>
+        <v>3.4671</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.851</v>
+        <v>-0.8369</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.871</v>
+        <v>-17.5749</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.36</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6888</v>
+        <v>0.6319</v>
       </c>
       <c r="J167" t="n">
-        <v>14.4648</v>
+        <v>13.2699</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.04</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1238</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>2.5998</v>
+        <v>1.9677</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.073</v>
+        <v>-0.0585</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.533</v>
+        <v>-1.2285</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2124</v>
+        <v>-0.1918</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.4604</v>
+        <v>-4.0278</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.83</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2227</v>
+        <v>-0.2022</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.6767</v>
+        <v>-4.2462</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0933</v>
+        <v>1.1046</v>
       </c>
       <c r="J172" t="n">
-        <v>31.7057</v>
+        <v>32.0334</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.43</v>
       </c>
       <c r="I173" t="n">
-        <v>1.0187</v>
+        <v>1.0189</v>
       </c>
       <c r="J173" t="n">
-        <v>29.5423</v>
+        <v>29.5481</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.2</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5553</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J174" t="n">
-        <v>16.1037</v>
+        <v>15.0104</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.9</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.367</v>
+        <v>-0.3248</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.643</v>
+        <v>-9.4192</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.9787</v>
+        <v>-0.9758</v>
       </c>
       <c r="J176" t="n">
-        <v>-28.3823</v>
+        <v>-28.2982</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.82</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2421</v>
+        <v>1.2383</v>
       </c>
       <c r="J177" t="n">
-        <v>36.0209</v>
+        <v>35.9107</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.06</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1656</v>
+        <v>0.13</v>
       </c>
       <c r="J178" t="n">
-        <v>4.8024</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.89</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1612</v>
+        <v>-0.1409</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.6748</v>
+        <v>-4.0861</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2455</v>
+        <v>-0.2255</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.1195</v>
+        <v>-6.5395</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.59</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4486</v>
+        <v>-0.4441</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.0094</v>
+        <v>-12.8789</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.43</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6307</v>
+        <v>0.6643</v>
       </c>
       <c r="J182" t="n">
-        <v>15.1368</v>
+        <v>15.9432</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0363</v>
+        <v>0.0272</v>
       </c>
       <c r="J183" t="n">
-        <v>0.8712</v>
+        <v>0.6528</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.097</v>
+        <v>-0.0808</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.328</v>
+        <v>-1.9392</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2401</v>
+        <v>-0.2199</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.7624</v>
+        <v>-5.2776</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.68</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3636</v>
+        <v>-0.3499</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.7264</v>
+        <v>-8.397600000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.86</v>
       </c>
       <c r="I187" t="n">
-        <v>0.9751</v>
+        <v>0.917</v>
       </c>
       <c r="J187" t="n">
-        <v>23.4024</v>
+        <v>22.008</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.49</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6172</v>
+        <v>0.5457</v>
       </c>
       <c r="J188" t="n">
-        <v>14.8128</v>
+        <v>13.0968</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.335</v>
+        <v>0.2784</v>
       </c>
       <c r="J189" t="n">
-        <v>8.039999999999999</v>
+        <v>6.6816</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2775</v>
+        <v>-0.26</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.66</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4844</v>
+        <v>-0.4865</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.6256</v>
+        <v>-11.676</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.87</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5387</v>
+        <v>1.5733</v>
       </c>
       <c r="J192" t="n">
-        <v>23.0805</v>
+        <v>23.5995</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.51</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0865</v>
+        <v>1.0996</v>
       </c>
       <c r="J193" t="n">
-        <v>16.2975</v>
+        <v>16.494</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.5</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0732</v>
+        <v>1.0853</v>
       </c>
       <c r="J194" t="n">
-        <v>16.098</v>
+        <v>16.2795</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.28</v>
       </c>
       <c r="I195" t="n">
-        <v>0.6893</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J195" t="n">
-        <v>10.3395</v>
+        <v>10.017</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7422</v>
+        <v>-0.7222</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.133</v>
+        <v>-10.833</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.04</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1524</v>
+        <v>0.1181</v>
       </c>
       <c r="J197" t="n">
-        <v>2.286</v>
+        <v>1.7715</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.93</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1012</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.518</v>
+        <v>-1.305</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.9</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1368</v>
+        <v>-0.1204</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.052</v>
+        <v>-1.806</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1795</v>
+        <v>-0.1613</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.6925</v>
+        <v>-2.4195</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.59</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4336</v>
+        <v>-0.4256</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.504</v>
+        <v>-6.384</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0944</v>
+        <v>1.1052</v>
       </c>
       <c r="J202" t="n">
-        <v>37.2096</v>
+        <v>37.5768</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9157</v>
+        <v>0.8998</v>
       </c>
       <c r="J203" t="n">
-        <v>31.1338</v>
+        <v>30.5932</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4591</v>
+        <v>0.4236</v>
       </c>
       <c r="J204" t="n">
-        <v>15.6094</v>
+        <v>14.4024</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.96</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2022</v>
+        <v>-0.1676</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.8748</v>
+        <v>-5.6984</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.92</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3223</v>
+        <v>-0.2818</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.9582</v>
+        <v>-9.581200000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.41</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7766</v>
+        <v>0.7255</v>
       </c>
       <c r="J207" t="n">
-        <v>26.4044</v>
+        <v>24.667</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.96</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0706</v>
+        <v>-0.0571</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.4004</v>
+        <v>-1.9414</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1775</v>
+        <v>-0.1573</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.035</v>
+        <v>-5.3482</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.85</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1988</v>
+        <v>-0.1783</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.7592</v>
+        <v>-6.0622</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.76</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2886</v>
+        <v>-0.27</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.8124</v>
+        <v>-9.18</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5131</v>
+        <v>0.4538</v>
       </c>
       <c r="J212" t="n">
-        <v>12.3144</v>
+        <v>10.8912</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.15</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3429</v>
+        <v>0.2896</v>
       </c>
       <c r="J213" t="n">
-        <v>8.2296</v>
+        <v>6.9504</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.13</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3066</v>
+        <v>0.2557</v>
       </c>
       <c r="J214" t="n">
-        <v>7.3584</v>
+        <v>6.1368</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.07</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1892</v>
+        <v>0.1499</v>
       </c>
       <c r="J215" t="n">
-        <v>4.5408</v>
+        <v>3.5976</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.48</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5487</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.9792</v>
+        <v>-13.1688</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.55</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1919</v>
+        <v>1.2081</v>
       </c>
       <c r="J217" t="n">
-        <v>28.6056</v>
+        <v>28.9944</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.12</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3715</v>
+        <v>0.3341</v>
       </c>
       <c r="J218" t="n">
-        <v>8.916</v>
+        <v>8.0184</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.05</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1824</v>
+        <v>0.1546</v>
       </c>
       <c r="J219" t="n">
-        <v>4.3776</v>
+        <v>3.7104</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.05</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1824</v>
+        <v>0.1546</v>
       </c>
       <c r="J220" t="n">
-        <v>4.3776</v>
+        <v>3.7104</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.85</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4936</v>
+        <v>-0.4523</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.8464</v>
+        <v>-10.8552</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.19</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5023</v>
+        <v>0.4597</v>
       </c>
       <c r="J222" t="n">
-        <v>9.543699999999999</v>
+        <v>8.734299999999999</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.77</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2596</v>
+        <v>-0.2433</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.9324</v>
+        <v>-4.6227</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.73</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2958</v>
+        <v>-0.2797</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.6202</v>
+        <v>-5.3143</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.63</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3865</v>
+        <v>-0.3741</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.3435</v>
+        <v>-7.1079</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.48</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.853400000000001</v>
+        <v>-9.8743</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.64</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2562</v>
+        <v>1.2738</v>
       </c>
       <c r="J227" t="n">
-        <v>23.8678</v>
+        <v>24.2022</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.56</v>
       </c>
       <c r="I228" t="n">
-        <v>1.1534</v>
+        <v>1.1681</v>
       </c>
       <c r="J228" t="n">
-        <v>21.9146</v>
+        <v>22.1939</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.28</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6691</v>
       </c>
       <c r="J229" t="n">
-        <v>13.129</v>
+        <v>12.7129</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.26</v>
       </c>
       <c r="I230" t="n">
-        <v>0.65</v>
+        <v>0.6263</v>
       </c>
       <c r="J230" t="n">
-        <v>12.35</v>
+        <v>11.8997</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I231" t="n">
-        <v>0.3339</v>
+        <v>0.3018</v>
       </c>
       <c r="J231" t="n">
-        <v>6.3441</v>
+        <v>5.7342</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.74</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4328</v>
+        <v>1.4643</v>
       </c>
       <c r="J232" t="n">
-        <v>31.5216</v>
+        <v>32.2146</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.58</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2209</v>
+        <v>1.2375</v>
       </c>
       <c r="J233" t="n">
-        <v>26.8598</v>
+        <v>27.225</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.95</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2316</v>
+        <v>-0.1946</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.0952</v>
+        <v>-4.2812</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5968</v>
+        <v>-0.5605</v>
       </c>
       <c r="J235" t="n">
-        <v>-13.1296</v>
+        <v>-12.331</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7101</v>
+        <v>-0.6811</v>
       </c>
       <c r="J236" t="n">
-        <v>-15.6222</v>
+        <v>-14.9842</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.401</v>
+        <v>0.3457</v>
       </c>
       <c r="J237" t="n">
-        <v>8.821999999999999</v>
+        <v>7.6054</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2687</v>
+        <v>0.2207</v>
       </c>
       <c r="J238" t="n">
-        <v>5.9114</v>
+        <v>4.8554</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2064</v>
+        <v>0.1642</v>
       </c>
       <c r="J239" t="n">
-        <v>4.5408</v>
+        <v>3.6124</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.86</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1841</v>
+        <v>-0.1643</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.0502</v>
+        <v>-3.6146</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.42</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5843</v>
+        <v>-0.5979</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.8546</v>
+        <v>-13.1538</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1538</v>
+        <v>1.1674</v>
       </c>
       <c r="J242" t="n">
-        <v>32.3064</v>
+        <v>32.6872</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7604</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="J243" t="n">
-        <v>21.2912</v>
+        <v>20.5072</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.144</v>
+        <v>0.1199</v>
       </c>
       <c r="J244" t="n">
-        <v>4.032</v>
+        <v>3.3572</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.144</v>
+        <v>0.1199</v>
       </c>
       <c r="J245" t="n">
-        <v>4.032</v>
+        <v>3.3572</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.91</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3467</v>
+        <v>-0.3053</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.707599999999999</v>
+        <v>-8.548400000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3674</v>
+        <v>0.3136</v>
       </c>
       <c r="J247" t="n">
-        <v>10.2872</v>
+        <v>8.780799999999999</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2088</v>
+        <v>0.1665</v>
       </c>
       <c r="J248" t="n">
-        <v>5.8464</v>
+        <v>4.662</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.98</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0367</v>
+        <v>-0.0286</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.0276</v>
+        <v>-0.8008</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2443</v>
+        <v>-0.2245</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.8404</v>
+        <v>-6.286</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.456</v>
+        <v>-0.4509</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.768</v>
+        <v>-12.6252</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.96</v>
       </c>
       <c r="I252" t="n">
-        <v>1.6754</v>
+        <v>1.726</v>
       </c>
       <c r="J252" t="n">
-        <v>31.8326</v>
+        <v>32.794</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.61</v>
       </c>
       <c r="I253" t="n">
-        <v>1.2351</v>
+        <v>1.2513</v>
       </c>
       <c r="J253" t="n">
-        <v>23.4669</v>
+        <v>23.7747</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.14</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3979</v>
+        <v>0.3655</v>
       </c>
       <c r="J254" t="n">
-        <v>7.5601</v>
+        <v>6.9445</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.96</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2187</v>
+        <v>-0.1856</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.1553</v>
+        <v>-3.5264</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.72</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8141</v>
+        <v>-0.7974</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.4679</v>
+        <v>-15.1506</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.99</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0012</v>
+        <v>0.0059</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.0228</v>
+        <v>0.1121</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1165</v>
+        <v>-0.1019</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.2135</v>
+        <v>-1.9361</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1514</v>
+        <v>-0.1356</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.8766</v>
+        <v>-2.5764</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.73</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2992</v>
+        <v>-0.2823</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.6848</v>
+        <v>-5.3637</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5394</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.2486</v>
+        <v>-10.3341</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.56</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2012</v>
+        <v>1.2175</v>
       </c>
       <c r="J262" t="n">
-        <v>26.4264</v>
+        <v>26.785</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.25</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6614</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="J263" t="n">
-        <v>14.5508</v>
+        <v>13.805</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.02</v>
       </c>
       <c r="I264" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0614</v>
       </c>
       <c r="J264" t="n">
-        <v>1.7204</v>
+        <v>1.3508</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2569</v>
+        <v>-0.2181</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.6518</v>
+        <v>-4.7982</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.93</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2863</v>
+        <v>-0.2461</v>
       </c>
       <c r="J266" t="n">
-        <v>-6.2986</v>
+        <v>-5.4142</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3931</v>
+        <v>0.3392</v>
       </c>
       <c r="J267" t="n">
-        <v>8.648199999999999</v>
+        <v>7.4624</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.93</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1039</v>
+        <v>-0.089</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.2858</v>
+        <v>-1.958</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.88</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1602</v>
+        <v>-0.142</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.5244</v>
+        <v>-3.124</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.242</v>
+        <v>-0.2224</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.324</v>
+        <v>-4.8928</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3556</v>
+        <v>-0.3407</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.8232</v>
+        <v>-7.4954</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.79</v>
       </c>
       <c r="I272" t="n">
-        <v>1.5331</v>
+        <v>1.5813</v>
       </c>
       <c r="J272" t="n">
-        <v>36.7944</v>
+        <v>37.9512</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.93</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.2734</v>
+        <v>-0.2332</v>
       </c>
       <c r="J273" t="n">
-        <v>-6.5616</v>
+        <v>-5.5968</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2734</v>
+        <v>-0.2332</v>
       </c>
       <c r="J274" t="n">
-        <v>-6.5616</v>
+        <v>-5.5968</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3827</v>
+        <v>-0.3397</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.184799999999999</v>
+        <v>-8.152799999999999</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5555</v>
+        <v>-0.5155</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.332</v>
+        <v>-12.372</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.45</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8081</v>
+        <v>0.7548</v>
       </c>
       <c r="J277" t="n">
-        <v>19.3944</v>
+        <v>18.1152</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.45</v>
       </c>
       <c r="I278" t="n">
-        <v>0.8081</v>
+        <v>0.7548</v>
       </c>
       <c r="J278" t="n">
-        <v>19.3944</v>
+        <v>18.1152</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.96</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0767</v>
+        <v>-0.0615</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.8408</v>
+        <v>-1.476</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3151</v>
+        <v>-0.2985</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.5624</v>
+        <v>-7.164</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3795</v>
+        <v>-0.3679</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.108000000000001</v>
+        <v>-8.829599999999999</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.18</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3203</v>
+        <v>0.31</v>
       </c>
       <c r="J282" t="n">
-        <v>7.0466</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2782</v>
+        <v>0.2647</v>
       </c>
       <c r="J283" t="n">
-        <v>6.1204</v>
+        <v>5.8234</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0701</v>
+        <v>-0.0569</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.5422</v>
+        <v>-1.2518</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.93</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1084</v>
+        <v>-0.0915</v>
       </c>
       <c r="J285" t="n">
-        <v>-2.3848</v>
+        <v>-2.013</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.58</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4513</v>
+        <v>-0.4462</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.928599999999999</v>
+        <v>-9.8164</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.71</v>
       </c>
       <c r="I287" t="n">
-        <v>0.8325</v>
+        <v>0.7631</v>
       </c>
       <c r="J287" t="n">
-        <v>18.315</v>
+        <v>16.7882</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>0.6248</v>
+        <v>0.5532</v>
       </c>
       <c r="J288" t="n">
-        <v>13.7456</v>
+        <v>12.1704</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.14</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2247</v>
+        <v>0.1811</v>
       </c>
       <c r="J289" t="n">
-        <v>4.9434</v>
+        <v>3.9842</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.85</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2181</v>
+        <v>-0.1987</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.7982</v>
+        <v>-4.3714</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.259</v>
+        <v>-0.2408</v>
       </c>
       <c r="J291" t="n">
-        <v>-5.698</v>
+        <v>-5.2976</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.44</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0569</v>
+        <v>1.0657</v>
       </c>
       <c r="J292" t="n">
-        <v>23.2518</v>
+        <v>23.4454</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.2</v>
       </c>
       <c r="I293" t="n">
-        <v>0.5729</v>
+        <v>0.5332</v>
       </c>
       <c r="J293" t="n">
-        <v>12.6038</v>
+        <v>11.7304</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.04</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1622</v>
+        <v>0.1337</v>
       </c>
       <c r="J294" t="n">
-        <v>3.5684</v>
+        <v>2.9414</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5746</v>
+        <v>-0.535</v>
       </c>
       <c r="J295" t="n">
-        <v>-12.6412</v>
+        <v>-11.77</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.76</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6884</v>
+        <v>-0.6552</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.1448</v>
+        <v>-14.4144</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.42</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7691</v>
+        <v>0.7143</v>
       </c>
       <c r="J297" t="n">
-        <v>16.9202</v>
+        <v>15.7146</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.12</v>
       </c>
       <c r="I298" t="n">
-        <v>0.2842</v>
+        <v>0.2356</v>
       </c>
       <c r="J298" t="n">
-        <v>6.2524</v>
+        <v>5.1832</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2463</v>
+        <v>0.2012</v>
       </c>
       <c r="J299" t="n">
-        <v>5.4186</v>
+        <v>4.4264</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.97</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.061</v>
+        <v>-0.0476</v>
       </c>
       <c r="J300" t="n">
-        <v>-1.342</v>
+        <v>-1.0472</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.58</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4576</v>
+        <v>-0.4542</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.0672</v>
+        <v>-9.9924</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.67</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3061</v>
+        <v>1.3256</v>
       </c>
       <c r="J302" t="n">
-        <v>24.8159</v>
+        <v>25.1864</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>1.0972</v>
+        <v>1.1092</v>
       </c>
       <c r="J303" t="n">
-        <v>20.8468</v>
+        <v>21.0748</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.44</v>
       </c>
       <c r="I304" t="n">
-        <v>0.996</v>
+        <v>0.9951</v>
       </c>
       <c r="J304" t="n">
-        <v>18.924</v>
+        <v>18.9069</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.99</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.112</v>
+        <v>-0.0924</v>
       </c>
       <c r="J305" t="n">
-        <v>-2.128</v>
+        <v>-1.7556</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2862</v>
+        <v>-0.2503</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.4378</v>
+        <v>-4.7557</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.44</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8602</v>
+        <v>0.8235</v>
       </c>
       <c r="J307" t="n">
-        <v>16.3438</v>
+        <v>15.6465</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2312</v>
+        <v>-0.2117</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.3928</v>
+        <v>-4.0223</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.75</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2893</v>
+        <v>-0.271</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.4967</v>
+        <v>-5.149</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.71</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3269</v>
+        <v>-0.3102</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.2111</v>
+        <v>-5.8938</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3454</v>
+        <v>-0.3298</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.5626</v>
+        <v>-6.2662</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.43</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0075</v>
+        <v>1.0056</v>
       </c>
       <c r="J312" t="n">
-        <v>22.165</v>
+        <v>22.1232</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.33</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8193</v>
+        <v>0.7954</v>
       </c>
       <c r="J313" t="n">
-        <v>18.0246</v>
+        <v>17.4988</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3899</v>
+        <v>0.3545</v>
       </c>
       <c r="J314" t="n">
-        <v>8.5778</v>
+        <v>7.799</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.06</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2044</v>
+        <v>0.1758</v>
       </c>
       <c r="J315" t="n">
-        <v>4.4968</v>
+        <v>3.8676</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3482</v>
+        <v>-0.3069</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.6604</v>
+        <v>-6.7518</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.07</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2154</v>
+        <v>0.1729</v>
       </c>
       <c r="J317" t="n">
-        <v>4.7388</v>
+        <v>3.8038</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.04</v>
       </c>
       <c r="I318" t="n">
-        <v>0.1461</v>
+        <v>0.112</v>
       </c>
       <c r="J318" t="n">
-        <v>3.2142</v>
+        <v>2.464</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.84</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2017</v>
+        <v>-0.1823</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.4374</v>
+        <v>-4.0106</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.82</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2219</v>
+        <v>-0.2023</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.8818</v>
+        <v>-4.4506</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.67</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3645</v>
+        <v>-0.3503</v>
       </c>
       <c r="J321" t="n">
-        <v>-8.019</v>
+        <v>-7.7066</v>
       </c>
     </row>
   </sheetData>
